--- a/Bilan_2026_MTCB.xlsx
+++ b/Bilan_2026_MTCB.xlsx
@@ -39,7 +39,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +58,11 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="19">
     <border>
@@ -313,7 +318,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -354,6 +359,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -751,14 +766,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="D1:L30"/>
+  <dimension ref="D1:L257"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="37.42578125" bestFit="1" customWidth="1" min="4" max="4"/>
     <col width="10.29" bestFit="1" customWidth="1" min="5" max="5"/>
     <col width="32.29" customWidth="1" min="6" max="6"/>
     <col width="9" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
     <col width="47.29" bestFit="1" customWidth="1" min="9" max="9"/>
     <col width="8.43" bestFit="1" customWidth="1" min="10" max="10"/>
     <col width="7.71" bestFit="1" customWidth="1" min="11" max="11"/>
@@ -1273,16 +1288,3908 @@
       <c r="L29" s="35" t="n"/>
     </row>
     <row r="30">
-      <c r="G30" s="34">
-        <f>SUM(G6:G29)</f>
+      <c r="E30" s="16" t="inlineStr">
+        <is>
+          <t>Février</t>
+        </is>
+      </c>
+      <c r="F30" s="17" t="inlineStr">
+        <is>
+          <t>LAM2601</t>
+        </is>
+      </c>
+      <c r="G30" s="31" t="n">
+        <v>4057.5</v>
+      </c>
+      <c r="H30" s="32" t="n"/>
+      <c r="I30" s="28" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J30" s="36" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K30" s="28" t="n"/>
+      <c r="L30" s="32" t="inlineStr">
+        <is>
+          <t>Administration communale, Bruxelles</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="E31" s="16" t="n"/>
+      <c r="F31" s="37" t="inlineStr">
+        <is>
+          <t>Approvisionnement compte - Thibault Duchène</t>
+        </is>
+      </c>
+      <c r="G31" s="38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H31" s="39" t="inlineStr">
+        <is>
+          <t>Apport du gérant, pas un produit — à traiter en compte courant</t>
+        </is>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>Carburant</t>
+        </is>
+      </c>
+      <c r="J31" s="33" t="n">
+        <v>63.37</v>
+      </c>
+      <c r="K31" s="28" t="n"/>
+      <c r="L31" s="32" t="n"/>
+    </row>
+    <row r="32">
+      <c r="E32" s="16" t="n"/>
+      <c r="F32" s="37" t="inlineStr">
+        <is>
+          <t>Alimentation du compte - Thibault Duchène</t>
+        </is>
+      </c>
+      <c r="G32" s="38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H32" s="39" t="inlineStr">
+        <is>
+          <t>Apport du gérant, pas un produit — à traiter en compte courant</t>
+        </is>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>Précompte salarial janvier 2026 Thibault Duchène</t>
+        </is>
+      </c>
+      <c r="J32" s="33" t="n">
+        <v>2250</v>
+      </c>
+      <c r="K32" s="28" t="n"/>
+      <c r="L32" s="32" t="n"/>
+    </row>
+    <row r="33">
+      <c r="E33" s="16" t="n"/>
+      <c r="F33" s="17" t="inlineStr">
+        <is>
+          <t>LAM2602</t>
+        </is>
+      </c>
+      <c r="G33" s="31" t="n">
+        <v>5790.15</v>
+      </c>
+      <c r="H33" s="32" t="n"/>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>SD Worx</t>
+        </is>
+      </c>
+      <c r="J33" s="33" t="n">
+        <v>332.49</v>
+      </c>
+      <c r="K33" s="28" t="n"/>
+      <c r="L33" s="32" t="n"/>
+    </row>
+    <row r="34">
+      <c r="E34" s="16" t="n"/>
+      <c r="F34" s="17" t="inlineStr">
+        <is>
+          <t>Remboursement contrats Babolat - RTC Lambermont</t>
+        </is>
+      </c>
+      <c r="G34" s="31" t="n">
+        <v>440</v>
+      </c>
+      <c r="H34" s="32" t="n"/>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J34" s="33" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K34" s="28" t="n"/>
+      <c r="L34" s="32" t="n"/>
+    </row>
+    <row r="35">
+      <c r="E35" s="16" t="n"/>
+      <c r="F35" s="17" t="n"/>
+      <c r="G35" s="31" t="n"/>
+      <c r="H35" s="32" t="n"/>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>Crédit voiture</t>
+        </is>
+      </c>
+      <c r="J35" s="33" t="n">
+        <v>724.12</v>
+      </c>
+      <c r="K35" s="28" t="n"/>
+      <c r="L35" s="32" t="n"/>
+    </row>
+    <row r="36">
+      <c r="E36" s="16" t="n"/>
+      <c r="F36" s="17" t="n"/>
+      <c r="G36" s="31" t="n"/>
+      <c r="H36" s="32" t="n"/>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>Farys (eau)</t>
+        </is>
+      </c>
+      <c r="J36" s="33" t="n">
+        <v>306</v>
+      </c>
+      <c r="K36" s="28" t="n"/>
+      <c r="L36" s="32" t="n"/>
+    </row>
+    <row r="37">
+      <c r="E37" s="16" t="n"/>
+      <c r="F37" s="17" t="n"/>
+      <c r="G37" s="31" t="n"/>
+      <c r="H37" s="32" t="n"/>
+      <c r="I37" s="40" t="inlineStr">
+        <is>
+          <t>Abonnement club David Lloyd</t>
+        </is>
+      </c>
+      <c r="J37" s="41" t="n">
+        <v>1027.75</v>
+      </c>
+      <c r="K37" s="28" t="n"/>
+      <c r="L37" s="39" t="inlineStr">
+        <is>
+          <t>Sterrebeek — usage professionnel à confirmer</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="E38" s="16" t="n"/>
+      <c r="F38" s="17" t="n"/>
+      <c r="G38" s="31" t="n"/>
+      <c r="H38" s="32" t="n"/>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J38" s="33" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="K38" s="28" t="n"/>
+      <c r="L38" s="32" t="n"/>
+    </row>
+    <row r="39">
+      <c r="E39" s="16" t="n"/>
+      <c r="F39" s="17" t="n"/>
+      <c r="G39" s="31" t="n"/>
+      <c r="H39" s="32" t="n"/>
+      <c r="I39" s="40" t="inlineStr">
+        <is>
+          <t>Abonnement club David Lloyd</t>
+        </is>
+      </c>
+      <c r="J39" s="41" t="n">
+        <v>1061</v>
+      </c>
+      <c r="K39" s="28" t="n"/>
+      <c r="L39" s="39" t="inlineStr">
+        <is>
+          <t>Sterrebeek — usage professionnel à confirmer</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="E40" s="16" t="n"/>
+      <c r="F40" s="17" t="n"/>
+      <c r="G40" s="31" t="n"/>
+      <c r="H40" s="32" t="n"/>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>Electrabel</t>
+        </is>
+      </c>
+      <c r="J40" s="33" t="n">
+        <v>263.44</v>
+      </c>
+      <c r="K40" s="28" t="n"/>
+      <c r="L40" s="32" t="n"/>
+    </row>
+    <row r="41">
+      <c r="E41" s="16" t="n"/>
+      <c r="F41" s="17" t="n"/>
+      <c r="G41" s="31" t="n"/>
+      <c r="H41" s="32" t="n"/>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>Réception marchandise - FEDEX</t>
+        </is>
+      </c>
+      <c r="J41" s="33" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="K41" s="28" t="n"/>
+      <c r="L41" s="32" t="n"/>
+    </row>
+    <row r="42">
+      <c r="E42" s="16" t="n"/>
+      <c r="F42" s="17" t="n"/>
+      <c r="G42" s="31" t="n"/>
+      <c r="H42" s="32" t="n"/>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J42" s="33" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K42" s="28" t="n"/>
+      <c r="L42" s="32" t="n"/>
+    </row>
+    <row r="43">
+      <c r="E43" s="16" t="n"/>
+      <c r="F43" s="17" t="n"/>
+      <c r="G43" s="31" t="n"/>
+      <c r="H43" s="32" t="n"/>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>Carburant</t>
+        </is>
+      </c>
+      <c r="J43" s="33" t="n">
+        <v>64.23999999999999</v>
+      </c>
+      <c r="K43" s="28" t="n"/>
+      <c r="L43" s="32" t="n"/>
+    </row>
+    <row r="44">
+      <c r="E44" s="16" t="n"/>
+      <c r="F44" s="17" t="n"/>
+      <c r="G44" s="31" t="n"/>
+      <c r="H44" s="32" t="n"/>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J44" s="33" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="K44" s="28" t="n"/>
+      <c r="L44" s="32" t="n"/>
+    </row>
+    <row r="45">
+      <c r="E45" s="16" t="n"/>
+      <c r="F45" s="17" t="n"/>
+      <c r="G45" s="31" t="n"/>
+      <c r="H45" s="32" t="n"/>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J45" s="33" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K45" s="28" t="n"/>
+      <c r="L45" s="32" t="n"/>
+    </row>
+    <row r="46">
+      <c r="E46" s="16" t="n"/>
+      <c r="F46" s="17" t="n"/>
+      <c r="G46" s="31" t="n"/>
+      <c r="H46" s="32" t="n"/>
+      <c r="I46" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J46" s="33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K46" s="28" t="n"/>
+      <c r="L46" s="32" t="n"/>
+    </row>
+    <row r="47">
+      <c r="E47" s="16" t="n"/>
+      <c r="F47" s="17" t="n"/>
+      <c r="G47" s="31" t="n"/>
+      <c r="H47" s="32" t="n"/>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>Carburant</t>
+        </is>
+      </c>
+      <c r="J47" s="33" t="n">
+        <v>63.63</v>
+      </c>
+      <c r="K47" s="28" t="n"/>
+      <c r="L47" s="32" t="n"/>
+    </row>
+    <row r="48">
+      <c r="E48" s="16" t="n"/>
+      <c r="F48" s="17" t="n"/>
+      <c r="G48" s="31" t="n"/>
+      <c r="H48" s="32" t="n"/>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>Péage autoroute France</t>
+        </is>
+      </c>
+      <c r="J48" s="33" t="n">
+        <v>42</v>
+      </c>
+      <c r="K48" s="28" t="n"/>
+      <c r="L48" s="32" t="n"/>
+    </row>
+    <row r="49">
+      <c r="E49" s="16" t="n"/>
+      <c r="F49" s="17" t="n"/>
+      <c r="G49" s="31" t="n"/>
+      <c r="H49" s="32" t="n"/>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>Consommation - SV Victoria</t>
+        </is>
+      </c>
+      <c r="J49" s="33" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="K49" s="28" t="n"/>
+      <c r="L49" s="32" t="inlineStr">
+        <is>
+          <t>Rotterdam (Pays-Bas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="E50" s="16" t="n"/>
+      <c r="F50" s="17" t="n"/>
+      <c r="G50" s="31" t="n"/>
+      <c r="H50" s="32" t="n"/>
+      <c r="I50" s="13" t="inlineStr">
+        <is>
+          <t>Consommation - SV Victoria</t>
+        </is>
+      </c>
+      <c r="J50" s="33" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="K50" s="28" t="n"/>
+      <c r="L50" s="32" t="inlineStr">
+        <is>
+          <t>Rotterdam (Pays-Bas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="E51" s="16" t="n"/>
+      <c r="F51" s="17" t="n"/>
+      <c r="G51" s="31" t="n"/>
+      <c r="H51" s="32" t="n"/>
+      <c r="I51" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J51" s="33" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="K51" s="28" t="n"/>
+      <c r="L51" s="32" t="n"/>
+    </row>
+    <row r="52">
+      <c r="E52" s="16" t="n"/>
+      <c r="F52" s="17" t="n"/>
+      <c r="G52" s="31" t="n"/>
+      <c r="H52" s="32" t="n"/>
+      <c r="I52" s="13" t="inlineStr">
+        <is>
+          <t>Achat vêtements sport - NIKE</t>
+        </is>
+      </c>
+      <c r="J52" s="33" t="n">
+        <v>230.48</v>
+      </c>
+      <c r="K52" s="28" t="n"/>
+      <c r="L52" s="32" t="n"/>
+    </row>
+    <row r="53">
+      <c r="E53" s="16" t="n"/>
+      <c r="F53" s="17" t="n"/>
+      <c r="G53" s="31" t="n"/>
+      <c r="H53" s="32" t="n"/>
+      <c r="I53" s="13" t="inlineStr">
+        <is>
+          <t>Achat vêtements sport - Sportsdirect</t>
+        </is>
+      </c>
+      <c r="J53" s="33" t="n">
+        <v>112</v>
+      </c>
+      <c r="K53" s="28" t="n"/>
+      <c r="L53" s="32" t="n"/>
+    </row>
+    <row r="54">
+      <c r="E54" s="16" t="n"/>
+      <c r="F54" s="17" t="n"/>
+      <c r="G54" s="31" t="n"/>
+      <c r="H54" s="32" t="n"/>
+      <c r="I54" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J54" s="33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K54" s="28" t="n"/>
+      <c r="L54" s="32" t="n"/>
+    </row>
+    <row r="55">
+      <c r="E55" s="16" t="n"/>
+      <c r="F55" s="17" t="n"/>
+      <c r="G55" s="31" t="n"/>
+      <c r="H55" s="32" t="n"/>
+      <c r="I55" s="13" t="inlineStr">
+        <is>
+          <t>Carburant</t>
+        </is>
+      </c>
+      <c r="J55" s="33" t="n">
+        <v>62.54</v>
+      </c>
+      <c r="K55" s="28" t="n"/>
+      <c r="L55" s="32" t="n"/>
+    </row>
+    <row r="56">
+      <c r="E56" s="16" t="n"/>
+      <c r="F56" s="17" t="n"/>
+      <c r="G56" s="31" t="n"/>
+      <c r="H56" s="32" t="n"/>
+      <c r="I56" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J56" s="33" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K56" s="28" t="n"/>
+      <c r="L56" s="32" t="n"/>
+    </row>
+    <row r="57">
+      <c r="E57" s="16" t="n"/>
+      <c r="F57" s="17" t="n"/>
+      <c r="G57" s="31" t="n"/>
+      <c r="H57" s="32" t="n"/>
+      <c r="I57" s="13" t="inlineStr">
+        <is>
+          <t>Précompte salarial fevrier 2026 Thibault Duchène</t>
+        </is>
+      </c>
+      <c r="J57" s="33" t="n">
+        <v>2250</v>
+      </c>
+      <c r="K57" s="28" t="n"/>
+      <c r="L57" s="32" t="n"/>
+    </row>
+    <row r="58">
+      <c r="E58" s="16" t="n"/>
+      <c r="F58" s="17" t="n"/>
+      <c r="G58" s="31" t="n"/>
+      <c r="H58" s="32" t="n"/>
+      <c r="I58" s="13" t="inlineStr">
+        <is>
+          <t>SD Worx</t>
+        </is>
+      </c>
+      <c r="J58" s="33" t="n">
+        <v>332.49</v>
+      </c>
+      <c r="K58" s="28" t="n"/>
+      <c r="L58" s="32" t="n"/>
+    </row>
+    <row r="59">
+      <c r="E59" s="16" t="n"/>
+      <c r="F59" s="17" t="n"/>
+      <c r="G59" s="31" t="n"/>
+      <c r="H59" s="32" t="n"/>
+      <c r="I59" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J59" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="K59" s="28" t="n"/>
+      <c r="L59" s="32" t="n"/>
+    </row>
+    <row r="60">
+      <c r="G60" s="34" t="n"/>
+      <c r="H60" s="35" t="n"/>
+      <c r="J60" s="34" t="n"/>
+      <c r="L60" s="35" t="n"/>
+    </row>
+    <row r="61">
+      <c r="G61" s="34" t="n"/>
+      <c r="H61" s="35" t="n"/>
+      <c r="J61" s="34" t="n"/>
+      <c r="L61" s="35" t="n"/>
+    </row>
+    <row r="62">
+      <c r="E62" s="16" t="inlineStr">
+        <is>
+          <t>Mars</t>
+        </is>
+      </c>
+      <c r="F62" s="37" t="inlineStr">
+        <is>
+          <t>Dépôt d'espèces</t>
+        </is>
+      </c>
+      <c r="G62" s="38" t="n">
+        <v>2600</v>
+      </c>
+      <c r="H62" s="39" t="inlineStr">
+        <is>
+          <t>Versement au distributeur, communication « PAIEMENTS » — origine des fonds à documenter</t>
+        </is>
+      </c>
+      <c r="I62" s="28" t="inlineStr">
+        <is>
+          <t>Achat vêtements sport - NIKE</t>
+        </is>
+      </c>
+      <c r="J62" s="36" t="n">
+        <v>130.46</v>
+      </c>
+      <c r="K62" s="28" t="n"/>
+      <c r="L62" s="32" t="n"/>
+    </row>
+    <row r="63">
+      <c r="E63" s="16" t="n"/>
+      <c r="F63" s="17" t="inlineStr">
+        <is>
+          <t>Remboursement hôtel Imola - Thibault Duchène</t>
+        </is>
+      </c>
+      <c r="G63" s="31" t="n">
+        <v>364.5</v>
+      </c>
+      <c r="H63" s="32" t="n"/>
+      <c r="I63" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J63" s="33" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K63" s="28" t="n"/>
+      <c r="L63" s="32" t="n"/>
+    </row>
+    <row r="64">
+      <c r="E64" s="16" t="n"/>
+      <c r="F64" s="17" t="inlineStr">
+        <is>
+          <t>Remboursement billet de train Bologne - Thibault Duchène</t>
+        </is>
+      </c>
+      <c r="G64" s="31" t="n">
+        <v>197.3</v>
+      </c>
+      <c r="H64" s="32" t="n"/>
+      <c r="I64" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J64" s="33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K64" s="28" t="n"/>
+      <c r="L64" s="32" t="n"/>
+    </row>
+    <row r="65">
+      <c r="E65" s="16" t="n"/>
+      <c r="F65" s="17" t="inlineStr">
+        <is>
+          <t>LAM2603</t>
+        </is>
+      </c>
+      <c r="G65" s="31" t="n">
+        <v>4110</v>
+      </c>
+      <c r="H65" s="32" t="n"/>
+      <c r="I65" s="13" t="inlineStr">
+        <is>
+          <t>Carburant</t>
+        </is>
+      </c>
+      <c r="J65" s="33" t="n">
+        <v>64.62</v>
+      </c>
+      <c r="K65" s="28" t="n"/>
+      <c r="L65" s="32" t="n"/>
+    </row>
+    <row r="66">
+      <c r="E66" s="16" t="n"/>
+      <c r="F66" s="17" t="n"/>
+      <c r="G66" s="31" t="n"/>
+      <c r="H66" s="32" t="n"/>
+      <c r="I66" s="13" t="inlineStr">
+        <is>
+          <t>Crédit voiture</t>
+        </is>
+      </c>
+      <c r="J66" s="33" t="n">
+        <v>724.12</v>
+      </c>
+      <c r="K66" s="28" t="n"/>
+      <c r="L66" s="32" t="n"/>
+    </row>
+    <row r="67">
+      <c r="E67" s="16" t="n"/>
+      <c r="F67" s="17" t="n"/>
+      <c r="G67" s="31" t="n"/>
+      <c r="H67" s="32" t="n"/>
+      <c r="I67" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J67" s="33" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="K67" s="28" t="n"/>
+      <c r="L67" s="32" t="n"/>
+    </row>
+    <row r="68">
+      <c r="E68" s="16" t="n"/>
+      <c r="F68" s="17" t="n"/>
+      <c r="G68" s="31" t="n"/>
+      <c r="H68" s="32" t="n"/>
+      <c r="I68" s="13" t="inlineStr">
+        <is>
+          <t>Partena</t>
+        </is>
+      </c>
+      <c r="J68" s="33" t="n">
+        <v>1747.34</v>
+      </c>
+      <c r="K68" s="28" t="n"/>
+      <c r="L68" s="32" t="n"/>
+    </row>
+    <row r="69">
+      <c r="E69" s="16" t="n"/>
+      <c r="F69" s="17" t="n"/>
+      <c r="G69" s="31" t="n"/>
+      <c r="H69" s="32" t="n"/>
+      <c r="I69" s="13" t="inlineStr">
+        <is>
+          <t>Partena</t>
+        </is>
+      </c>
+      <c r="J69" s="33" t="n">
+        <v>935.96</v>
+      </c>
+      <c r="K69" s="28" t="n"/>
+      <c r="L69" s="32" t="n"/>
+    </row>
+    <row r="70">
+      <c r="E70" s="16" t="n"/>
+      <c r="F70" s="17" t="n"/>
+      <c r="G70" s="31" t="n"/>
+      <c r="H70" s="32" t="n"/>
+      <c r="I70" s="13" t="inlineStr">
+        <is>
+          <t>Proximus</t>
+        </is>
+      </c>
+      <c r="J70" s="33" t="n">
+        <v>293.82</v>
+      </c>
+      <c r="K70" s="28" t="n"/>
+      <c r="L70" s="32" t="n"/>
+    </row>
+    <row r="71">
+      <c r="E71" s="16" t="n"/>
+      <c r="F71" s="17" t="n"/>
+      <c r="G71" s="31" t="n"/>
+      <c r="H71" s="32" t="n"/>
+      <c r="I71" s="13" t="inlineStr">
+        <is>
+          <t>Electrabel</t>
+        </is>
+      </c>
+      <c r="J71" s="33" t="n">
+        <v>263.44</v>
+      </c>
+      <c r="K71" s="28" t="n"/>
+      <c r="L71" s="32" t="n"/>
+    </row>
+    <row r="72">
+      <c r="E72" s="16" t="n"/>
+      <c r="F72" s="17" t="n"/>
+      <c r="G72" s="31" t="n"/>
+      <c r="H72" s="32" t="n"/>
+      <c r="I72" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J72" s="33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K72" s="28" t="n"/>
+      <c r="L72" s="32" t="n"/>
+    </row>
+    <row r="73">
+      <c r="E73" s="16" t="n"/>
+      <c r="F73" s="17" t="n"/>
+      <c r="G73" s="31" t="n"/>
+      <c r="H73" s="32" t="n"/>
+      <c r="I73" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J73" s="33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K73" s="28" t="n"/>
+      <c r="L73" s="32" t="n"/>
+    </row>
+    <row r="74">
+      <c r="E74" s="16" t="n"/>
+      <c r="F74" s="17" t="n"/>
+      <c r="G74" s="31" t="n"/>
+      <c r="H74" s="32" t="n"/>
+      <c r="I74" s="13" t="inlineStr">
+        <is>
+          <t>Remboursement alimentation du compte - Thibault Duchène</t>
+        </is>
+      </c>
+      <c r="J74" s="33" t="n">
+        <v>750</v>
+      </c>
+      <c r="K74" s="28" t="n"/>
+      <c r="L74" s="32" t="inlineStr">
+        <is>
+          <t>Restitution des apports de février 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="E75" s="16" t="n"/>
+      <c r="F75" s="17" t="n"/>
+      <c r="G75" s="31" t="n"/>
+      <c r="H75" s="32" t="n"/>
+      <c r="I75" s="13" t="inlineStr">
+        <is>
+          <t>Carburant</t>
+        </is>
+      </c>
+      <c r="J75" s="33" t="n">
+        <v>76.45</v>
+      </c>
+      <c r="K75" s="28" t="n"/>
+      <c r="L75" s="32" t="n"/>
+    </row>
+    <row r="76">
+      <c r="E76" s="16" t="n"/>
+      <c r="F76" s="17" t="n"/>
+      <c r="G76" s="31" t="n"/>
+      <c r="H76" s="32" t="n"/>
+      <c r="I76" s="13" t="inlineStr">
+        <is>
+          <t>Paiement carte de crédit</t>
+        </is>
+      </c>
+      <c r="J76" s="33" t="n">
+        <v>1104.46</v>
+      </c>
+      <c r="K76" s="28" t="n"/>
+      <c r="L76" s="32" t="n"/>
+    </row>
+    <row r="77">
+      <c r="E77" s="16" t="n"/>
+      <c r="F77" s="17" t="n"/>
+      <c r="G77" s="31" t="n"/>
+      <c r="H77" s="32" t="n"/>
+      <c r="I77" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J77" s="33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K77" s="28" t="n"/>
+      <c r="L77" s="32" t="n"/>
+    </row>
+    <row r="78">
+      <c r="E78" s="16" t="n"/>
+      <c r="F78" s="17" t="n"/>
+      <c r="G78" s="31" t="n"/>
+      <c r="H78" s="32" t="n"/>
+      <c r="I78" s="13" t="inlineStr">
+        <is>
+          <t>Carburant</t>
+        </is>
+      </c>
+      <c r="J78" s="33" t="n">
+        <v>65.54000000000001</v>
+      </c>
+      <c r="K78" s="28" t="n"/>
+      <c r="L78" s="32" t="n"/>
+    </row>
+    <row r="79">
+      <c r="E79" s="16" t="n"/>
+      <c r="F79" s="17" t="n"/>
+      <c r="G79" s="31" t="n"/>
+      <c r="H79" s="32" t="n"/>
+      <c r="I79" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J79" s="33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K79" s="28" t="n"/>
+      <c r="L79" s="32" t="n"/>
+    </row>
+    <row r="80">
+      <c r="E80" s="16" t="n"/>
+      <c r="F80" s="17" t="n"/>
+      <c r="G80" s="31" t="n"/>
+      <c r="H80" s="32" t="n"/>
+      <c r="I80" s="13" t="inlineStr">
+        <is>
+          <t>Carburant</t>
+        </is>
+      </c>
+      <c r="J80" s="33" t="n">
+        <v>63.82</v>
+      </c>
+      <c r="K80" s="28" t="n"/>
+      <c r="L80" s="32" t="n"/>
+    </row>
+    <row r="81">
+      <c r="E81" s="16" t="n"/>
+      <c r="F81" s="17" t="n"/>
+      <c r="G81" s="31" t="n"/>
+      <c r="H81" s="32" t="n"/>
+      <c r="I81" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J81" s="33" t="n">
+        <v>9</v>
+      </c>
+      <c r="K81" s="28" t="n"/>
+      <c r="L81" s="32" t="inlineStr">
+        <is>
+          <t>Düsseldorf (Allemagne)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="E82" s="16" t="n"/>
+      <c r="F82" s="17" t="n"/>
+      <c r="G82" s="31" t="n"/>
+      <c r="H82" s="32" t="n"/>
+      <c r="I82" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J82" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="K82" s="28" t="n"/>
+      <c r="L82" s="32" t="inlineStr">
+        <is>
+          <t>Düsseldorf (Allemagne)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="E83" s="16" t="n"/>
+      <c r="F83" s="17" t="n"/>
+      <c r="G83" s="31" t="n"/>
+      <c r="H83" s="32" t="n"/>
+      <c r="I83" s="13" t="inlineStr">
+        <is>
+          <t>Carburant</t>
+        </is>
+      </c>
+      <c r="J83" s="33" t="n">
+        <v>84.56</v>
+      </c>
+      <c r="K83" s="28" t="n"/>
+      <c r="L83" s="32" t="n"/>
+    </row>
+    <row r="84">
+      <c r="E84" s="16" t="n"/>
+      <c r="F84" s="17" t="n"/>
+      <c r="G84" s="31" t="n"/>
+      <c r="H84" s="32" t="n"/>
+      <c r="I84" s="40" t="inlineStr">
+        <is>
+          <t>Parking - Chirec</t>
+        </is>
+      </c>
+      <c r="J84" s="41" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="K84" s="28" t="n"/>
+      <c r="L84" s="39" t="inlineStr">
+        <is>
+          <t>Hôpital, Bruxelles — à confirmer</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="E85" s="16" t="n"/>
+      <c r="F85" s="17" t="n"/>
+      <c r="G85" s="31" t="n"/>
+      <c r="H85" s="32" t="n"/>
+      <c r="I85" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J85" s="33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K85" s="28" t="n"/>
+      <c r="L85" s="32" t="n"/>
+    </row>
+    <row r="86">
+      <c r="E86" s="16" t="n"/>
+      <c r="F86" s="17" t="n"/>
+      <c r="G86" s="31" t="n"/>
+      <c r="H86" s="32" t="n"/>
+      <c r="I86" s="13" t="inlineStr">
+        <is>
+          <t>Précompte salarial mars 2026 Thibault Duchène</t>
+        </is>
+      </c>
+      <c r="J86" s="33" t="n">
+        <v>2250</v>
+      </c>
+      <c r="K86" s="28" t="n"/>
+      <c r="L86" s="32" t="n"/>
+    </row>
+    <row r="87">
+      <c r="E87" s="16" t="n"/>
+      <c r="F87" s="17" t="n"/>
+      <c r="G87" s="31" t="n"/>
+      <c r="H87" s="32" t="n"/>
+      <c r="I87" s="40" t="inlineStr">
+        <is>
+          <t>Achat - Berca</t>
+        </is>
+      </c>
+      <c r="J87" s="41" t="n">
+        <v>38.97</v>
+      </c>
+      <c r="K87" s="28" t="n"/>
+      <c r="L87" s="39" t="inlineStr">
+        <is>
+          <t>Ardooie — à identifier</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="E88" s="16" t="n"/>
+      <c r="F88" s="17" t="n"/>
+      <c r="G88" s="31" t="n"/>
+      <c r="H88" s="32" t="n"/>
+      <c r="I88" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J88" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="K88" s="28" t="n"/>
+      <c r="L88" s="32" t="inlineStr">
+        <is>
+          <t>Italie</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="E89" s="16" t="n"/>
+      <c r="F89" s="17" t="n"/>
+      <c r="G89" s="31" t="n"/>
+      <c r="H89" s="32" t="n"/>
+      <c r="I89" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J89" s="33" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="K89" s="28" t="n"/>
+      <c r="L89" s="32" t="inlineStr">
+        <is>
+          <t>Italie</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="E90" s="16" t="n"/>
+      <c r="F90" s="17" t="n"/>
+      <c r="G90" s="31" t="n"/>
+      <c r="H90" s="32" t="n"/>
+      <c r="I90" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J90" s="33" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="K90" s="28" t="n"/>
+      <c r="L90" s="32" t="inlineStr">
+        <is>
+          <t>Italie</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="E91" s="16" t="n"/>
+      <c r="F91" s="17" t="n"/>
+      <c r="G91" s="31" t="n"/>
+      <c r="H91" s="32" t="n"/>
+      <c r="I91" s="13" t="inlineStr">
+        <is>
+          <t>Remboursement alimentation du compte - Thibault Duchène</t>
+        </is>
+      </c>
+      <c r="J91" s="33" t="n">
+        <v>750</v>
+      </c>
+      <c r="K91" s="28" t="n"/>
+      <c r="L91" s="32" t="inlineStr">
+        <is>
+          <t>Restitution des apports de février 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="E92" s="16" t="n"/>
+      <c r="F92" s="17" t="n"/>
+      <c r="G92" s="31" t="n"/>
+      <c r="H92" s="32" t="n"/>
+      <c r="I92" s="13" t="inlineStr">
+        <is>
+          <t>SD Worx</t>
+        </is>
+      </c>
+      <c r="J92" s="33" t="n">
+        <v>332.49</v>
+      </c>
+      <c r="K92" s="28" t="n"/>
+      <c r="L92" s="32" t="n"/>
+    </row>
+    <row r="93">
+      <c r="E93" s="16" t="n"/>
+      <c r="F93" s="17" t="n"/>
+      <c r="G93" s="31" t="n"/>
+      <c r="H93" s="32" t="n"/>
+      <c r="I93" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J93" s="33" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="K93" s="28" t="n"/>
+      <c r="L93" s="32" t="inlineStr">
+        <is>
+          <t>Italie</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="E94" s="16" t="n"/>
+      <c r="F94" s="17" t="n"/>
+      <c r="G94" s="31" t="n"/>
+      <c r="H94" s="32" t="n"/>
+      <c r="I94" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J94" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K94" s="28" t="n"/>
+      <c r="L94" s="32" t="inlineStr">
+        <is>
+          <t>Italie</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="G95" s="34" t="n"/>
+      <c r="H95" s="35" t="n"/>
+      <c r="J95" s="34" t="n"/>
+      <c r="L95" s="35" t="n"/>
+    </row>
+    <row r="96">
+      <c r="G96" s="34" t="n"/>
+      <c r="H96" s="35" t="n"/>
+      <c r="J96" s="34" t="n"/>
+      <c r="L96" s="35" t="n"/>
+    </row>
+    <row r="97">
+      <c r="E97" s="16" t="inlineStr">
+        <is>
+          <t>Avril</t>
+        </is>
+      </c>
+      <c r="F97" s="17" t="inlineStr">
+        <is>
+          <t>LAM2604</t>
+        </is>
+      </c>
+      <c r="G97" s="31" t="n">
+        <v>7000</v>
+      </c>
+      <c r="H97" s="32" t="n"/>
+      <c r="I97" s="28" t="inlineStr">
+        <is>
+          <t>Carburant</t>
+        </is>
+      </c>
+      <c r="J97" s="36" t="n">
+        <v>64.48</v>
+      </c>
+      <c r="K97" s="28" t="n"/>
+      <c r="L97" s="32" t="inlineStr">
+        <is>
+          <t>ENI (Italie)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="E98" s="16" t="n"/>
+      <c r="F98" s="17" t="inlineStr">
+        <is>
+          <t>Remboursement d'impôt - SPF Finances</t>
+        </is>
+      </c>
+      <c r="G98" s="31" t="n">
+        <v>2349.66</v>
+      </c>
+      <c r="H98" s="32" t="inlineStr">
+        <is>
+          <t>Rôle 0867847943</t>
+        </is>
+      </c>
+      <c r="I98" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J98" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="K98" s="28" t="n"/>
+      <c r="L98" s="32" t="inlineStr">
+        <is>
+          <t>Italie</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="E99" s="16" t="n"/>
+      <c r="F99" s="17" t="n"/>
+      <c r="G99" s="31" t="n"/>
+      <c r="H99" s="32" t="n"/>
+      <c r="I99" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J99" s="33" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K99" s="28" t="n"/>
+      <c r="L99" s="32" t="inlineStr">
+        <is>
+          <t>Italie</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="E100" s="16" t="n"/>
+      <c r="F100" s="17" t="n"/>
+      <c r="G100" s="31" t="n"/>
+      <c r="H100" s="32" t="n"/>
+      <c r="I100" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J100" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="K100" s="28" t="n"/>
+      <c r="L100" s="32" t="inlineStr">
+        <is>
+          <t>Italie</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="E101" s="16" t="n"/>
+      <c r="F101" s="17" t="n"/>
+      <c r="G101" s="31" t="n"/>
+      <c r="H101" s="32" t="n"/>
+      <c r="I101" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J101" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="K101" s="28" t="n"/>
+      <c r="L101" s="32" t="inlineStr">
+        <is>
+          <t>Italie</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="E102" s="16" t="n"/>
+      <c r="F102" s="17" t="n"/>
+      <c r="G102" s="31" t="n"/>
+      <c r="H102" s="32" t="n"/>
+      <c r="I102" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J102" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="K102" s="28" t="n"/>
+      <c r="L102" s="32" t="inlineStr">
+        <is>
+          <t>Italie</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="E103" s="16" t="n"/>
+      <c r="F103" s="17" t="n"/>
+      <c r="G103" s="31" t="n"/>
+      <c r="H103" s="32" t="n"/>
+      <c r="I103" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J103" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="K103" s="28" t="n"/>
+      <c r="L103" s="32" t="inlineStr">
+        <is>
+          <t>Italie</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="E104" s="16" t="n"/>
+      <c r="F104" s="17" t="n"/>
+      <c r="G104" s="31" t="n"/>
+      <c r="H104" s="32" t="n"/>
+      <c r="I104" s="13" t="inlineStr">
+        <is>
+          <t>Carburant</t>
+        </is>
+      </c>
+      <c r="J104" s="33" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="K104" s="28" t="n"/>
+      <c r="L104" s="32" t="inlineStr">
+        <is>
+          <t>ENI (Italie)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="E105" s="16" t="n"/>
+      <c r="F105" s="17" t="n"/>
+      <c r="G105" s="31" t="n"/>
+      <c r="H105" s="32" t="n"/>
+      <c r="I105" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J105" s="33" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="K105" s="28" t="n"/>
+      <c r="L105" s="32" t="inlineStr">
+        <is>
+          <t>Italie</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="E106" s="16" t="n"/>
+      <c r="F106" s="17" t="n"/>
+      <c r="G106" s="31" t="n"/>
+      <c r="H106" s="32" t="n"/>
+      <c r="I106" s="13" t="inlineStr">
+        <is>
+          <t>Crédit voiture</t>
+        </is>
+      </c>
+      <c r="J106" s="33" t="n">
+        <v>724.12</v>
+      </c>
+      <c r="K106" s="28" t="n"/>
+      <c r="L106" s="32" t="n"/>
+    </row>
+    <row r="107">
+      <c r="E107" s="16" t="n"/>
+      <c r="F107" s="17" t="n"/>
+      <c r="G107" s="31" t="n"/>
+      <c r="H107" s="32" t="n"/>
+      <c r="I107" s="13" t="inlineStr">
+        <is>
+          <t>Proximus</t>
+        </is>
+      </c>
+      <c r="J107" s="33" t="n">
+        <v>264.52</v>
+      </c>
+      <c r="K107" s="28" t="n"/>
+      <c r="L107" s="32" t="n"/>
+    </row>
+    <row r="108">
+      <c r="E108" s="16" t="n"/>
+      <c r="F108" s="17" t="n"/>
+      <c r="G108" s="31" t="n"/>
+      <c r="H108" s="32" t="n"/>
+      <c r="I108" s="13" t="inlineStr">
+        <is>
+          <t>Lavage voiture</t>
+        </is>
+      </c>
+      <c r="J108" s="33" t="n">
+        <v>34</v>
+      </c>
+      <c r="K108" s="28" t="n"/>
+      <c r="L108" s="32" t="inlineStr">
+        <is>
+          <t>Wash Time Tervuren</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="E109" s="16" t="n"/>
+      <c r="F109" s="17" t="n"/>
+      <c r="G109" s="31" t="n"/>
+      <c r="H109" s="32" t="n"/>
+      <c r="I109" s="13" t="inlineStr">
+        <is>
+          <t>Transport - STIB</t>
+        </is>
+      </c>
+      <c r="J109" s="33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K109" s="28" t="n"/>
+      <c r="L109" s="32" t="n"/>
+    </row>
+    <row r="110">
+      <c r="E110" s="16" t="n"/>
+      <c r="F110" s="17" t="n"/>
+      <c r="G110" s="31" t="n"/>
+      <c r="H110" s="32" t="n"/>
+      <c r="I110" s="13" t="inlineStr">
+        <is>
+          <t>Versement impôts anticipé</t>
+        </is>
+      </c>
+      <c r="J110" s="33" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K110" s="28" t="n"/>
+      <c r="L110" s="32" t="inlineStr">
+        <is>
+          <t>Comm. 073/4616/33527</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="E111" s="16" t="n"/>
+      <c r="F111" s="17" t="n"/>
+      <c r="G111" s="31" t="n"/>
+      <c r="H111" s="32" t="n"/>
+      <c r="I111" s="13" t="inlineStr">
+        <is>
+          <t>Frais comptable BDH</t>
+        </is>
+      </c>
+      <c r="J111" s="33" t="n">
+        <v>254.1</v>
+      </c>
+      <c r="K111" s="28" t="n"/>
+      <c r="L111" s="32" t="n"/>
+    </row>
+    <row r="112">
+      <c r="E112" s="16" t="n"/>
+      <c r="F112" s="17" t="n"/>
+      <c r="G112" s="31" t="n"/>
+      <c r="H112" s="32" t="n"/>
+      <c r="I112" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J112" s="33" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K112" s="28" t="n"/>
+      <c r="L112" s="32" t="inlineStr">
+        <is>
+          <t>Italie</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="E113" s="16" t="n"/>
+      <c r="F113" s="17" t="n"/>
+      <c r="G113" s="31" t="n"/>
+      <c r="H113" s="32" t="n"/>
+      <c r="I113" s="13" t="inlineStr">
+        <is>
+          <t>Farys (eau)</t>
+        </is>
+      </c>
+      <c r="J113" s="33" t="n">
+        <v>306</v>
+      </c>
+      <c r="K113" s="28" t="n"/>
+      <c r="L113" s="32" t="n"/>
+    </row>
+    <row r="114">
+      <c r="E114" s="16" t="n"/>
+      <c r="F114" s="17" t="n"/>
+      <c r="G114" s="31" t="n"/>
+      <c r="H114" s="32" t="n"/>
+      <c r="I114" s="13" t="inlineStr">
+        <is>
+          <t>Repas Lunch Garden</t>
+        </is>
+      </c>
+      <c r="J114" s="33" t="n">
+        <v>30.48</v>
+      </c>
+      <c r="K114" s="28" t="n"/>
+      <c r="L114" s="32" t="n"/>
+    </row>
+    <row r="115">
+      <c r="E115" s="16" t="n"/>
+      <c r="F115" s="17" t="n"/>
+      <c r="G115" s="31" t="n"/>
+      <c r="H115" s="32" t="n"/>
+      <c r="I115" s="13" t="inlineStr">
+        <is>
+          <t>Frais bancaires trimestriels</t>
+        </is>
+      </c>
+      <c r="J115" s="33" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="K115" s="28" t="n"/>
+      <c r="L115" s="32" t="n"/>
+    </row>
+    <row r="116">
+      <c r="E116" s="16" t="n"/>
+      <c r="F116" s="17" t="n"/>
+      <c r="G116" s="31" t="n"/>
+      <c r="H116" s="32" t="n"/>
+      <c r="I116" s="13" t="inlineStr">
+        <is>
+          <t>Collation</t>
+        </is>
+      </c>
+      <c r="J116" s="33" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="K116" s="28" t="n"/>
+      <c r="L116" s="32" t="n"/>
+    </row>
+    <row r="117">
+      <c r="E117" s="16" t="n"/>
+      <c r="F117" s="17" t="n"/>
+      <c r="G117" s="31" t="n"/>
+      <c r="H117" s="32" t="n"/>
+      <c r="I117" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J117" s="33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K117" s="28" t="n"/>
+      <c r="L117" s="32" t="n"/>
+    </row>
+    <row r="118">
+      <c r="E118" s="16" t="n"/>
+      <c r="F118" s="17" t="n"/>
+      <c r="G118" s="31" t="n"/>
+      <c r="H118" s="32" t="n"/>
+      <c r="I118" s="13" t="inlineStr">
+        <is>
+          <t>Paiement carte de crédit</t>
+        </is>
+      </c>
+      <c r="J118" s="33" t="n">
+        <v>275.86</v>
+      </c>
+      <c r="K118" s="28" t="n"/>
+      <c r="L118" s="32" t="n"/>
+    </row>
+    <row r="119">
+      <c r="E119" s="16" t="n"/>
+      <c r="F119" s="17" t="n"/>
+      <c r="G119" s="31" t="n"/>
+      <c r="H119" s="32" t="n"/>
+      <c r="I119" s="13" t="inlineStr">
+        <is>
+          <t>Carburant</t>
+        </is>
+      </c>
+      <c r="J119" s="33" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="K119" s="28" t="n"/>
+      <c r="L119" s="32" t="n"/>
+    </row>
+    <row r="120">
+      <c r="E120" s="16" t="n"/>
+      <c r="F120" s="17" t="n"/>
+      <c r="G120" s="31" t="n"/>
+      <c r="H120" s="32" t="n"/>
+      <c r="I120" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J120" s="33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K120" s="28" t="n"/>
+      <c r="L120" s="32" t="n"/>
+    </row>
+    <row r="121">
+      <c r="E121" s="16" t="n"/>
+      <c r="F121" s="17" t="n"/>
+      <c r="G121" s="31" t="n"/>
+      <c r="H121" s="32" t="n"/>
+      <c r="I121" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J121" s="33" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="K121" s="28" t="n"/>
+      <c r="L121" s="32" t="n"/>
+    </row>
+    <row r="122">
+      <c r="E122" s="16" t="n"/>
+      <c r="F122" s="17" t="n"/>
+      <c r="G122" s="31" t="n"/>
+      <c r="H122" s="32" t="n"/>
+      <c r="I122" s="40" t="inlineStr">
+        <is>
+          <t>Redevance de stationnement - OPC</t>
+        </is>
+      </c>
+      <c r="J122" s="41" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K122" s="28" t="n"/>
+      <c r="L122" s="39" t="inlineStr">
+        <is>
+          <t>à confirmer (redevance ou amende)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="E123" s="16" t="n"/>
+      <c r="F123" s="17" t="n"/>
+      <c r="G123" s="31" t="n"/>
+      <c r="H123" s="32" t="n"/>
+      <c r="I123" s="13" t="inlineStr">
+        <is>
+          <t>Carburant</t>
+        </is>
+      </c>
+      <c r="J123" s="33" t="n">
+        <v>77.88</v>
+      </c>
+      <c r="K123" s="28" t="n"/>
+      <c r="L123" s="32" t="n"/>
+    </row>
+    <row r="124">
+      <c r="E124" s="16" t="n"/>
+      <c r="F124" s="17" t="n"/>
+      <c r="G124" s="31" t="n"/>
+      <c r="H124" s="32" t="n"/>
+      <c r="I124" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J124" s="33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K124" s="28" t="n"/>
+      <c r="L124" s="32" t="n"/>
+    </row>
+    <row r="125">
+      <c r="E125" s="16" t="n"/>
+      <c r="F125" s="17" t="n"/>
+      <c r="G125" s="31" t="n"/>
+      <c r="H125" s="32" t="n"/>
+      <c r="I125" s="13" t="inlineStr">
+        <is>
+          <t>Repas Lunch Garden</t>
+        </is>
+      </c>
+      <c r="J125" s="33" t="n">
+        <v>16.54</v>
+      </c>
+      <c r="K125" s="28" t="n"/>
+      <c r="L125" s="32" t="n"/>
+    </row>
+    <row r="126">
+      <c r="E126" s="16" t="n"/>
+      <c r="F126" s="17" t="n"/>
+      <c r="G126" s="31" t="n"/>
+      <c r="H126" s="32" t="n"/>
+      <c r="I126" s="40" t="inlineStr">
+        <is>
+          <t>Achat - Orgefi SPRL</t>
+        </is>
+      </c>
+      <c r="J126" s="41" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K126" s="28" t="n"/>
+      <c r="L126" s="39" t="inlineStr">
+        <is>
+          <t>Nivelles — à identifier</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="E127" s="16" t="n"/>
+      <c r="F127" s="17" t="n"/>
+      <c r="G127" s="31" t="n"/>
+      <c r="H127" s="32" t="n"/>
+      <c r="I127" s="13" t="inlineStr">
+        <is>
+          <t>Carburant</t>
+        </is>
+      </c>
+      <c r="J127" s="33" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="K127" s="28" t="n"/>
+      <c r="L127" s="32" t="inlineStr">
+        <is>
+          <t>Total Schaerbeek</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="E128" s="16" t="n"/>
+      <c r="F128" s="17" t="n"/>
+      <c r="G128" s="31" t="n"/>
+      <c r="H128" s="32" t="n"/>
+      <c r="I128" s="40" t="inlineStr">
+        <is>
+          <t>Achat - Orgefi SPRL</t>
+        </is>
+      </c>
+      <c r="J128" s="41" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K128" s="28" t="n"/>
+      <c r="L128" s="39" t="inlineStr">
+        <is>
+          <t>Nivelles — à identifier</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="E129" s="16" t="n"/>
+      <c r="F129" s="17" t="n"/>
+      <c r="G129" s="31" t="n"/>
+      <c r="H129" s="32" t="n"/>
+      <c r="I129" s="13" t="inlineStr">
+        <is>
+          <t>Assurance voiture</t>
+        </is>
+      </c>
+      <c r="J129" s="33" t="n">
+        <v>458.66</v>
+      </c>
+      <c r="K129" s="28" t="n"/>
+      <c r="L129" s="32" t="n"/>
+    </row>
+    <row r="130">
+      <c r="E130" s="16" t="n"/>
+      <c r="F130" s="17" t="n"/>
+      <c r="G130" s="31" t="n"/>
+      <c r="H130" s="32" t="n"/>
+      <c r="I130" s="13" t="inlineStr">
+        <is>
+          <t>Electrabel</t>
+        </is>
+      </c>
+      <c r="J130" s="33" t="n">
+        <v>270.94</v>
+      </c>
+      <c r="K130" s="28" t="n"/>
+      <c r="L130" s="32" t="n"/>
+    </row>
+    <row r="131">
+      <c r="E131" s="16" t="n"/>
+      <c r="F131" s="17" t="n"/>
+      <c r="G131" s="31" t="n"/>
+      <c r="H131" s="32" t="n"/>
+      <c r="I131" s="13" t="inlineStr">
+        <is>
+          <t>Electrabel</t>
+        </is>
+      </c>
+      <c r="J131" s="33" t="n">
+        <v>263.44</v>
+      </c>
+      <c r="K131" s="28" t="n"/>
+      <c r="L131" s="32" t="n"/>
+    </row>
+    <row r="132">
+      <c r="E132" s="16" t="n"/>
+      <c r="F132" s="17" t="n"/>
+      <c r="G132" s="31" t="n"/>
+      <c r="H132" s="32" t="n"/>
+      <c r="I132" s="13" t="inlineStr">
+        <is>
+          <t>Proximus</t>
+        </is>
+      </c>
+      <c r="J132" s="33" t="n">
+        <v>226.02</v>
+      </c>
+      <c r="K132" s="28" t="n"/>
+      <c r="L132" s="32" t="n"/>
+    </row>
+    <row r="133">
+      <c r="E133" s="16" t="n"/>
+      <c r="F133" s="17" t="n"/>
+      <c r="G133" s="31" t="n"/>
+      <c r="H133" s="32" t="n"/>
+      <c r="I133" s="13" t="inlineStr">
+        <is>
+          <t>Réception marchandise - UPS</t>
+        </is>
+      </c>
+      <c r="J133" s="33" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="K133" s="28" t="n"/>
+      <c r="L133" s="32" t="n"/>
+    </row>
+    <row r="134">
+      <c r="E134" s="16" t="n"/>
+      <c r="F134" s="17" t="n"/>
+      <c r="G134" s="31" t="n"/>
+      <c r="H134" s="32" t="n"/>
+      <c r="I134" s="13" t="inlineStr">
+        <is>
+          <t>Repas Lunch Garden</t>
+        </is>
+      </c>
+      <c r="J134" s="33" t="n">
+        <v>51.02</v>
+      </c>
+      <c r="K134" s="28" t="n"/>
+      <c r="L134" s="32" t="n"/>
+    </row>
+    <row r="135">
+      <c r="E135" s="16" t="n"/>
+      <c r="F135" s="17" t="n"/>
+      <c r="G135" s="31" t="n"/>
+      <c r="H135" s="32" t="n"/>
+      <c r="I135" s="40" t="inlineStr">
+        <is>
+          <t>Redevance de stationnement - OPC</t>
+        </is>
+      </c>
+      <c r="J135" s="41" t="n">
+        <v>40</v>
+      </c>
+      <c r="K135" s="28" t="n"/>
+      <c r="L135" s="39" t="inlineStr">
+        <is>
+          <t>à confirmer (redevance ou amende)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="G136" s="34" t="n"/>
+      <c r="H136" s="35" t="n"/>
+      <c r="J136" s="34" t="n"/>
+      <c r="L136" s="35" t="n"/>
+    </row>
+    <row r="137">
+      <c r="G137" s="34" t="n"/>
+      <c r="H137" s="35" t="n"/>
+      <c r="J137" s="34" t="n"/>
+      <c r="L137" s="35" t="n"/>
+    </row>
+    <row r="138">
+      <c r="E138" s="16" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="F138" s="17" t="inlineStr">
+        <is>
+          <t>LAM2605</t>
+        </is>
+      </c>
+      <c r="G138" s="31" t="n">
+        <v>4619.2</v>
+      </c>
+      <c r="H138" s="32" t="n"/>
+      <c r="I138" s="28" t="inlineStr">
+        <is>
+          <t>Carburant</t>
+        </is>
+      </c>
+      <c r="J138" s="36" t="n">
+        <v>89.01000000000001</v>
+      </c>
+      <c r="K138" s="28" t="n"/>
+      <c r="L138" s="32" t="n"/>
+    </row>
+    <row r="139">
+      <c r="E139" s="16" t="n"/>
+      <c r="F139" s="17" t="n"/>
+      <c r="G139" s="31" t="n"/>
+      <c r="H139" s="32" t="n"/>
+      <c r="I139" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J139" s="33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K139" s="28" t="n"/>
+      <c r="L139" s="32" t="n"/>
+    </row>
+    <row r="140">
+      <c r="E140" s="16" t="n"/>
+      <c r="F140" s="17" t="n"/>
+      <c r="G140" s="31" t="n"/>
+      <c r="H140" s="32" t="n"/>
+      <c r="I140" s="13" t="inlineStr">
+        <is>
+          <t>Précompte salarial avril 2026 Thibault Duchène</t>
+        </is>
+      </c>
+      <c r="J140" s="33" t="n">
+        <v>2250</v>
+      </c>
+      <c r="K140" s="28" t="n"/>
+      <c r="L140" s="32" t="n"/>
+    </row>
+    <row r="141">
+      <c r="E141" s="16" t="n"/>
+      <c r="F141" s="17" t="n"/>
+      <c r="G141" s="31" t="n"/>
+      <c r="H141" s="32" t="n"/>
+      <c r="I141" s="13" t="inlineStr">
+        <is>
+          <t>Partena</t>
+        </is>
+      </c>
+      <c r="J141" s="33" t="n">
+        <v>1747.34</v>
+      </c>
+      <c r="K141" s="28" t="n"/>
+      <c r="L141" s="32" t="n"/>
+    </row>
+    <row r="142">
+      <c r="E142" s="16" t="n"/>
+      <c r="F142" s="17" t="n"/>
+      <c r="G142" s="31" t="n"/>
+      <c r="H142" s="32" t="n"/>
+      <c r="I142" s="13" t="inlineStr">
+        <is>
+          <t>Crédit voiture</t>
+        </is>
+      </c>
+      <c r="J142" s="33" t="n">
+        <v>724.12</v>
+      </c>
+      <c r="K142" s="28" t="n"/>
+      <c r="L142" s="32" t="n"/>
+    </row>
+    <row r="143">
+      <c r="E143" s="16" t="n"/>
+      <c r="F143" s="17" t="n"/>
+      <c r="G143" s="31" t="n"/>
+      <c r="H143" s="32" t="n"/>
+      <c r="I143" s="13" t="inlineStr">
+        <is>
+          <t>Remboursement alimentation du compte - Thibault Duchène</t>
+        </is>
+      </c>
+      <c r="J143" s="33" t="n">
+        <v>500</v>
+      </c>
+      <c r="K143" s="28" t="n"/>
+      <c r="L143" s="32" t="inlineStr">
+        <is>
+          <t>Restitution des apports de février 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="E144" s="16" t="n"/>
+      <c r="F144" s="17" t="n"/>
+      <c r="G144" s="31" t="n"/>
+      <c r="H144" s="32" t="n"/>
+      <c r="I144" s="13" t="inlineStr">
+        <is>
+          <t>Collation</t>
+        </is>
+      </c>
+      <c r="J144" s="33" t="n">
+        <v>8</v>
+      </c>
+      <c r="K144" s="28" t="n"/>
+      <c r="L144" s="32" t="n"/>
+    </row>
+    <row r="145">
+      <c r="E145" s="16" t="n"/>
+      <c r="F145" s="17" t="n"/>
+      <c r="G145" s="31" t="n"/>
+      <c r="H145" s="32" t="n"/>
+      <c r="I145" s="13" t="inlineStr">
+        <is>
+          <t>Collation</t>
+        </is>
+      </c>
+      <c r="J145" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="K145" s="28" t="n"/>
+      <c r="L145" s="32" t="n"/>
+    </row>
+    <row r="146">
+      <c r="E146" s="16" t="n"/>
+      <c r="F146" s="17" t="n"/>
+      <c r="G146" s="31" t="n"/>
+      <c r="H146" s="32" t="n"/>
+      <c r="I146" s="13" t="inlineStr">
+        <is>
+          <t>Carburant</t>
+        </is>
+      </c>
+      <c r="J146" s="33" t="n">
+        <v>85.45</v>
+      </c>
+      <c r="K146" s="28" t="n"/>
+      <c r="L146" s="32" t="inlineStr">
+        <is>
+          <t>Total Schaerbeek</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="E147" s="16" t="n"/>
+      <c r="F147" s="17" t="n"/>
+      <c r="G147" s="31" t="n"/>
+      <c r="H147" s="32" t="n"/>
+      <c r="I147" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J147" s="33" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="K147" s="28" t="n"/>
+      <c r="L147" s="32" t="n"/>
+    </row>
+    <row r="148">
+      <c r="E148" s="16" t="n"/>
+      <c r="F148" s="17" t="n"/>
+      <c r="G148" s="31" t="n"/>
+      <c r="H148" s="32" t="n"/>
+      <c r="I148" s="13" t="inlineStr">
+        <is>
+          <t>Collation</t>
+        </is>
+      </c>
+      <c r="J148" s="33" t="n">
+        <v>8</v>
+      </c>
+      <c r="K148" s="28" t="n"/>
+      <c r="L148" s="32" t="n"/>
+    </row>
+    <row r="149">
+      <c r="E149" s="16" t="n"/>
+      <c r="F149" s="17" t="n"/>
+      <c r="G149" s="31" t="n"/>
+      <c r="H149" s="32" t="n"/>
+      <c r="I149" s="13" t="inlineStr">
+        <is>
+          <t>Paiement carte de crédit</t>
+        </is>
+      </c>
+      <c r="J149" s="33" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="K149" s="28" t="n"/>
+      <c r="L149" s="32" t="n"/>
+    </row>
+    <row r="150">
+      <c r="E150" s="16" t="n"/>
+      <c r="F150" s="17" t="n"/>
+      <c r="G150" s="31" t="n"/>
+      <c r="H150" s="32" t="n"/>
+      <c r="I150" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J150" s="33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K150" s="28" t="n"/>
+      <c r="L150" s="32" t="n"/>
+    </row>
+    <row r="151">
+      <c r="E151" s="16" t="n"/>
+      <c r="F151" s="17" t="n"/>
+      <c r="G151" s="31" t="n"/>
+      <c r="H151" s="32" t="n"/>
+      <c r="I151" s="13" t="inlineStr">
+        <is>
+          <t>Carburant</t>
+        </is>
+      </c>
+      <c r="J151" s="33" t="n">
+        <v>72.66</v>
+      </c>
+      <c r="K151" s="28" t="n"/>
+      <c r="L151" s="32" t="n"/>
+    </row>
+    <row r="152">
+      <c r="E152" s="16" t="n"/>
+      <c r="F152" s="17" t="n"/>
+      <c r="G152" s="31" t="n"/>
+      <c r="H152" s="32" t="n"/>
+      <c r="I152" s="13" t="inlineStr">
+        <is>
+          <t>Carburant</t>
+        </is>
+      </c>
+      <c r="J152" s="33" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="K152" s="28" t="n"/>
+      <c r="L152" s="32" t="n"/>
+    </row>
+    <row r="153">
+      <c r="E153" s="16" t="n"/>
+      <c r="F153" s="17" t="n"/>
+      <c r="G153" s="31" t="n"/>
+      <c r="H153" s="32" t="n"/>
+      <c r="I153" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J153" s="33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K153" s="28" t="n"/>
+      <c r="L153" s="32" t="n"/>
+    </row>
+    <row r="154">
+      <c r="E154" s="16" t="n"/>
+      <c r="F154" s="17" t="n"/>
+      <c r="G154" s="31" t="n"/>
+      <c r="H154" s="32" t="n"/>
+      <c r="I154" s="40" t="inlineStr">
+        <is>
+          <t>Abonnement salle FitRaw</t>
+        </is>
+      </c>
+      <c r="J154" s="41" t="n">
+        <v>59.04</v>
+      </c>
+      <c r="K154" s="28" t="n"/>
+      <c r="L154" s="39" t="inlineStr">
+        <is>
+          <t>Sterrebeek — usage professionnel à confirmer</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="E155" s="16" t="n"/>
+      <c r="F155" s="17" t="n"/>
+      <c r="G155" s="31" t="n"/>
+      <c r="H155" s="32" t="n"/>
+      <c r="I155" s="13" t="inlineStr">
+        <is>
+          <t>Lavage voiture</t>
+        </is>
+      </c>
+      <c r="J155" s="33" t="n">
+        <v>32</v>
+      </c>
+      <c r="K155" s="28" t="n"/>
+      <c r="L155" s="32" t="inlineStr">
+        <is>
+          <t>Wash Time Tervuren</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="E156" s="16" t="n"/>
+      <c r="F156" s="17" t="n"/>
+      <c r="G156" s="31" t="n"/>
+      <c r="H156" s="32" t="n"/>
+      <c r="I156" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J156" s="33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K156" s="28" t="n"/>
+      <c r="L156" s="32" t="n"/>
+    </row>
+    <row r="157">
+      <c r="E157" s="16" t="n"/>
+      <c r="F157" s="17" t="n"/>
+      <c r="G157" s="31" t="n"/>
+      <c r="H157" s="32" t="n"/>
+      <c r="I157" s="13" t="inlineStr">
+        <is>
+          <t>Carburant</t>
+        </is>
+      </c>
+      <c r="J157" s="33" t="n">
+        <v>79.51000000000001</v>
+      </c>
+      <c r="K157" s="28" t="n"/>
+      <c r="L157" s="32" t="n"/>
+    </row>
+    <row r="158">
+      <c r="E158" s="16" t="n"/>
+      <c r="F158" s="17" t="n"/>
+      <c r="G158" s="31" t="n"/>
+      <c r="H158" s="32" t="n"/>
+      <c r="I158" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J158" s="33" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="K158" s="28" t="n"/>
+      <c r="L158" s="32" t="inlineStr">
+        <is>
+          <t>Schiphol (Pays-Bas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="E159" s="16" t="n"/>
+      <c r="F159" s="17" t="n"/>
+      <c r="G159" s="31" t="n"/>
+      <c r="H159" s="32" t="n"/>
+      <c r="I159" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J159" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="K159" s="28" t="n"/>
+      <c r="L159" s="32" t="n"/>
+    </row>
+    <row r="160">
+      <c r="E160" s="16" t="n"/>
+      <c r="F160" s="17" t="n"/>
+      <c r="G160" s="31" t="n"/>
+      <c r="H160" s="32" t="n"/>
+      <c r="I160" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J160" s="33" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K160" s="28" t="n"/>
+      <c r="L160" s="32" t="n"/>
+    </row>
+    <row r="161">
+      <c r="G161" s="34" t="n"/>
+      <c r="H161" s="35" t="n"/>
+      <c r="J161" s="34" t="n"/>
+      <c r="L161" s="35" t="n"/>
+    </row>
+    <row r="162">
+      <c r="G162" s="34" t="n"/>
+      <c r="H162" s="35" t="n"/>
+      <c r="J162" s="34" t="n"/>
+      <c r="L162" s="35" t="n"/>
+    </row>
+    <row r="163">
+      <c r="E163" s="16" t="inlineStr">
+        <is>
+          <t>Juin</t>
+        </is>
+      </c>
+      <c r="F163" s="17" t="inlineStr">
+        <is>
+          <t>LAM2606</t>
+        </is>
+      </c>
+      <c r="G163" s="31" t="n">
+        <v>4803.5</v>
+      </c>
+      <c r="H163" s="32" t="n"/>
+      <c r="I163" s="28" t="inlineStr">
+        <is>
+          <t>Carburant</t>
+        </is>
+      </c>
+      <c r="J163" s="36" t="n">
+        <v>75.41</v>
+      </c>
+      <c r="K163" s="28" t="n"/>
+      <c r="L163" s="32" t="n"/>
+    </row>
+    <row r="164">
+      <c r="E164" s="16" t="n"/>
+      <c r="F164" s="17" t="inlineStr">
+        <is>
+          <t>Remboursement billet d'avion - Thibault Duchène</t>
+        </is>
+      </c>
+      <c r="G164" s="31" t="n">
+        <v>1815.16</v>
+      </c>
+      <c r="H164" s="32" t="n"/>
+      <c r="I164" s="40" t="inlineStr">
+        <is>
+          <t>Abonnement club David Lloyd</t>
+        </is>
+      </c>
+      <c r="J164" s="41" t="n">
+        <v>493</v>
+      </c>
+      <c r="K164" s="28" t="n"/>
+      <c r="L164" s="39" t="inlineStr">
+        <is>
+          <t>Sterrebeek — usage professionnel à confirmer</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="E165" s="16" t="n"/>
+      <c r="F165" s="17" t="n"/>
+      <c r="G165" s="31" t="n"/>
+      <c r="H165" s="32" t="n"/>
+      <c r="I165" s="13" t="inlineStr">
+        <is>
+          <t>Crédit voiture</t>
+        </is>
+      </c>
+      <c r="J165" s="33" t="n">
+        <v>724.12</v>
+      </c>
+      <c r="K165" s="28" t="n"/>
+      <c r="L165" s="32" t="n"/>
+    </row>
+    <row r="166">
+      <c r="E166" s="16" t="n"/>
+      <c r="F166" s="17" t="n"/>
+      <c r="G166" s="31" t="n"/>
+      <c r="H166" s="32" t="n"/>
+      <c r="I166" s="13" t="inlineStr">
+        <is>
+          <t>Carburant</t>
+        </is>
+      </c>
+      <c r="J166" s="33" t="n">
+        <v>83.72</v>
+      </c>
+      <c r="K166" s="28" t="n"/>
+      <c r="L166" s="32" t="n"/>
+    </row>
+    <row r="167">
+      <c r="E167" s="16" t="n"/>
+      <c r="F167" s="17" t="n"/>
+      <c r="G167" s="31" t="n"/>
+      <c r="H167" s="32" t="n"/>
+      <c r="I167" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J167" s="33" t="n">
+        <v>43.75</v>
+      </c>
+      <c r="K167" s="28" t="n"/>
+      <c r="L167" s="32" t="n"/>
+    </row>
+    <row r="168">
+      <c r="E168" s="16" t="n"/>
+      <c r="F168" s="17" t="n"/>
+      <c r="G168" s="31" t="n"/>
+      <c r="H168" s="32" t="n"/>
+      <c r="I168" s="13" t="inlineStr">
+        <is>
+          <t>Précompte salarial mai 2026 Thibault Duchène</t>
+        </is>
+      </c>
+      <c r="J168" s="33" t="n">
+        <v>2250</v>
+      </c>
+      <c r="K168" s="28" t="n"/>
+      <c r="L168" s="32" t="n"/>
+    </row>
+    <row r="169">
+      <c r="E169" s="16" t="n"/>
+      <c r="F169" s="17" t="n"/>
+      <c r="G169" s="31" t="n"/>
+      <c r="H169" s="32" t="n"/>
+      <c r="I169" s="13" t="inlineStr">
+        <is>
+          <t>SD Worx</t>
+        </is>
+      </c>
+      <c r="J169" s="33" t="n">
+        <v>332.84</v>
+      </c>
+      <c r="K169" s="28" t="n"/>
+      <c r="L169" s="32" t="n"/>
+    </row>
+    <row r="170">
+      <c r="E170" s="16" t="n"/>
+      <c r="F170" s="17" t="n"/>
+      <c r="G170" s="31" t="n"/>
+      <c r="H170" s="32" t="n"/>
+      <c r="I170" s="13" t="inlineStr">
+        <is>
+          <t>Proximus</t>
+        </is>
+      </c>
+      <c r="J170" s="33" t="n">
+        <v>203.91</v>
+      </c>
+      <c r="K170" s="28" t="n"/>
+      <c r="L170" s="32" t="n"/>
+    </row>
+    <row r="171">
+      <c r="E171" s="16" t="n"/>
+      <c r="F171" s="17" t="n"/>
+      <c r="G171" s="31" t="n"/>
+      <c r="H171" s="32" t="n"/>
+      <c r="I171" s="13" t="inlineStr">
+        <is>
+          <t>Carburant</t>
+        </is>
+      </c>
+      <c r="J171" s="33" t="n">
+        <v>80.15000000000001</v>
+      </c>
+      <c r="K171" s="28" t="n"/>
+      <c r="L171" s="32" t="n"/>
+    </row>
+    <row r="172">
+      <c r="E172" s="16" t="n"/>
+      <c r="F172" s="17" t="n"/>
+      <c r="G172" s="31" t="n"/>
+      <c r="H172" s="32" t="n"/>
+      <c r="I172" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J172" s="33" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K172" s="28" t="n"/>
+      <c r="L172" s="32" t="n"/>
+    </row>
+    <row r="173">
+      <c r="E173" s="16" t="n"/>
+      <c r="F173" s="17" t="n"/>
+      <c r="G173" s="31" t="n"/>
+      <c r="H173" s="32" t="n"/>
+      <c r="I173" s="13" t="inlineStr">
+        <is>
+          <t>Lavage voiture</t>
+        </is>
+      </c>
+      <c r="J173" s="33" t="n">
+        <v>17</v>
+      </c>
+      <c r="K173" s="28" t="n"/>
+      <c r="L173" s="32" t="inlineStr">
+        <is>
+          <t>Wash Time Tervuren</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="E174" s="16" t="n"/>
+      <c r="F174" s="17" t="n"/>
+      <c r="G174" s="31" t="n"/>
+      <c r="H174" s="32" t="n"/>
+      <c r="I174" s="13" t="inlineStr">
+        <is>
+          <t>Paiement carte de crédit</t>
+        </is>
+      </c>
+      <c r="J174" s="33" t="n">
+        <v>1815.16</v>
+      </c>
+      <c r="K174" s="28" t="n"/>
+      <c r="L174" s="32" t="n"/>
+    </row>
+    <row r="175">
+      <c r="E175" s="16" t="n"/>
+      <c r="F175" s="17" t="n"/>
+      <c r="G175" s="31" t="n"/>
+      <c r="H175" s="32" t="n"/>
+      <c r="I175" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J175" s="33" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="K175" s="28" t="n"/>
+      <c r="L175" s="32" t="n"/>
+    </row>
+    <row r="176">
+      <c r="E176" s="16" t="n"/>
+      <c r="F176" s="17" t="n"/>
+      <c r="G176" s="31" t="n"/>
+      <c r="H176" s="32" t="n"/>
+      <c r="I176" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J176" s="33" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K176" s="28" t="n"/>
+      <c r="L176" s="32" t="n"/>
+    </row>
+    <row r="177">
+      <c r="E177" s="16" t="n"/>
+      <c r="F177" s="17" t="n"/>
+      <c r="G177" s="31" t="n"/>
+      <c r="H177" s="32" t="n"/>
+      <c r="I177" s="13" t="inlineStr">
+        <is>
+          <t>Electrabel</t>
+        </is>
+      </c>
+      <c r="J177" s="33" t="n">
+        <v>297.28</v>
+      </c>
+      <c r="K177" s="28" t="n"/>
+      <c r="L177" s="32" t="n"/>
+    </row>
+    <row r="178">
+      <c r="E178" s="16" t="n"/>
+      <c r="F178" s="17" t="n"/>
+      <c r="G178" s="31" t="n"/>
+      <c r="H178" s="32" t="n"/>
+      <c r="I178" s="13" t="inlineStr">
+        <is>
+          <t>Electrabel</t>
+        </is>
+      </c>
+      <c r="J178" s="33" t="n">
+        <v>270.94</v>
+      </c>
+      <c r="K178" s="28" t="n"/>
+      <c r="L178" s="32" t="n"/>
+    </row>
+    <row r="179">
+      <c r="E179" s="16" t="n"/>
+      <c r="F179" s="17" t="n"/>
+      <c r="G179" s="31" t="n"/>
+      <c r="H179" s="32" t="n"/>
+      <c r="I179" s="13" t="inlineStr">
+        <is>
+          <t>Proximus</t>
+        </is>
+      </c>
+      <c r="J179" s="33" t="n">
+        <v>239.76</v>
+      </c>
+      <c r="K179" s="28" t="n"/>
+      <c r="L179" s="32" t="n"/>
+    </row>
+    <row r="180">
+      <c r="E180" s="16" t="n"/>
+      <c r="F180" s="17" t="n"/>
+      <c r="G180" s="31" t="n"/>
+      <c r="H180" s="32" t="n"/>
+      <c r="I180" s="13" t="inlineStr">
+        <is>
+          <t>Carburant</t>
+        </is>
+      </c>
+      <c r="J180" s="33" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="K180" s="28" t="n"/>
+      <c r="L180" s="32" t="n"/>
+    </row>
+    <row r="181">
+      <c r="E181" s="16" t="n"/>
+      <c r="F181" s="17" t="n"/>
+      <c r="G181" s="31" t="n"/>
+      <c r="H181" s="32" t="n"/>
+      <c r="I181" s="13" t="inlineStr">
+        <is>
+          <t>Achat matériel sportif - DECATHLON</t>
+        </is>
+      </c>
+      <c r="J181" s="33" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="K181" s="28" t="n"/>
+      <c r="L181" s="32" t="n"/>
+    </row>
+    <row r="182">
+      <c r="E182" s="16" t="n"/>
+      <c r="F182" s="17" t="n"/>
+      <c r="G182" s="31" t="n"/>
+      <c r="H182" s="32" t="n"/>
+      <c r="I182" s="13" t="inlineStr">
+        <is>
+          <t>SD Worx</t>
+        </is>
+      </c>
+      <c r="J182" s="33" t="n">
+        <v>32.84</v>
+      </c>
+      <c r="K182" s="28" t="n"/>
+      <c r="L182" s="32" t="n"/>
+    </row>
+    <row r="183">
+      <c r="E183" s="16" t="n"/>
+      <c r="F183" s="17" t="n"/>
+      <c r="G183" s="31" t="n"/>
+      <c r="H183" s="32" t="n"/>
+      <c r="I183" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J183" s="33" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="K183" s="28" t="n"/>
+      <c r="L183" s="32" t="n"/>
+    </row>
+    <row r="184">
+      <c r="E184" s="16" t="n"/>
+      <c r="F184" s="17" t="n"/>
+      <c r="G184" s="31" t="n"/>
+      <c r="H184" s="32" t="n"/>
+      <c r="I184" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J184" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="K184" s="28" t="n"/>
+      <c r="L184" s="32" t="n"/>
+    </row>
+    <row r="185">
+      <c r="E185" s="16" t="n"/>
+      <c r="F185" s="17" t="n"/>
+      <c r="G185" s="31" t="n"/>
+      <c r="H185" s="32" t="n"/>
+      <c r="I185" s="13" t="inlineStr">
+        <is>
+          <t>Divers - sanitaires autoroute</t>
+        </is>
+      </c>
+      <c r="J185" s="33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K185" s="28" t="n"/>
+      <c r="L185" s="32" t="inlineStr">
+        <is>
+          <t>Aire de Rotselaar</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="E186" s="16" t="n"/>
+      <c r="F186" s="17" t="n"/>
+      <c r="G186" s="31" t="n"/>
+      <c r="H186" s="32" t="n"/>
+      <c r="I186" s="13" t="inlineStr">
+        <is>
+          <t>Divers - sanitaires autoroute</t>
+        </is>
+      </c>
+      <c r="J186" s="33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K186" s="28" t="n"/>
+      <c r="L186" s="32" t="inlineStr">
+        <is>
+          <t>Aire de Rotselaar</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="E187" s="16" t="n"/>
+      <c r="F187" s="17" t="n"/>
+      <c r="G187" s="31" t="n"/>
+      <c r="H187" s="32" t="n"/>
+      <c r="I187" s="13" t="inlineStr">
+        <is>
+          <t>Carburant</t>
+        </is>
+      </c>
+      <c r="J187" s="33" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="K187" s="28" t="n"/>
+      <c r="L187" s="32" t="n"/>
+    </row>
+    <row r="188">
+      <c r="E188" s="16" t="n"/>
+      <c r="F188" s="17" t="n"/>
+      <c r="G188" s="31" t="n"/>
+      <c r="H188" s="32" t="n"/>
+      <c r="I188" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J188" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="K188" s="28" t="n"/>
+      <c r="L188" s="32" t="n"/>
+    </row>
+    <row r="189">
+      <c r="E189" s="16" t="n"/>
+      <c r="F189" s="17" t="n"/>
+      <c r="G189" s="31" t="n"/>
+      <c r="H189" s="32" t="n"/>
+      <c r="I189" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J189" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="K189" s="28" t="n"/>
+      <c r="L189" s="32" t="n"/>
+    </row>
+    <row r="190">
+      <c r="E190" s="16" t="n"/>
+      <c r="F190" s="17" t="n"/>
+      <c r="G190" s="31" t="n"/>
+      <c r="H190" s="32" t="n"/>
+      <c r="I190" s="40" t="inlineStr">
+        <is>
+          <t>Hôtel Ibis Nieuwpoort</t>
+        </is>
+      </c>
+      <c r="J190" s="41" t="n">
+        <v>15</v>
+      </c>
+      <c r="K190" s="28" t="n"/>
+      <c r="L190" s="39" t="inlineStr">
+        <is>
+          <t>à confirmer (nuitée ou consommation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="E191" s="16" t="n"/>
+      <c r="F191" s="17" t="n"/>
+      <c r="G191" s="31" t="n"/>
+      <c r="H191" s="32" t="n"/>
+      <c r="I191" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J191" s="33" t="n">
+        <v>8</v>
+      </c>
+      <c r="K191" s="28" t="n"/>
+      <c r="L191" s="32" t="n"/>
+    </row>
+    <row r="192">
+      <c r="E192" s="16" t="n"/>
+      <c r="F192" s="17" t="n"/>
+      <c r="G192" s="31" t="n"/>
+      <c r="H192" s="32" t="n"/>
+      <c r="I192" s="13" t="inlineStr">
+        <is>
+          <t>Carburant</t>
+        </is>
+      </c>
+      <c r="J192" s="33" t="n">
+        <v>76.98999999999999</v>
+      </c>
+      <c r="K192" s="28" t="n"/>
+      <c r="L192" s="32" t="n"/>
+    </row>
+    <row r="193">
+      <c r="G193" s="34" t="n"/>
+      <c r="H193" s="35" t="n"/>
+      <c r="J193" s="34" t="n"/>
+      <c r="L193" s="35" t="n"/>
+    </row>
+    <row r="194">
+      <c r="G194" s="34" t="n"/>
+      <c r="H194" s="35" t="n"/>
+      <c r="J194" s="34" t="n"/>
+      <c r="L194" s="35" t="n"/>
+    </row>
+    <row r="195">
+      <c r="E195" s="16" t="inlineStr">
+        <is>
+          <t>Juillet</t>
+        </is>
+      </c>
+      <c r="F195" s="17" t="inlineStr">
+        <is>
+          <t>LAM2607</t>
+        </is>
+      </c>
+      <c r="G195" s="31" t="n">
+        <v>4156.08</v>
+      </c>
+      <c r="H195" s="32" t="n"/>
+      <c r="I195" s="42" t="inlineStr">
+        <is>
+          <t>Abonnement club David Lloyd</t>
+        </is>
+      </c>
+      <c r="J195" s="43" t="n">
+        <v>493</v>
+      </c>
+      <c r="K195" s="28" t="n"/>
+      <c r="L195" s="39" t="inlineStr">
+        <is>
+          <t>Sterrebeek — usage professionnel à confirmer</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="E196" s="16" t="n"/>
+      <c r="F196" s="17" t="inlineStr">
+        <is>
+          <t>Remboursement SD Worx</t>
+        </is>
+      </c>
+      <c r="G196" s="31" t="n">
+        <v>32.84</v>
+      </c>
+      <c r="H196" s="32" t="inlineStr">
+        <is>
+          <t>Cotisation payée deux fois</t>
+        </is>
+      </c>
+      <c r="I196" s="13" t="inlineStr">
+        <is>
+          <t>Précompte salarial juin 2026 Thibault Duchène</t>
+        </is>
+      </c>
+      <c r="J196" s="33" t="n">
+        <v>2250</v>
+      </c>
+      <c r="K196" s="28" t="n"/>
+      <c r="L196" s="32" t="n"/>
+    </row>
+    <row r="197">
+      <c r="E197" s="16" t="n"/>
+      <c r="F197" s="17" t="inlineStr">
+        <is>
+          <t>LAM2608</t>
+        </is>
+      </c>
+      <c r="G197" s="31" t="n">
+        <v>6448.4</v>
+      </c>
+      <c r="H197" s="32" t="n"/>
+      <c r="I197" s="13" t="inlineStr">
+        <is>
+          <t>SD Worx</t>
+        </is>
+      </c>
+      <c r="J197" s="33" t="n">
+        <v>332.84</v>
+      </c>
+      <c r="K197" s="28" t="n"/>
+      <c r="L197" s="32" t="n"/>
+    </row>
+    <row r="198">
+      <c r="E198" s="16" t="n"/>
+      <c r="F198" s="17" t="inlineStr">
+        <is>
+          <t>Remboursement Airbnb - Thibault Duchène</t>
+        </is>
+      </c>
+      <c r="G198" s="31" t="n">
+        <v>2431.44</v>
+      </c>
+      <c r="H198" s="32" t="n"/>
+      <c r="I198" s="13" t="inlineStr">
+        <is>
+          <t>SD Worx</t>
+        </is>
+      </c>
+      <c r="J198" s="33" t="n">
+        <v>332.84</v>
+      </c>
+      <c r="K198" s="28" t="n"/>
+      <c r="L198" s="32" t="n"/>
+    </row>
+    <row r="199">
+      <c r="E199" s="16" t="n"/>
+      <c r="F199" s="17" t="n"/>
+      <c r="G199" s="31" t="n"/>
+      <c r="H199" s="32" t="n"/>
+      <c r="I199" s="13" t="inlineStr">
+        <is>
+          <t>Crédit voiture</t>
+        </is>
+      </c>
+      <c r="J199" s="33" t="n">
+        <v>724.12</v>
+      </c>
+      <c r="K199" s="28" t="n"/>
+      <c r="L199" s="32" t="n"/>
+    </row>
+    <row r="200">
+      <c r="E200" s="16" t="n"/>
+      <c r="F200" s="17" t="n"/>
+      <c r="G200" s="31" t="n"/>
+      <c r="H200" s="32" t="n"/>
+      <c r="I200" s="13" t="inlineStr">
+        <is>
+          <t>Frais bancaires trimestriels</t>
+        </is>
+      </c>
+      <c r="J200" s="33" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="K200" s="28" t="n"/>
+      <c r="L200" s="32" t="n"/>
+    </row>
+    <row r="201">
+      <c r="E201" s="16" t="n"/>
+      <c r="F201" s="17" t="n"/>
+      <c r="G201" s="31" t="n"/>
+      <c r="H201" s="32" t="n"/>
+      <c r="I201" s="13" t="inlineStr">
+        <is>
+          <t>Carburant</t>
+        </is>
+      </c>
+      <c r="J201" s="33" t="n">
+        <v>79.41</v>
+      </c>
+      <c r="K201" s="28" t="n"/>
+      <c r="L201" s="32" t="n"/>
+    </row>
+    <row r="202">
+      <c r="E202" s="16" t="n"/>
+      <c r="F202" s="17" t="n"/>
+      <c r="G202" s="31" t="n"/>
+      <c r="H202" s="32" t="n"/>
+      <c r="I202" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J202" s="33" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K202" s="28" t="n"/>
+      <c r="L202" s="32" t="n"/>
+    </row>
+    <row r="203">
+      <c r="E203" s="16" t="n"/>
+      <c r="F203" s="17" t="n"/>
+      <c r="G203" s="31" t="n"/>
+      <c r="H203" s="32" t="n"/>
+      <c r="I203" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J203" s="33" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K203" s="28" t="n"/>
+      <c r="L203" s="32" t="n"/>
+    </row>
+    <row r="204">
+      <c r="E204" s="16" t="n"/>
+      <c r="F204" s="17" t="n"/>
+      <c r="G204" s="31" t="n"/>
+      <c r="H204" s="32" t="n"/>
+      <c r="I204" s="13" t="inlineStr">
+        <is>
+          <t>Collation</t>
+        </is>
+      </c>
+      <c r="J204" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="K204" s="28" t="n"/>
+      <c r="L204" s="32" t="n"/>
+    </row>
+    <row r="205">
+      <c r="E205" s="16" t="n"/>
+      <c r="F205" s="17" t="n"/>
+      <c r="G205" s="31" t="n"/>
+      <c r="H205" s="32" t="n"/>
+      <c r="I205" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J205" s="33" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K205" s="28" t="n"/>
+      <c r="L205" s="32" t="n"/>
+    </row>
+    <row r="206">
+      <c r="E206" s="16" t="n"/>
+      <c r="F206" s="17" t="n"/>
+      <c r="G206" s="31" t="n"/>
+      <c r="H206" s="32" t="n"/>
+      <c r="I206" s="13" t="inlineStr">
+        <is>
+          <t>Péage autoroute France</t>
+        </is>
+      </c>
+      <c r="J206" s="33" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="K206" s="28" t="n"/>
+      <c r="L206" s="32" t="n"/>
+    </row>
+    <row r="207">
+      <c r="E207" s="16" t="n"/>
+      <c r="F207" s="17" t="n"/>
+      <c r="G207" s="31" t="n"/>
+      <c r="H207" s="32" t="n"/>
+      <c r="I207" s="13" t="inlineStr">
+        <is>
+          <t>Carburant</t>
+        </is>
+      </c>
+      <c r="J207" s="33" t="n">
+        <v>79.42</v>
+      </c>
+      <c r="K207" s="28" t="n"/>
+      <c r="L207" s="32" t="n"/>
+    </row>
+    <row r="208">
+      <c r="E208" s="16" t="n"/>
+      <c r="F208" s="17" t="n"/>
+      <c r="G208" s="31" t="n"/>
+      <c r="H208" s="32" t="n"/>
+      <c r="I208" s="13" t="inlineStr">
+        <is>
+          <t>Collation</t>
+        </is>
+      </c>
+      <c r="J208" s="33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K208" s="28" t="n"/>
+      <c r="L208" s="32" t="n"/>
+    </row>
+    <row r="209">
+      <c r="E209" s="16" t="n"/>
+      <c r="F209" s="17" t="n"/>
+      <c r="G209" s="31" t="n"/>
+      <c r="H209" s="32" t="n"/>
+      <c r="I209" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J209" s="33" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K209" s="28" t="n"/>
+      <c r="L209" s="32" t="n"/>
+    </row>
+    <row r="210">
+      <c r="E210" s="16" t="n"/>
+      <c r="F210" s="17" t="n"/>
+      <c r="G210" s="31" t="n"/>
+      <c r="H210" s="32" t="n"/>
+      <c r="I210" s="13" t="inlineStr">
+        <is>
+          <t>Lavage voiture</t>
+        </is>
+      </c>
+      <c r="J210" s="33" t="n">
+        <v>32</v>
+      </c>
+      <c r="K210" s="28" t="n"/>
+      <c r="L210" s="32" t="inlineStr">
+        <is>
+          <t>Wash Time Tervuren</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="E211" s="16" t="n"/>
+      <c r="F211" s="17" t="n"/>
+      <c r="G211" s="31" t="n"/>
+      <c r="H211" s="32" t="n"/>
+      <c r="I211" s="13" t="inlineStr">
+        <is>
+          <t>Achat matériel sportif - DECATHLON</t>
+        </is>
+      </c>
+      <c r="J211" s="33" t="n">
+        <v>9</v>
+      </c>
+      <c r="K211" s="28" t="n"/>
+      <c r="L211" s="32" t="n"/>
+    </row>
+    <row r="212">
+      <c r="E212" s="16" t="n"/>
+      <c r="F212" s="17" t="n"/>
+      <c r="G212" s="31" t="n"/>
+      <c r="H212" s="32" t="n"/>
+      <c r="I212" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J212" s="33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K212" s="28" t="n"/>
+      <c r="L212" s="32" t="n"/>
+    </row>
+    <row r="213">
+      <c r="E213" s="16" t="n"/>
+      <c r="F213" s="17" t="n"/>
+      <c r="G213" s="31" t="n"/>
+      <c r="H213" s="32" t="n"/>
+      <c r="I213" s="13" t="inlineStr">
+        <is>
+          <t>Proximus</t>
+        </is>
+      </c>
+      <c r="J213" s="33" t="n">
+        <v>180.92</v>
+      </c>
+      <c r="K213" s="28" t="n"/>
+      <c r="L213" s="32" t="n"/>
+    </row>
+    <row r="214">
+      <c r="E214" s="16" t="n"/>
+      <c r="F214" s="17" t="n"/>
+      <c r="G214" s="31" t="n"/>
+      <c r="H214" s="32" t="n"/>
+      <c r="I214" s="13" t="inlineStr">
+        <is>
+          <t>Carburant</t>
+        </is>
+      </c>
+      <c r="J214" s="33" t="n">
+        <v>76.89</v>
+      </c>
+      <c r="K214" s="28" t="n"/>
+      <c r="L214" s="32" t="n"/>
+    </row>
+    <row r="215">
+      <c r="E215" s="16" t="n"/>
+      <c r="F215" s="17" t="n"/>
+      <c r="G215" s="31" t="n"/>
+      <c r="H215" s="32" t="n"/>
+      <c r="I215" s="40" t="inlineStr">
+        <is>
+          <t>Abonnement salle FitRaw</t>
+        </is>
+      </c>
+      <c r="J215" s="41" t="n">
+        <v>22.86</v>
+      </c>
+      <c r="K215" s="28" t="n"/>
+      <c r="L215" s="39" t="inlineStr">
+        <is>
+          <t>Sterrebeek — usage professionnel à confirmer</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="E216" s="16" t="n"/>
+      <c r="F216" s="17" t="n"/>
+      <c r="G216" s="31" t="n"/>
+      <c r="H216" s="32" t="n"/>
+      <c r="I216" s="13" t="inlineStr">
+        <is>
+          <t>Précompte salarial juillet 2026 Thibault Duchène</t>
+        </is>
+      </c>
+      <c r="J216" s="33" t="n">
+        <v>2250</v>
+      </c>
+      <c r="K216" s="28" t="n"/>
+      <c r="L216" s="32" t="n"/>
+    </row>
+    <row r="217">
+      <c r="E217" s="16" t="n"/>
+      <c r="F217" s="17" t="n"/>
+      <c r="G217" s="31" t="n"/>
+      <c r="H217" s="32" t="n"/>
+      <c r="I217" s="13" t="inlineStr">
+        <is>
+          <t>Assurance voiture - Yuzzu</t>
+        </is>
+      </c>
+      <c r="J217" s="33" t="n">
+        <v>1190.65</v>
+      </c>
+      <c r="K217" s="28" t="n"/>
+      <c r="L217" s="32" t="n"/>
+    </row>
+    <row r="218">
+      <c r="E218" s="16" t="n"/>
+      <c r="F218" s="17" t="n"/>
+      <c r="G218" s="31" t="n"/>
+      <c r="H218" s="32" t="n"/>
+      <c r="I218" s="13" t="inlineStr">
+        <is>
+          <t>Entretien voiture - Monsieur Pneus</t>
+        </is>
+      </c>
+      <c r="J218" s="33" t="n">
+        <v>423.98</v>
+      </c>
+      <c r="K218" s="28" t="n"/>
+      <c r="L218" s="32" t="n"/>
+    </row>
+    <row r="219">
+      <c r="E219" s="16" t="n"/>
+      <c r="F219" s="17" t="n"/>
+      <c r="G219" s="31" t="n"/>
+      <c r="H219" s="32" t="n"/>
+      <c r="I219" s="13" t="inlineStr">
+        <is>
+          <t>SD Worx</t>
+        </is>
+      </c>
+      <c r="J219" s="33" t="n">
+        <v>333.29</v>
+      </c>
+      <c r="K219" s="28" t="n"/>
+      <c r="L219" s="32" t="n"/>
+    </row>
+    <row r="220">
+      <c r="G220" s="34" t="n"/>
+      <c r="H220" s="35" t="n"/>
+      <c r="J220" s="34" t="n"/>
+      <c r="L220" s="35" t="n"/>
+    </row>
+    <row r="221">
+      <c r="G221" s="34" t="n"/>
+      <c r="H221" s="35" t="n"/>
+      <c r="J221" s="34" t="n"/>
+      <c r="L221" s="35" t="n"/>
+    </row>
+    <row r="222">
+      <c r="E222" s="16" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="F222" s="17" t="inlineStr">
+        <is>
+          <t>LAM2609</t>
+        </is>
+      </c>
+      <c r="G222" s="31" t="n">
+        <v>5341.8</v>
+      </c>
+      <c r="H222" s="32" t="n"/>
+      <c r="I222" s="28" t="inlineStr">
+        <is>
+          <t>Divers - Mister Minit</t>
+        </is>
+      </c>
+      <c r="J222" s="36" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="K222" s="28" t="n"/>
+      <c r="L222" s="32" t="n"/>
+    </row>
+    <row r="223">
+      <c r="E223" s="16" t="n"/>
+      <c r="F223" s="17" t="inlineStr">
+        <is>
+          <t>LAM2610</t>
+        </is>
+      </c>
+      <c r="G223" s="31" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H223" s="32" t="n"/>
+      <c r="I223" s="13" t="inlineStr">
+        <is>
+          <t>Achat matériel sportif - Bellissimo Sport</t>
+        </is>
+      </c>
+      <c r="J223" s="33" t="n">
+        <v>12</v>
+      </c>
+      <c r="K223" s="28" t="n"/>
+      <c r="L223" s="32" t="n"/>
+    </row>
+    <row r="224">
+      <c r="E224" s="16" t="n"/>
+      <c r="F224" s="17" t="n"/>
+      <c r="G224" s="31" t="n"/>
+      <c r="H224" s="32" t="n"/>
+      <c r="I224" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J224" s="33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K224" s="28" t="n"/>
+      <c r="L224" s="32" t="n"/>
+    </row>
+    <row r="225">
+      <c r="E225" s="16" t="n"/>
+      <c r="F225" s="17" t="n"/>
+      <c r="G225" s="31" t="n"/>
+      <c r="H225" s="32" t="n"/>
+      <c r="I225" s="13" t="inlineStr">
+        <is>
+          <t>Farys (eau)</t>
+        </is>
+      </c>
+      <c r="J225" s="33" t="n">
+        <v>306</v>
+      </c>
+      <c r="K225" s="28" t="n"/>
+      <c r="L225" s="32" t="n"/>
+    </row>
+    <row r="226">
+      <c r="E226" s="16" t="n"/>
+      <c r="F226" s="17" t="n"/>
+      <c r="G226" s="31" t="n"/>
+      <c r="H226" s="32" t="n"/>
+      <c r="I226" s="13" t="inlineStr">
+        <is>
+          <t>Electrabel</t>
+        </is>
+      </c>
+      <c r="J226" s="33" t="n">
+        <v>141.56</v>
+      </c>
+      <c r="K226" s="28" t="n"/>
+      <c r="L226" s="32" t="n"/>
+    </row>
+    <row r="227">
+      <c r="E227" s="16" t="n"/>
+      <c r="F227" s="17" t="n"/>
+      <c r="G227" s="31" t="n"/>
+      <c r="H227" s="32" t="n"/>
+      <c r="I227" s="13" t="inlineStr">
+        <is>
+          <t>Crédit voiture</t>
+        </is>
+      </c>
+      <c r="J227" s="33" t="n">
+        <v>724.12</v>
+      </c>
+      <c r="K227" s="28" t="n"/>
+      <c r="L227" s="32" t="n"/>
+    </row>
+    <row r="228">
+      <c r="E228" s="16" t="n"/>
+      <c r="F228" s="17" t="n"/>
+      <c r="G228" s="31" t="n"/>
+      <c r="H228" s="32" t="n"/>
+      <c r="I228" s="40" t="inlineStr">
+        <is>
+          <t>Abonnement club David Lloyd</t>
+        </is>
+      </c>
+      <c r="J228" s="41" t="n">
+        <v>493</v>
+      </c>
+      <c r="K228" s="28" t="n"/>
+      <c r="L228" s="39" t="inlineStr">
+        <is>
+          <t>Sterrebeek — usage professionnel à confirmer</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="E229" s="16" t="n"/>
+      <c r="F229" s="17" t="n"/>
+      <c r="G229" s="31" t="n"/>
+      <c r="H229" s="32" t="n"/>
+      <c r="I229" s="13" t="inlineStr">
+        <is>
+          <t>Carburant</t>
+        </is>
+      </c>
+      <c r="J229" s="33" t="n">
+        <v>98.54000000000001</v>
+      </c>
+      <c r="K229" s="28" t="n"/>
+      <c r="L229" s="32" t="n"/>
+    </row>
+    <row r="230">
+      <c r="E230" s="16" t="n"/>
+      <c r="F230" s="17" t="n"/>
+      <c r="G230" s="31" t="n"/>
+      <c r="H230" s="32" t="n"/>
+      <c r="I230" s="13" t="inlineStr">
+        <is>
+          <t>Carburant</t>
+        </is>
+      </c>
+      <c r="J230" s="33" t="n">
+        <v>84.61</v>
+      </c>
+      <c r="K230" s="28" t="n"/>
+      <c r="L230" s="32" t="n"/>
+    </row>
+    <row r="231">
+      <c r="E231" s="16" t="n"/>
+      <c r="F231" s="17" t="n"/>
+      <c r="G231" s="31" t="n"/>
+      <c r="H231" s="32" t="n"/>
+      <c r="I231" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J231" s="33" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K231" s="28" t="n"/>
+      <c r="L231" s="32" t="inlineStr">
+        <is>
+          <t>Côte d'Azur (France)</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="E232" s="16" t="n"/>
+      <c r="F232" s="17" t="n"/>
+      <c r="G232" s="31" t="n"/>
+      <c r="H232" s="32" t="n"/>
+      <c r="I232" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J232" s="33" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K232" s="28" t="n"/>
+      <c r="L232" s="32" t="inlineStr">
+        <is>
+          <t>Côte d'Azur (France)</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="E233" s="16" t="n"/>
+      <c r="F233" s="17" t="n"/>
+      <c r="G233" s="31" t="n"/>
+      <c r="H233" s="32" t="n"/>
+      <c r="I233" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J233" s="33" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K233" s="28" t="n"/>
+      <c r="L233" s="32" t="inlineStr">
+        <is>
+          <t>Côte d'Azur (France)</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="E234" s="16" t="n"/>
+      <c r="F234" s="17" t="n"/>
+      <c r="G234" s="31" t="n"/>
+      <c r="H234" s="32" t="n"/>
+      <c r="I234" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J234" s="33" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K234" s="28" t="n"/>
+      <c r="L234" s="32" t="inlineStr">
+        <is>
+          <t>Côte d'Azur (France)</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="E235" s="16" t="n"/>
+      <c r="F235" s="17" t="n"/>
+      <c r="G235" s="31" t="n"/>
+      <c r="H235" s="32" t="n"/>
+      <c r="I235" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J235" s="33" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K235" s="28" t="n"/>
+      <c r="L235" s="32" t="inlineStr">
+        <is>
+          <t>Côte d'Azur (France)</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="E236" s="16" t="n"/>
+      <c r="F236" s="17" t="n"/>
+      <c r="G236" s="31" t="n"/>
+      <c r="H236" s="32" t="n"/>
+      <c r="I236" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J236" s="33" t="n">
+        <v>9</v>
+      </c>
+      <c r="K236" s="28" t="n"/>
+      <c r="L236" s="32" t="n"/>
+    </row>
+    <row r="237">
+      <c r="E237" s="16" t="n"/>
+      <c r="F237" s="17" t="n"/>
+      <c r="G237" s="31" t="n"/>
+      <c r="H237" s="32" t="n"/>
+      <c r="I237" s="40" t="inlineStr">
+        <is>
+          <t>Achat - Castillon Fréjus</t>
+        </is>
+      </c>
+      <c r="J237" s="41" t="n">
+        <v>80</v>
+      </c>
+      <c r="K237" s="28" t="n"/>
+      <c r="L237" s="39" t="inlineStr">
+        <is>
+          <t>France — à identifier</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="E238" s="16" t="n"/>
+      <c r="F238" s="17" t="n"/>
+      <c r="G238" s="31" t="n"/>
+      <c r="H238" s="32" t="n"/>
+      <c r="I238" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J238" s="33" t="n">
+        <v>19</v>
+      </c>
+      <c r="K238" s="28" t="n"/>
+      <c r="L238" s="32" t="inlineStr">
+        <is>
+          <t>Côte d'Azur (France)</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="E239" s="16" t="n"/>
+      <c r="F239" s="17" t="n"/>
+      <c r="G239" s="31" t="n"/>
+      <c r="H239" s="32" t="n"/>
+      <c r="I239" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J239" s="33" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="K239" s="28" t="n"/>
+      <c r="L239" s="32" t="inlineStr">
+        <is>
+          <t>Côte d'Azur (France)</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="E240" s="16" t="n"/>
+      <c r="F240" s="17" t="n"/>
+      <c r="G240" s="31" t="n"/>
+      <c r="H240" s="32" t="n"/>
+      <c r="I240" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J240" s="33" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K240" s="28" t="n"/>
+      <c r="L240" s="32" t="inlineStr">
+        <is>
+          <t>Côte d'Azur (France)</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="E241" s="16" t="n"/>
+      <c r="F241" s="17" t="n"/>
+      <c r="G241" s="31" t="n"/>
+      <c r="H241" s="32" t="n"/>
+      <c r="I241" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J241" s="33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K241" s="28" t="n"/>
+      <c r="L241" s="32" t="inlineStr">
+        <is>
+          <t>Côte d'Azur (France)</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="E242" s="16" t="n"/>
+      <c r="F242" s="17" t="n"/>
+      <c r="G242" s="31" t="n"/>
+      <c r="H242" s="32" t="n"/>
+      <c r="I242" s="13" t="inlineStr">
+        <is>
+          <t>Paiement carte de crédit</t>
+        </is>
+      </c>
+      <c r="J242" s="33" t="n">
+        <v>2431.44</v>
+      </c>
+      <c r="K242" s="28" t="n"/>
+      <c r="L242" s="32" t="n"/>
+    </row>
+    <row r="243">
+      <c r="E243" s="16" t="n"/>
+      <c r="F243" s="17" t="n"/>
+      <c r="G243" s="31" t="n"/>
+      <c r="H243" s="32" t="n"/>
+      <c r="I243" s="40" t="inlineStr">
+        <is>
+          <t>Carburant</t>
+        </is>
+      </c>
+      <c r="J243" s="41" t="n">
+        <v>75.33</v>
+      </c>
+      <c r="K243" s="28" t="n"/>
+      <c r="L243" s="39" t="inlineStr">
+        <is>
+          <t>E.Leclerc Mornas (France) — à confirmer</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="E244" s="16" t="n"/>
+      <c r="F244" s="17" t="n"/>
+      <c r="G244" s="31" t="n"/>
+      <c r="H244" s="32" t="n"/>
+      <c r="I244" s="13" t="inlineStr">
+        <is>
+          <t>Carburant</t>
+        </is>
+      </c>
+      <c r="J244" s="33" t="n">
+        <v>83.84999999999999</v>
+      </c>
+      <c r="K244" s="28" t="n"/>
+      <c r="L244" s="32" t="n"/>
+    </row>
+    <row r="245">
+      <c r="E245" s="16" t="n"/>
+      <c r="F245" s="17" t="n"/>
+      <c r="G245" s="31" t="n"/>
+      <c r="H245" s="32" t="n"/>
+      <c r="I245" s="13" t="inlineStr">
+        <is>
+          <t>Carburant</t>
+        </is>
+      </c>
+      <c r="J245" s="33" t="n">
+        <v>77.98</v>
+      </c>
+      <c r="K245" s="28" t="n"/>
+      <c r="L245" s="32" t="n"/>
+    </row>
+    <row r="246">
+      <c r="E246" s="16" t="n"/>
+      <c r="F246" s="17" t="n"/>
+      <c r="G246" s="31" t="n"/>
+      <c r="H246" s="32" t="n"/>
+      <c r="I246" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J246" s="33" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K246" s="28" t="n"/>
+      <c r="L246" s="32" t="n"/>
+    </row>
+    <row r="247">
+      <c r="E247" s="16" t="n"/>
+      <c r="F247" s="17" t="n"/>
+      <c r="G247" s="31" t="n"/>
+      <c r="H247" s="32" t="n"/>
+      <c r="I247" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J247" s="33" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K247" s="28" t="n"/>
+      <c r="L247" s="32" t="n"/>
+    </row>
+    <row r="248">
+      <c r="E248" s="16" t="n"/>
+      <c r="F248" s="17" t="n"/>
+      <c r="G248" s="31" t="n"/>
+      <c r="H248" s="32" t="n"/>
+      <c r="I248" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J248" s="33" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K248" s="28" t="n"/>
+      <c r="L248" s="32" t="n"/>
+    </row>
+    <row r="249">
+      <c r="E249" s="16" t="n"/>
+      <c r="F249" s="17" t="n"/>
+      <c r="G249" s="31" t="n"/>
+      <c r="H249" s="32" t="n"/>
+      <c r="I249" s="13" t="inlineStr">
+        <is>
+          <t>Précompte salarial aout 2026 Thibault Duchène</t>
+        </is>
+      </c>
+      <c r="J249" s="33" t="n">
+        <v>2250</v>
+      </c>
+      <c r="K249" s="28" t="n"/>
+      <c r="L249" s="32" t="n"/>
+    </row>
+    <row r="250">
+      <c r="E250" s="16" t="n"/>
+      <c r="F250" s="17" t="n"/>
+      <c r="G250" s="31" t="n"/>
+      <c r="H250" s="32" t="n"/>
+      <c r="I250" s="13" t="inlineStr">
+        <is>
+          <t>Partena</t>
+        </is>
+      </c>
+      <c r="J250" s="33" t="n">
+        <v>1747.34</v>
+      </c>
+      <c r="K250" s="28" t="n"/>
+      <c r="L250" s="32" t="n"/>
+    </row>
+    <row r="251">
+      <c r="E251" s="16" t="n"/>
+      <c r="F251" s="17" t="n"/>
+      <c r="G251" s="31" t="n"/>
+      <c r="H251" s="32" t="n"/>
+      <c r="I251" s="13" t="inlineStr">
+        <is>
+          <t>SD Worx</t>
+        </is>
+      </c>
+      <c r="J251" s="33" t="n">
+        <v>333.29</v>
+      </c>
+      <c r="K251" s="28" t="n"/>
+      <c r="L251" s="32" t="n"/>
+    </row>
+    <row r="252">
+      <c r="E252" s="16" t="n"/>
+      <c r="F252" s="17" t="n"/>
+      <c r="G252" s="31" t="n"/>
+      <c r="H252" s="32" t="n"/>
+      <c r="I252" s="13" t="inlineStr">
+        <is>
+          <t>Electrabel</t>
+        </is>
+      </c>
+      <c r="J252" s="33" t="n">
+        <v>294.73</v>
+      </c>
+      <c r="K252" s="28" t="n"/>
+      <c r="L252" s="32" t="n"/>
+    </row>
+    <row r="253">
+      <c r="E253" s="16" t="n"/>
+      <c r="F253" s="17" t="n"/>
+      <c r="G253" s="31" t="n"/>
+      <c r="H253" s="32" t="n"/>
+      <c r="I253" s="13" t="inlineStr">
+        <is>
+          <t>Vlaamse Belastingsdienst - taxe de circulation</t>
+        </is>
+      </c>
+      <c r="J253" s="33" t="n">
+        <v>167.59</v>
+      </c>
+      <c r="K253" s="28" t="n"/>
+      <c r="L253" s="32" t="n"/>
+    </row>
+    <row r="254">
+      <c r="E254" s="16" t="n"/>
+      <c r="F254" s="17" t="n"/>
+      <c r="G254" s="31" t="n"/>
+      <c r="H254" s="32" t="n"/>
+      <c r="I254" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J254" s="33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K254" s="28" t="n"/>
+      <c r="L254" s="32" t="n"/>
+    </row>
+    <row r="255">
+      <c r="G255" s="34" t="n"/>
+      <c r="H255" s="35" t="n"/>
+      <c r="J255" s="34" t="n"/>
+      <c r="L255" s="35" t="n"/>
+    </row>
+    <row r="256">
+      <c r="G256" s="34" t="n"/>
+      <c r="H256" s="35" t="n"/>
+      <c r="J256" s="34" t="n"/>
+      <c r="L256" s="35" t="n"/>
+    </row>
+    <row r="257">
+      <c r="G257" s="34">
+        <f>SUM(G6:G256)</f>
         <v/>
       </c>
-      <c r="H30" s="35" t="n"/>
-      <c r="J30" s="34">
-        <f>SUM(J6:J29)</f>
+      <c r="H257" s="35" t="n"/>
+      <c r="J257" s="34">
+        <f>SUM(J6:J256)</f>
         <v/>
       </c>
-      <c r="L30" s="35" t="n"/>
+      <c r="L257" s="35" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Bilan_2026_MTCB.xlsx
+++ b/Bilan_2026_MTCB.xlsx
@@ -1228,10 +1228,14 @@
       <c r="J25" s="33" t="n">
         <v>1179.75</v>
       </c>
-      <c r="K25" s="28" t="n"/>
+      <c r="K25" s="28" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="L25" s="32" t="inlineStr">
         <is>
-          <t>Facture 20250542 — facture 2025 payée en 2026</t>
+          <t>Facture 20250542 — facture 2025 payée en 2026 — Facture BDH en main, chargée dans Billtobox</t>
         </is>
       </c>
     </row>

--- a/Bilan_2026_MTCB.xlsx
+++ b/Bilan_2026_MTCB.xlsx
@@ -868,7 +868,11 @@
       <c r="J6" s="33" t="n">
         <v>69.7</v>
       </c>
-      <c r="K6" s="28" t="n"/>
+      <c r="K6" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L6" s="32" t="inlineStr">
         <is>
           <t>Shell Kraainem</t>
@@ -996,7 +1000,11 @@
       <c r="J13" s="33" t="n">
         <v>44.88</v>
       </c>
-      <c r="K13" s="28" t="n"/>
+      <c r="K13" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L13" s="32" t="inlineStr">
         <is>
           <t>Lukoil Wezembeek</t>
@@ -1016,7 +1024,11 @@
       <c r="J14" s="33" t="n">
         <v>65.2</v>
       </c>
-      <c r="K14" s="28" t="n"/>
+      <c r="K14" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L14" s="32" t="inlineStr">
         <is>
           <t>Total Saverne (France)</t>
@@ -1052,7 +1064,11 @@
       <c r="J16" s="33" t="n">
         <v>57.46</v>
       </c>
-      <c r="K16" s="28" t="n"/>
+      <c r="K16" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L16" s="32" t="inlineStr">
         <is>
           <t>BP Vaduz (Liechtenstein) — 51,90 CHF</t>
@@ -1092,7 +1108,11 @@
       <c r="J18" s="33" t="n">
         <v>73.48</v>
       </c>
-      <c r="K18" s="28" t="n"/>
+      <c r="K18" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L18" s="32" t="inlineStr">
         <is>
           <t>Esso Brumath (France)</t>
@@ -1132,7 +1152,11 @@
       <c r="J20" s="33" t="n">
         <v>74.63</v>
       </c>
-      <c r="K20" s="28" t="n"/>
+      <c r="K20" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L20" s="32" t="inlineStr">
         <is>
           <t>Q8 Easy Zaventem</t>
@@ -1208,7 +1232,11 @@
       <c r="J24" s="33" t="n">
         <v>64.56999999999999</v>
       </c>
-      <c r="K24" s="28" t="n"/>
+      <c r="K24" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L24" s="32" t="inlineStr">
         <is>
           <t>Shell Kraainem</t>
@@ -1344,7 +1372,11 @@
       <c r="J31" s="33" t="n">
         <v>63.37</v>
       </c>
-      <c r="K31" s="28" t="n"/>
+      <c r="K31" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L31" s="32" t="n"/>
     </row>
     <row r="32">
@@ -1566,7 +1598,11 @@
       <c r="J43" s="33" t="n">
         <v>64.23999999999999</v>
       </c>
-      <c r="K43" s="28" t="n"/>
+      <c r="K43" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L43" s="32" t="n"/>
     </row>
     <row r="44">
@@ -1630,7 +1666,11 @@
       <c r="J47" s="33" t="n">
         <v>63.63</v>
       </c>
-      <c r="K47" s="28" t="n"/>
+      <c r="K47" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L47" s="32" t="n"/>
     </row>
     <row r="48">
@@ -1766,7 +1806,11 @@
       <c r="J55" s="33" t="n">
         <v>62.54</v>
       </c>
-      <c r="K55" s="28" t="n"/>
+      <c r="K55" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L55" s="32" t="n"/>
     </row>
     <row r="56">
@@ -1938,7 +1982,11 @@
       <c r="J65" s="33" t="n">
         <v>64.62</v>
       </c>
-      <c r="K65" s="28" t="n"/>
+      <c r="K65" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L65" s="32" t="n"/>
     </row>
     <row r="66">
@@ -2102,7 +2150,11 @@
       <c r="J75" s="33" t="n">
         <v>76.45</v>
       </c>
-      <c r="K75" s="28" t="n"/>
+      <c r="K75" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L75" s="32" t="n"/>
     </row>
     <row r="76">
@@ -2150,7 +2202,11 @@
       <c r="J78" s="33" t="n">
         <v>65.54000000000001</v>
       </c>
-      <c r="K78" s="28" t="n"/>
+      <c r="K78" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L78" s="32" t="n"/>
     </row>
     <row r="79">
@@ -2182,7 +2238,11 @@
       <c r="J80" s="33" t="n">
         <v>63.82</v>
       </c>
-      <c r="K80" s="28" t="n"/>
+      <c r="K80" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L80" s="32" t="n"/>
     </row>
     <row r="81">
@@ -2238,7 +2298,11 @@
       <c r="J83" s="33" t="n">
         <v>84.56</v>
       </c>
-      <c r="K83" s="28" t="n"/>
+      <c r="K83" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L83" s="32" t="n"/>
     </row>
     <row r="84">
@@ -2484,7 +2548,11 @@
       <c r="J97" s="36" t="n">
         <v>64.48</v>
       </c>
-      <c r="K97" s="28" t="n"/>
+      <c r="K97" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L97" s="32" t="inlineStr">
         <is>
           <t>ENI (Italie)</t>
@@ -2634,7 +2702,11 @@
       <c r="J104" s="33" t="n">
         <v>76.5</v>
       </c>
-      <c r="K104" s="28" t="n"/>
+      <c r="K104" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L104" s="32" t="inlineStr">
         <is>
           <t>ENI (Italie)</t>
@@ -2894,7 +2966,11 @@
       <c r="J119" s="33" t="n">
         <v>80.90000000000001</v>
       </c>
-      <c r="K119" s="28" t="n"/>
+      <c r="K119" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L119" s="32" t="n"/>
     </row>
     <row r="120">
@@ -2962,7 +3038,11 @@
       <c r="J123" s="33" t="n">
         <v>77.88</v>
       </c>
-      <c r="K123" s="28" t="n"/>
+      <c r="K123" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L123" s="32" t="n"/>
     </row>
     <row r="124">
@@ -3030,7 +3110,11 @@
       <c r="J127" s="33" t="n">
         <v>4.35</v>
       </c>
-      <c r="K127" s="28" t="n"/>
+      <c r="K127" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L127" s="32" t="inlineStr">
         <is>
           <t>Total Schaerbeek</t>
@@ -3208,7 +3292,11 @@
       <c r="J138" s="36" t="n">
         <v>89.01000000000001</v>
       </c>
-      <c r="K138" s="28" t="n"/>
+      <c r="K138" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L138" s="32" t="n"/>
     </row>
     <row r="139">
@@ -3340,7 +3428,11 @@
       <c r="J146" s="33" t="n">
         <v>85.45</v>
       </c>
-      <c r="K146" s="28" t="n"/>
+      <c r="K146" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L146" s="32" t="inlineStr">
         <is>
           <t>Total Schaerbeek</t>
@@ -3424,7 +3516,11 @@
       <c r="J151" s="33" t="n">
         <v>72.66</v>
       </c>
-      <c r="K151" s="28" t="n"/>
+      <c r="K151" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L151" s="32" t="n"/>
     </row>
     <row r="152">
@@ -3440,7 +3536,11 @@
       <c r="J152" s="33" t="n">
         <v>6.55</v>
       </c>
-      <c r="K152" s="28" t="n"/>
+      <c r="K152" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L152" s="32" t="n"/>
     </row>
     <row r="153">
@@ -3528,7 +3628,11 @@
       <c r="J157" s="33" t="n">
         <v>79.51000000000001</v>
       </c>
-      <c r="K157" s="28" t="n"/>
+      <c r="K157" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L157" s="32" t="n"/>
     </row>
     <row r="158">
@@ -3618,7 +3722,11 @@
       <c r="J163" s="36" t="n">
         <v>75.41</v>
       </c>
-      <c r="K163" s="28" t="n"/>
+      <c r="K163" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L163" s="32" t="n"/>
     </row>
     <row r="164">
@@ -3676,7 +3784,11 @@
       <c r="J166" s="33" t="n">
         <v>83.72</v>
       </c>
-      <c r="K166" s="28" t="n"/>
+      <c r="K166" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L166" s="32" t="n"/>
     </row>
     <row r="167">
@@ -3756,7 +3868,11 @@
       <c r="J171" s="33" t="n">
         <v>80.15000000000001</v>
       </c>
-      <c r="K171" s="28" t="n"/>
+      <c r="K171" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L171" s="32" t="n"/>
     </row>
     <row r="172">
@@ -3904,7 +4020,11 @@
       <c r="J180" s="33" t="n">
         <v>83.5</v>
       </c>
-      <c r="K180" s="28" t="n"/>
+      <c r="K180" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L180" s="32" t="n"/>
     </row>
     <row r="181">
@@ -4024,7 +4144,11 @@
       <c r="J187" s="33" t="n">
         <v>77.3</v>
       </c>
-      <c r="K187" s="28" t="n"/>
+      <c r="K187" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L187" s="32" t="n"/>
     </row>
     <row r="188">
@@ -4108,7 +4232,11 @@
       <c r="J192" s="33" t="n">
         <v>76.98999999999999</v>
       </c>
-      <c r="K192" s="28" t="n"/>
+      <c r="K192" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L192" s="32" t="n"/>
     </row>
     <row r="193">
@@ -4268,7 +4396,11 @@
       <c r="J201" s="33" t="n">
         <v>79.41</v>
       </c>
-      <c r="K201" s="28" t="n"/>
+      <c r="K201" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L201" s="32" t="n"/>
     </row>
     <row r="202">
@@ -4364,7 +4496,11 @@
       <c r="J207" s="33" t="n">
         <v>79.42</v>
       </c>
-      <c r="K207" s="28" t="n"/>
+      <c r="K207" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L207" s="32" t="n"/>
     </row>
     <row r="208">
@@ -4480,7 +4616,11 @@
       <c r="J214" s="33" t="n">
         <v>76.89</v>
       </c>
-      <c r="K214" s="28" t="n"/>
+      <c r="K214" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L214" s="32" t="n"/>
     </row>
     <row r="215">
@@ -4724,7 +4864,11 @@
       <c r="J229" s="33" t="n">
         <v>98.54000000000001</v>
       </c>
-      <c r="K229" s="28" t="n"/>
+      <c r="K229" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L229" s="32" t="n"/>
     </row>
     <row r="230">
@@ -4740,7 +4884,11 @@
       <c r="J230" s="33" t="n">
         <v>84.61</v>
       </c>
-      <c r="K230" s="28" t="n"/>
+      <c r="K230" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L230" s="32" t="n"/>
     </row>
     <row r="231">
@@ -4988,7 +5136,11 @@
       <c r="J243" s="41" t="n">
         <v>75.33</v>
       </c>
-      <c r="K243" s="28" t="n"/>
+      <c r="K243" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L243" s="39" t="inlineStr">
         <is>
           <t>E.Leclerc Mornas (France) — à confirmer</t>
@@ -5008,7 +5160,11 @@
       <c r="J244" s="33" t="n">
         <v>83.84999999999999</v>
       </c>
-      <c r="K244" s="28" t="n"/>
+      <c r="K244" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L244" s="32" t="n"/>
     </row>
     <row r="245">
@@ -5024,7 +5180,11 @@
       <c r="J245" s="33" t="n">
         <v>77.98</v>
       </c>
-      <c r="K245" s="28" t="n"/>
+      <c r="K245" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L245" s="32" t="n"/>
     </row>
     <row r="246">

--- a/Bilan_2026_MTCB.xlsx
+++ b/Bilan_2026_MTCB.xlsx
@@ -932,7 +932,11 @@
       <c r="J9" s="33" t="n">
         <v>4.8</v>
       </c>
-      <c r="K9" s="28" t="n"/>
+      <c r="K9" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L9" s="32" t="inlineStr">
         <is>
           <t>Woluwe-Saint-Lambert</t>
@@ -952,7 +956,11 @@
       <c r="J10" s="33" t="n">
         <v>724.12</v>
       </c>
-      <c r="K10" s="28" t="n"/>
+      <c r="K10" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L10" s="32" t="n"/>
     </row>
     <row r="11">
@@ -1088,7 +1096,11 @@
       <c r="J17" s="33" t="n">
         <v>20.3</v>
       </c>
-      <c r="K17" s="28" t="n"/>
+      <c r="K17" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L17" s="32" t="inlineStr">
         <is>
           <t>Parkhaus Bahnhofplatz, Coire (Suisse) — 18,00 CHF</t>
@@ -1132,7 +1144,11 @@
       <c r="J19" s="33" t="n">
         <v>1.85</v>
       </c>
-      <c r="K19" s="28" t="n"/>
+      <c r="K19" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L19" s="32" t="inlineStr">
         <is>
           <t>Q-Park Woluwe Esplanade</t>
@@ -1212,7 +1228,11 @@
       <c r="J23" s="33" t="n">
         <v>11</v>
       </c>
-      <c r="K23" s="28" t="n"/>
+      <c r="K23" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L23" s="32" t="inlineStr">
         <is>
           <t>Parking Grand-Place, Bruxelles</t>
@@ -1280,7 +1300,11 @@
       <c r="J26" s="33" t="n">
         <v>1.6</v>
       </c>
-      <c r="K26" s="28" t="n"/>
+      <c r="K26" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L26" s="32" t="inlineStr">
         <is>
           <t>Woluwe-Saint-Lambert</t>
@@ -1300,7 +1324,11 @@
       <c r="J27" s="33" t="n">
         <v>1.35</v>
       </c>
-      <c r="K27" s="28" t="n"/>
+      <c r="K27" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L27" s="32" t="inlineStr">
         <is>
           <t>Schaerbeek</t>
@@ -1342,7 +1370,11 @@
       <c r="J30" s="36" t="n">
         <v>3.7</v>
       </c>
-      <c r="K30" s="28" t="n"/>
+      <c r="K30" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L30" s="32" t="inlineStr">
         <is>
           <t>Administration communale, Bruxelles</t>
@@ -1446,7 +1478,11 @@
       <c r="J34" s="33" t="n">
         <v>3.8</v>
       </c>
-      <c r="K34" s="28" t="n"/>
+      <c r="K34" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L34" s="32" t="n"/>
     </row>
     <row r="35">
@@ -1462,7 +1498,11 @@
       <c r="J35" s="33" t="n">
         <v>724.12</v>
       </c>
-      <c r="K35" s="28" t="n"/>
+      <c r="K35" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L35" s="32" t="n"/>
     </row>
     <row r="36">
@@ -1514,7 +1554,11 @@
       <c r="J38" s="33" t="n">
         <v>10.2</v>
       </c>
-      <c r="K38" s="28" t="n"/>
+      <c r="K38" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L38" s="32" t="n"/>
     </row>
     <row r="39">
@@ -1582,7 +1626,11 @@
       <c r="J42" s="33" t="n">
         <v>3.8</v>
       </c>
-      <c r="K42" s="28" t="n"/>
+      <c r="K42" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L42" s="32" t="n"/>
     </row>
     <row r="43">
@@ -1618,7 +1666,11 @@
       <c r="J44" s="33" t="n">
         <v>7.6</v>
       </c>
-      <c r="K44" s="28" t="n"/>
+      <c r="K44" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L44" s="32" t="n"/>
     </row>
     <row r="45">
@@ -1634,7 +1686,11 @@
       <c r="J45" s="33" t="n">
         <v>1.9</v>
       </c>
-      <c r="K45" s="28" t="n"/>
+      <c r="K45" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L45" s="32" t="n"/>
     </row>
     <row r="46">
@@ -1650,7 +1706,11 @@
       <c r="J46" s="33" t="n">
         <v>3.4</v>
       </c>
-      <c r="K46" s="28" t="n"/>
+      <c r="K46" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L46" s="32" t="n"/>
     </row>
     <row r="47">
@@ -1742,7 +1802,11 @@
       <c r="J51" s="33" t="n">
         <v>8.1</v>
       </c>
-      <c r="K51" s="28" t="n"/>
+      <c r="K51" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L51" s="32" t="n"/>
     </row>
     <row r="52">
@@ -1790,7 +1854,11 @@
       <c r="J54" s="33" t="n">
         <v>3.4</v>
       </c>
-      <c r="K54" s="28" t="n"/>
+      <c r="K54" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L54" s="32" t="n"/>
     </row>
     <row r="55">
@@ -1826,7 +1894,11 @@
       <c r="J56" s="33" t="n">
         <v>3.8</v>
       </c>
-      <c r="K56" s="28" t="n"/>
+      <c r="K56" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L56" s="32" t="n"/>
     </row>
     <row r="57">
@@ -1874,7 +1946,11 @@
       <c r="J59" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="K59" s="28" t="n"/>
+      <c r="K59" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L59" s="32" t="n"/>
     </row>
     <row r="60">
@@ -1938,7 +2014,11 @@
       <c r="J63" s="33" t="n">
         <v>4.5</v>
       </c>
-      <c r="K63" s="28" t="n"/>
+      <c r="K63" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L63" s="32" t="n"/>
     </row>
     <row r="64">
@@ -1960,7 +2040,11 @@
       <c r="J64" s="33" t="n">
         <v>1.7</v>
       </c>
-      <c r="K64" s="28" t="n"/>
+      <c r="K64" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L64" s="32" t="n"/>
     </row>
     <row r="65">
@@ -2002,7 +2086,11 @@
       <c r="J66" s="33" t="n">
         <v>724.12</v>
       </c>
-      <c r="K66" s="28" t="n"/>
+      <c r="K66" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L66" s="32" t="n"/>
     </row>
     <row r="67">
@@ -2018,7 +2106,11 @@
       <c r="J67" s="33" t="n">
         <v>5.7</v>
       </c>
-      <c r="K67" s="28" t="n"/>
+      <c r="K67" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L67" s="32" t="n"/>
     </row>
     <row r="68">
@@ -2098,7 +2190,11 @@
       <c r="J72" s="33" t="n">
         <v>3.4</v>
       </c>
-      <c r="K72" s="28" t="n"/>
+      <c r="K72" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L72" s="32" t="n"/>
     </row>
     <row r="73">
@@ -2114,7 +2210,11 @@
       <c r="J73" s="33" t="n">
         <v>1.7</v>
       </c>
-      <c r="K73" s="28" t="n"/>
+      <c r="K73" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L73" s="32" t="n"/>
     </row>
     <row r="74">
@@ -2186,7 +2286,11 @@
       <c r="J77" s="33" t="n">
         <v>3.4</v>
       </c>
-      <c r="K77" s="28" t="n"/>
+      <c r="K77" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L77" s="32" t="n"/>
     </row>
     <row r="78">
@@ -2222,7 +2326,11 @@
       <c r="J79" s="33" t="n">
         <v>2.3</v>
       </c>
-      <c r="K79" s="28" t="n"/>
+      <c r="K79" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L79" s="32" t="n"/>
     </row>
     <row r="80">
@@ -2258,7 +2366,11 @@
       <c r="J81" s="33" t="n">
         <v>9</v>
       </c>
-      <c r="K81" s="28" t="n"/>
+      <c r="K81" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L81" s="32" t="inlineStr">
         <is>
           <t>Düsseldorf (Allemagne)</t>
@@ -2278,7 +2390,11 @@
       <c r="J82" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="K82" s="28" t="n"/>
+      <c r="K82" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L82" s="32" t="inlineStr">
         <is>
           <t>Düsseldorf (Allemagne)</t>
@@ -2318,7 +2434,11 @@
       <c r="J84" s="41" t="n">
         <v>7.8</v>
       </c>
-      <c r="K84" s="28" t="n"/>
+      <c r="K84" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L84" s="39" t="inlineStr">
         <is>
           <t>Hôpital, Bruxelles — à confirmer</t>
@@ -2338,7 +2458,11 @@
       <c r="J85" s="33" t="n">
         <v>2.1</v>
       </c>
-      <c r="K85" s="28" t="n"/>
+      <c r="K85" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L85" s="32" t="n"/>
     </row>
     <row r="86">
@@ -2390,7 +2514,11 @@
       <c r="J88" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="K88" s="28" t="n"/>
+      <c r="K88" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L88" s="32" t="inlineStr">
         <is>
           <t>Italie</t>
@@ -2410,7 +2538,11 @@
       <c r="J89" s="33" t="n">
         <v>2.45</v>
       </c>
-      <c r="K89" s="28" t="n"/>
+      <c r="K89" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L89" s="32" t="inlineStr">
         <is>
           <t>Italie</t>
@@ -2430,7 +2562,11 @@
       <c r="J90" s="33" t="n">
         <v>9.25</v>
       </c>
-      <c r="K90" s="28" t="n"/>
+      <c r="K90" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L90" s="32" t="inlineStr">
         <is>
           <t>Italie</t>
@@ -2486,7 +2622,11 @@
       <c r="J93" s="33" t="n">
         <v>36.5</v>
       </c>
-      <c r="K93" s="28" t="n"/>
+      <c r="K93" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L93" s="32" t="inlineStr">
         <is>
           <t>Italie</t>
@@ -2506,7 +2646,11 @@
       <c r="J94" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="K94" s="28" t="n"/>
+      <c r="K94" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L94" s="32" t="inlineStr">
         <is>
           <t>Italie</t>
@@ -2582,7 +2726,11 @@
       <c r="J98" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="K98" s="28" t="n"/>
+      <c r="K98" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L98" s="32" t="inlineStr">
         <is>
           <t>Italie</t>
@@ -2602,7 +2750,11 @@
       <c r="J99" s="33" t="n">
         <v>5.5</v>
       </c>
-      <c r="K99" s="28" t="n"/>
+      <c r="K99" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L99" s="32" t="inlineStr">
         <is>
           <t>Italie</t>
@@ -2622,7 +2774,11 @@
       <c r="J100" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="K100" s="28" t="n"/>
+      <c r="K100" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L100" s="32" t="inlineStr">
         <is>
           <t>Italie</t>
@@ -2642,7 +2798,11 @@
       <c r="J101" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="K101" s="28" t="n"/>
+      <c r="K101" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L101" s="32" t="inlineStr">
         <is>
           <t>Italie</t>
@@ -2662,7 +2822,11 @@
       <c r="J102" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="K102" s="28" t="n"/>
+      <c r="K102" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L102" s="32" t="inlineStr">
         <is>
           <t>Italie</t>
@@ -2682,7 +2846,11 @@
       <c r="J103" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="K103" s="28" t="n"/>
+      <c r="K103" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L103" s="32" t="inlineStr">
         <is>
           <t>Italie</t>
@@ -2726,7 +2894,11 @@
       <c r="J105" s="33" t="n">
         <v>39.5</v>
       </c>
-      <c r="K105" s="28" t="n"/>
+      <c r="K105" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L105" s="32" t="inlineStr">
         <is>
           <t>Italie</t>
@@ -2746,7 +2918,11 @@
       <c r="J106" s="33" t="n">
         <v>724.12</v>
       </c>
-      <c r="K106" s="28" t="n"/>
+      <c r="K106" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L106" s="32" t="n"/>
     </row>
     <row r="107">
@@ -2798,7 +2974,11 @@
       <c r="J109" s="33" t="n">
         <v>2.4</v>
       </c>
-      <c r="K109" s="28" t="n"/>
+      <c r="K109" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L109" s="32" t="n"/>
     </row>
     <row r="110">
@@ -2814,7 +2994,11 @@
       <c r="J110" s="33" t="n">
         <v>5000</v>
       </c>
-      <c r="K110" s="28" t="n"/>
+      <c r="K110" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L110" s="32" t="inlineStr">
         <is>
           <t>Comm. 073/4616/33527</t>
@@ -2850,7 +3034,11 @@
       <c r="J112" s="33" t="n">
         <v>3.8</v>
       </c>
-      <c r="K112" s="28" t="n"/>
+      <c r="K112" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L112" s="32" t="inlineStr">
         <is>
           <t>Italie</t>
@@ -2934,7 +3122,11 @@
       <c r="J117" s="33" t="n">
         <v>1.7</v>
       </c>
-      <c r="K117" s="28" t="n"/>
+      <c r="K117" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L117" s="32" t="n"/>
     </row>
     <row r="118">
@@ -2986,7 +3178,11 @@
       <c r="J120" s="33" t="n">
         <v>3.4</v>
       </c>
-      <c r="K120" s="28" t="n"/>
+      <c r="K120" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L120" s="32" t="n"/>
     </row>
     <row r="121">
@@ -3002,7 +3198,11 @@
       <c r="J121" s="33" t="n">
         <v>7.2</v>
       </c>
-      <c r="K121" s="28" t="n"/>
+      <c r="K121" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L121" s="32" t="n"/>
     </row>
     <row r="122">
@@ -3058,7 +3258,11 @@
       <c r="J124" s="33" t="n">
         <v>1.7</v>
       </c>
-      <c r="K124" s="28" t="n"/>
+      <c r="K124" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L124" s="32" t="n"/>
     </row>
     <row r="125">
@@ -3312,7 +3516,11 @@
       <c r="J139" s="33" t="n">
         <v>1.7</v>
       </c>
-      <c r="K139" s="28" t="n"/>
+      <c r="K139" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L139" s="32" t="n"/>
     </row>
     <row r="140">
@@ -3360,7 +3568,11 @@
       <c r="J142" s="33" t="n">
         <v>724.12</v>
       </c>
-      <c r="K142" s="28" t="n"/>
+      <c r="K142" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L142" s="32" t="n"/>
     </row>
     <row r="143">
@@ -3452,7 +3664,11 @@
       <c r="J147" s="33" t="n">
         <v>11.7</v>
       </c>
-      <c r="K147" s="28" t="n"/>
+      <c r="K147" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L147" s="32" t="n"/>
     </row>
     <row r="148">
@@ -3500,7 +3716,11 @@
       <c r="J150" s="33" t="n">
         <v>0.5</v>
       </c>
-      <c r="K150" s="28" t="n"/>
+      <c r="K150" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L150" s="32" t="n"/>
     </row>
     <row r="151">
@@ -3556,7 +3776,11 @@
       <c r="J153" s="33" t="n">
         <v>4.2</v>
       </c>
-      <c r="K153" s="28" t="n"/>
+      <c r="K153" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L153" s="32" t="n"/>
     </row>
     <row r="154">
@@ -3612,7 +3836,11 @@
       <c r="J156" s="33" t="n">
         <v>1.7</v>
       </c>
-      <c r="K156" s="28" t="n"/>
+      <c r="K156" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L156" s="32" t="n"/>
     </row>
     <row r="157">
@@ -3648,7 +3876,11 @@
       <c r="J158" s="33" t="n">
         <v>15.6</v>
       </c>
-      <c r="K158" s="28" t="n"/>
+      <c r="K158" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L158" s="32" t="inlineStr">
         <is>
           <t>Schiphol (Pays-Bas)</t>
@@ -3668,7 +3900,11 @@
       <c r="J159" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="K159" s="28" t="n"/>
+      <c r="K159" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L159" s="32" t="n"/>
     </row>
     <row r="160">
@@ -3684,7 +3920,11 @@
       <c r="J160" s="33" t="n">
         <v>6.8</v>
       </c>
-      <c r="K160" s="28" t="n"/>
+      <c r="K160" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L160" s="32" t="n"/>
     </row>
     <row r="161">
@@ -3768,7 +4008,11 @@
       <c r="J165" s="33" t="n">
         <v>724.12</v>
       </c>
-      <c r="K165" s="28" t="n"/>
+      <c r="K165" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L165" s="32" t="n"/>
     </row>
     <row r="166">
@@ -3804,7 +4048,11 @@
       <c r="J167" s="33" t="n">
         <v>43.75</v>
       </c>
-      <c r="K167" s="28" t="n"/>
+      <c r="K167" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L167" s="32" t="n"/>
     </row>
     <row r="168">
@@ -3888,7 +4136,11 @@
       <c r="J172" s="33" t="n">
         <v>1.9</v>
       </c>
-      <c r="K172" s="28" t="n"/>
+      <c r="K172" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L172" s="32" t="n"/>
     </row>
     <row r="173">
@@ -3940,7 +4192,11 @@
       <c r="J175" s="33" t="n">
         <v>6.3</v>
       </c>
-      <c r="K175" s="28" t="n"/>
+      <c r="K175" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L175" s="32" t="n"/>
     </row>
     <row r="176">
@@ -3956,7 +4212,11 @@
       <c r="J176" s="33" t="n">
         <v>3.8</v>
       </c>
-      <c r="K176" s="28" t="n"/>
+      <c r="K176" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L176" s="32" t="n"/>
     </row>
     <row r="177">
@@ -4072,7 +4332,11 @@
       <c r="J183" s="33" t="n">
         <v>8.43</v>
       </c>
-      <c r="K183" s="28" t="n"/>
+      <c r="K183" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L183" s="32" t="n"/>
     </row>
     <row r="184">
@@ -4088,7 +4352,11 @@
       <c r="J184" s="33" t="n">
         <v>35</v>
       </c>
-      <c r="K184" s="28" t="n"/>
+      <c r="K184" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L184" s="32" t="n"/>
     </row>
     <row r="185">
@@ -4164,7 +4432,11 @@
       <c r="J188" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="K188" s="28" t="n"/>
+      <c r="K188" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L188" s="32" t="n"/>
     </row>
     <row r="189">
@@ -4180,7 +4452,11 @@
       <c r="J189" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="K189" s="28" t="n"/>
+      <c r="K189" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L189" s="32" t="n"/>
     </row>
     <row r="190">
@@ -4216,7 +4492,11 @@
       <c r="J191" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="K191" s="28" t="n"/>
+      <c r="K191" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L191" s="32" t="n"/>
     </row>
     <row r="192">
@@ -4364,7 +4644,11 @@
       <c r="J199" s="33" t="n">
         <v>724.12</v>
       </c>
-      <c r="K199" s="28" t="n"/>
+      <c r="K199" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L199" s="32" t="n"/>
     </row>
     <row r="200">
@@ -4416,7 +4700,11 @@
       <c r="J202" s="33" t="n">
         <v>1.9</v>
       </c>
-      <c r="K202" s="28" t="n"/>
+      <c r="K202" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L202" s="32" t="n"/>
     </row>
     <row r="203">
@@ -4432,7 +4720,11 @@
       <c r="J203" s="33" t="n">
         <v>1.9</v>
       </c>
-      <c r="K203" s="28" t="n"/>
+      <c r="K203" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L203" s="32" t="n"/>
     </row>
     <row r="204">
@@ -4464,7 +4756,11 @@
       <c r="J205" s="33" t="n">
         <v>5.5</v>
       </c>
-      <c r="K205" s="28" t="n"/>
+      <c r="K205" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L205" s="32" t="n"/>
     </row>
     <row r="206">
@@ -4532,7 +4828,11 @@
       <c r="J209" s="33" t="n">
         <v>2.8</v>
       </c>
-      <c r="K209" s="28" t="n"/>
+      <c r="K209" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L209" s="32" t="n"/>
     </row>
     <row r="210">
@@ -4584,7 +4884,11 @@
       <c r="J212" s="33" t="n">
         <v>3.6</v>
       </c>
-      <c r="K212" s="28" t="n"/>
+      <c r="K212" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L212" s="32" t="n"/>
     </row>
     <row r="213">
@@ -4780,7 +5084,11 @@
       <c r="J224" s="33" t="n">
         <v>1.7</v>
       </c>
-      <c r="K224" s="28" t="n"/>
+      <c r="K224" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L224" s="32" t="n"/>
     </row>
     <row r="225">
@@ -4828,7 +5136,11 @@
       <c r="J227" s="33" t="n">
         <v>724.12</v>
       </c>
-      <c r="K227" s="28" t="n"/>
+      <c r="K227" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L227" s="32" t="n"/>
     </row>
     <row r="228">
@@ -4904,7 +5216,11 @@
       <c r="J231" s="33" t="n">
         <v>5.4</v>
       </c>
-      <c r="K231" s="28" t="n"/>
+      <c r="K231" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L231" s="32" t="inlineStr">
         <is>
           <t>Côte d'Azur (France)</t>
@@ -4924,7 +5240,11 @@
       <c r="J232" s="33" t="n">
         <v>7.5</v>
       </c>
-      <c r="K232" s="28" t="n"/>
+      <c r="K232" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L232" s="32" t="inlineStr">
         <is>
           <t>Côte d'Azur (France)</t>
@@ -4944,7 +5264,11 @@
       <c r="J233" s="33" t="n">
         <v>7.5</v>
       </c>
-      <c r="K233" s="28" t="n"/>
+      <c r="K233" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L233" s="32" t="inlineStr">
         <is>
           <t>Côte d'Azur (France)</t>
@@ -4964,7 +5288,11 @@
       <c r="J234" s="33" t="n">
         <v>9.5</v>
       </c>
-      <c r="K234" s="28" t="n"/>
+      <c r="K234" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L234" s="32" t="inlineStr">
         <is>
           <t>Côte d'Azur (France)</t>
@@ -4984,7 +5312,11 @@
       <c r="J235" s="33" t="n">
         <v>8.5</v>
       </c>
-      <c r="K235" s="28" t="n"/>
+      <c r="K235" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L235" s="32" t="inlineStr">
         <is>
           <t>Côte d'Azur (France)</t>
@@ -5004,7 +5336,11 @@
       <c r="J236" s="33" t="n">
         <v>9</v>
       </c>
-      <c r="K236" s="28" t="n"/>
+      <c r="K236" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L236" s="32" t="n"/>
     </row>
     <row r="237">
@@ -5040,7 +5376,11 @@
       <c r="J238" s="33" t="n">
         <v>19</v>
       </c>
-      <c r="K238" s="28" t="n"/>
+      <c r="K238" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L238" s="32" t="inlineStr">
         <is>
           <t>Côte d'Azur (France)</t>
@@ -5060,7 +5400,11 @@
       <c r="J239" s="33" t="n">
         <v>10.6</v>
       </c>
-      <c r="K239" s="28" t="n"/>
+      <c r="K239" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L239" s="32" t="inlineStr">
         <is>
           <t>Côte d'Azur (France)</t>
@@ -5080,7 +5424,11 @@
       <c r="J240" s="33" t="n">
         <v>6.4</v>
       </c>
-      <c r="K240" s="28" t="n"/>
+      <c r="K240" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L240" s="32" t="inlineStr">
         <is>
           <t>Côte d'Azur (France)</t>
@@ -5100,7 +5448,11 @@
       <c r="J241" s="33" t="n">
         <v>4.2</v>
       </c>
-      <c r="K241" s="28" t="n"/>
+      <c r="K241" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L241" s="32" t="inlineStr">
         <is>
           <t>Côte d'Azur (France)</t>
@@ -5200,7 +5552,11 @@
       <c r="J246" s="33" t="n">
         <v>5.4</v>
       </c>
-      <c r="K246" s="28" t="n"/>
+      <c r="K246" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L246" s="32" t="n"/>
     </row>
     <row r="247">
@@ -5216,7 +5572,11 @@
       <c r="J247" s="33" t="n">
         <v>5.4</v>
       </c>
-      <c r="K247" s="28" t="n"/>
+      <c r="K247" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L247" s="32" t="n"/>
     </row>
     <row r="248">
@@ -5232,7 +5592,11 @@
       <c r="J248" s="33" t="n">
         <v>5.4</v>
       </c>
-      <c r="K248" s="28" t="n"/>
+      <c r="K248" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L248" s="32" t="n"/>
     </row>
     <row r="249">
@@ -5312,7 +5676,11 @@
       <c r="J253" s="33" t="n">
         <v>167.59</v>
       </c>
-      <c r="K253" s="28" t="n"/>
+      <c r="K253" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L253" s="32" t="n"/>
     </row>
     <row r="254">
@@ -5328,7 +5696,11 @@
       <c r="J254" s="33" t="n">
         <v>1.7</v>
       </c>
-      <c r="K254" s="28" t="n"/>
+      <c r="K254" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L254" s="32" t="n"/>
     </row>
     <row r="255">

--- a/Bilan_2026_MTCB.xlsx
+++ b/Bilan_2026_MTCB.xlsx
@@ -766,7 +766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="D1:L257"/>
+  <dimension ref="D1:L255"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="37.42578125" bestFit="1" customWidth="1" min="4" max="4"/>
@@ -1270,20 +1270,20 @@
       <c r="H25" s="32" t="n"/>
       <c r="I25" s="13" t="inlineStr">
         <is>
-          <t>Frais comptable BDH</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="J25" s="33" t="n">
-        <v>1179.75</v>
+        <v>1.6</v>
       </c>
       <c r="K25" s="28" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L25" s="32" t="inlineStr">
         <is>
-          <t>Facture 20250542 — facture 2025 payée en 2026 — Facture BDH en main, chargée dans Billtobox</t>
+          <t>Woluwe-Saint-Lambert</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
         </is>
       </c>
       <c r="J26" s="33" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="K26" s="28" t="inlineStr">
         <is>
@@ -1307,33 +1307,15 @@
       </c>
       <c r="L26" s="32" t="inlineStr">
         <is>
-          <t>Woluwe-Saint-Lambert</t>
+          <t>Schaerbeek</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="E27" s="16" t="n"/>
-      <c r="F27" s="17" t="n"/>
-      <c r="G27" s="31" t="n"/>
-      <c r="H27" s="32" t="n"/>
-      <c r="I27" s="13" t="inlineStr">
-        <is>
-          <t>Parking</t>
-        </is>
-      </c>
-      <c r="J27" s="33" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="K27" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L27" s="32" t="inlineStr">
-        <is>
-          <t>Schaerbeek</t>
-        </is>
-      </c>
+      <c r="G27" s="34" t="n"/>
+      <c r="H27" s="35" t="n"/>
+      <c r="J27" s="34" t="n"/>
+      <c r="L27" s="35" t="n"/>
     </row>
     <row r="28">
       <c r="G28" s="34" t="n"/>
@@ -1342,50 +1324,74 @@
       <c r="L28" s="35" t="n"/>
     </row>
     <row r="29">
-      <c r="G29" s="34" t="n"/>
-      <c r="H29" s="35" t="n"/>
-      <c r="J29" s="34" t="n"/>
-      <c r="L29" s="35" t="n"/>
+      <c r="E29" s="16" t="inlineStr">
+        <is>
+          <t>Février</t>
+        </is>
+      </c>
+      <c r="F29" s="17" t="inlineStr">
+        <is>
+          <t>LAM2601</t>
+        </is>
+      </c>
+      <c r="G29" s="31" t="n">
+        <v>4057.5</v>
+      </c>
+      <c r="H29" s="32" t="n"/>
+      <c r="I29" s="28" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J29" s="36" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K29" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L29" s="32" t="inlineStr">
+        <is>
+          <t>Administration communale, Bruxelles</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="E30" s="16" t="inlineStr">
-        <is>
-          <t>Février</t>
-        </is>
-      </c>
-      <c r="F30" s="17" t="inlineStr">
-        <is>
-          <t>LAM2601</t>
-        </is>
-      </c>
-      <c r="G30" s="31" t="n">
-        <v>4057.5</v>
-      </c>
-      <c r="H30" s="32" t="n"/>
-      <c r="I30" s="28" t="inlineStr">
-        <is>
-          <t>Parking</t>
-        </is>
-      </c>
-      <c r="J30" s="36" t="n">
-        <v>3.7</v>
+      <c r="E30" s="16" t="n"/>
+      <c r="F30" s="37" t="inlineStr">
+        <is>
+          <t>Approvisionnement compte - Thibault Duchène</t>
+        </is>
+      </c>
+      <c r="G30" s="38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H30" s="39" t="inlineStr">
+        <is>
+          <t>Apport du gérant, pas un produit — à traiter en compte courant</t>
+        </is>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>Carburant</t>
+        </is>
+      </c>
+      <c r="J30" s="33" t="n">
+        <v>63.37</v>
       </c>
       <c r="K30" s="28" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="L30" s="32" t="inlineStr">
-        <is>
-          <t>Administration communale, Bruxelles</t>
-        </is>
-      </c>
+      <c r="L30" s="32" t="n"/>
     </row>
     <row r="31">
       <c r="E31" s="16" t="n"/>
       <c r="F31" s="37" t="inlineStr">
         <is>
-          <t>Approvisionnement compte - Thibault Duchène</t>
+          <t>Alimentation du compte - Thibault Duchène</t>
         </is>
       </c>
       <c r="G31" s="38" t="n">
@@ -1398,41 +1404,33 @@
       </c>
       <c r="I31" s="13" t="inlineStr">
         <is>
-          <t>Carburant</t>
+          <t>Précompte salarial janvier 2026 Thibault Duchène</t>
         </is>
       </c>
       <c r="J31" s="33" t="n">
-        <v>63.37</v>
-      </c>
-      <c r="K31" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+        <v>2250</v>
+      </c>
+      <c r="K31" s="28" t="n"/>
       <c r="L31" s="32" t="n"/>
     </row>
     <row r="32">
       <c r="E32" s="16" t="n"/>
-      <c r="F32" s="37" t="inlineStr">
-        <is>
-          <t>Alimentation du compte - Thibault Duchène</t>
-        </is>
-      </c>
-      <c r="G32" s="38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H32" s="39" t="inlineStr">
-        <is>
-          <t>Apport du gérant, pas un produit — à traiter en compte courant</t>
-        </is>
-      </c>
+      <c r="F32" s="17" t="inlineStr">
+        <is>
+          <t>LAM2602</t>
+        </is>
+      </c>
+      <c r="G32" s="31" t="n">
+        <v>5790.15</v>
+      </c>
+      <c r="H32" s="32" t="n"/>
       <c r="I32" s="13" t="inlineStr">
         <is>
-          <t>Précompte salarial janvier 2026 Thibault Duchène</t>
+          <t>SD Worx</t>
         </is>
       </c>
       <c r="J32" s="33" t="n">
-        <v>2250</v>
+        <v>332.49</v>
       </c>
       <c r="K32" s="28" t="n"/>
       <c r="L32" s="32" t="n"/>
@@ -1441,42 +1439,40 @@
       <c r="E33" s="16" t="n"/>
       <c r="F33" s="17" t="inlineStr">
         <is>
-          <t>LAM2602</t>
+          <t>Remboursement contrats Babolat - RTC Lambermont</t>
         </is>
       </c>
       <c r="G33" s="31" t="n">
-        <v>5790.15</v>
+        <v>440</v>
       </c>
       <c r="H33" s="32" t="n"/>
       <c r="I33" s="13" t="inlineStr">
         <is>
-          <t>SD Worx</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="J33" s="33" t="n">
-        <v>332.49</v>
-      </c>
-      <c r="K33" s="28" t="n"/>
+        <v>3.8</v>
+      </c>
+      <c r="K33" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L33" s="32" t="n"/>
     </row>
     <row r="34">
       <c r="E34" s="16" t="n"/>
-      <c r="F34" s="17" t="inlineStr">
-        <is>
-          <t>Remboursement contrats Babolat - RTC Lambermont</t>
-        </is>
-      </c>
-      <c r="G34" s="31" t="n">
-        <v>440</v>
-      </c>
+      <c r="F34" s="17" t="n"/>
+      <c r="G34" s="31" t="n"/>
       <c r="H34" s="32" t="n"/>
       <c r="I34" s="13" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Crédit voiture</t>
         </is>
       </c>
       <c r="J34" s="33" t="n">
-        <v>3.8</v>
+        <v>724.12</v>
       </c>
       <c r="K34" s="28" t="inlineStr">
         <is>
@@ -1492,17 +1488,13 @@
       <c r="H35" s="32" t="n"/>
       <c r="I35" s="13" t="inlineStr">
         <is>
-          <t>Crédit voiture</t>
+          <t>Farys (eau)</t>
         </is>
       </c>
       <c r="J35" s="33" t="n">
-        <v>724.12</v>
-      </c>
-      <c r="K35" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="K35" s="28" t="n"/>
       <c r="L35" s="32" t="n"/>
     </row>
     <row r="36">
@@ -1510,76 +1502,76 @@
       <c r="F36" s="17" t="n"/>
       <c r="G36" s="31" t="n"/>
       <c r="H36" s="32" t="n"/>
-      <c r="I36" s="13" t="inlineStr">
-        <is>
-          <t>Farys (eau)</t>
-        </is>
-      </c>
-      <c r="J36" s="33" t="n">
-        <v>306</v>
+      <c r="I36" s="40" t="inlineStr">
+        <is>
+          <t>Abonnement club David Lloyd</t>
+        </is>
+      </c>
+      <c r="J36" s="41" t="n">
+        <v>1027.75</v>
       </c>
       <c r="K36" s="28" t="n"/>
-      <c r="L36" s="32" t="n"/>
+      <c r="L36" s="39" t="inlineStr">
+        <is>
+          <t>Sterrebeek — usage professionnel à confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="E37" s="16" t="n"/>
       <c r="F37" s="17" t="n"/>
       <c r="G37" s="31" t="n"/>
       <c r="H37" s="32" t="n"/>
-      <c r="I37" s="40" t="inlineStr">
-        <is>
-          <t>Abonnement club David Lloyd</t>
-        </is>
-      </c>
-      <c r="J37" s="41" t="n">
-        <v>1027.75</v>
-      </c>
-      <c r="K37" s="28" t="n"/>
-      <c r="L37" s="39" t="inlineStr">
-        <is>
-          <t>Sterrebeek — usage professionnel à confirmer</t>
-        </is>
-      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J37" s="33" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="K37" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L37" s="32" t="n"/>
     </row>
     <row r="38">
       <c r="E38" s="16" t="n"/>
       <c r="F38" s="17" t="n"/>
       <c r="G38" s="31" t="n"/>
       <c r="H38" s="32" t="n"/>
-      <c r="I38" s="13" t="inlineStr">
-        <is>
-          <t>Parking</t>
-        </is>
-      </c>
-      <c r="J38" s="33" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="K38" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L38" s="32" t="n"/>
+      <c r="I38" s="40" t="inlineStr">
+        <is>
+          <t>Abonnement club David Lloyd</t>
+        </is>
+      </c>
+      <c r="J38" s="41" t="n">
+        <v>1061</v>
+      </c>
+      <c r="K38" s="28" t="n"/>
+      <c r="L38" s="39" t="inlineStr">
+        <is>
+          <t>Sterrebeek — usage professionnel à confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="E39" s="16" t="n"/>
       <c r="F39" s="17" t="n"/>
       <c r="G39" s="31" t="n"/>
       <c r="H39" s="32" t="n"/>
-      <c r="I39" s="40" t="inlineStr">
-        <is>
-          <t>Abonnement club David Lloyd</t>
-        </is>
-      </c>
-      <c r="J39" s="41" t="n">
-        <v>1061</v>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>Electrabel</t>
+        </is>
+      </c>
+      <c r="J39" s="33" t="n">
+        <v>263.44</v>
       </c>
       <c r="K39" s="28" t="n"/>
-      <c r="L39" s="39" t="inlineStr">
-        <is>
-          <t>Sterrebeek — usage professionnel à confirmer</t>
-        </is>
-      </c>
+      <c r="L39" s="32" t="n"/>
     </row>
     <row r="40">
       <c r="E40" s="16" t="n"/>
@@ -1588,13 +1580,17 @@
       <c r="H40" s="32" t="n"/>
       <c r="I40" s="13" t="inlineStr">
         <is>
-          <t>Electrabel</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="J40" s="33" t="n">
-        <v>263.44</v>
-      </c>
-      <c r="K40" s="28" t="n"/>
+        <v>3.8</v>
+      </c>
+      <c r="K40" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L40" s="32" t="n"/>
     </row>
     <row r="41">
@@ -1604,13 +1600,17 @@
       <c r="H41" s="32" t="n"/>
       <c r="I41" s="13" t="inlineStr">
         <is>
-          <t>Réception marchandise - FEDEX</t>
+          <t>Carburant</t>
         </is>
       </c>
       <c r="J41" s="33" t="n">
-        <v>11.84</v>
-      </c>
-      <c r="K41" s="28" t="n"/>
+        <v>64.23999999999999</v>
+      </c>
+      <c r="K41" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L41" s="32" t="n"/>
     </row>
     <row r="42">
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="J42" s="33" t="n">
-        <v>3.8</v>
+        <v>7.6</v>
       </c>
       <c r="K42" s="28" t="inlineStr">
         <is>
@@ -1640,11 +1640,11 @@
       <c r="H43" s="32" t="n"/>
       <c r="I43" s="13" t="inlineStr">
         <is>
-          <t>Carburant</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="J43" s="33" t="n">
-        <v>64.23999999999999</v>
+        <v>1.9</v>
       </c>
       <c r="K43" s="28" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         </is>
       </c>
       <c r="J44" s="33" t="n">
-        <v>7.6</v>
+        <v>3.4</v>
       </c>
       <c r="K44" s="28" t="inlineStr">
         <is>
@@ -1680,11 +1680,11 @@
       <c r="H45" s="32" t="n"/>
       <c r="I45" s="13" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Carburant</t>
         </is>
       </c>
       <c r="J45" s="33" t="n">
-        <v>1.9</v>
+        <v>63.63</v>
       </c>
       <c r="K45" s="28" t="inlineStr">
         <is>
@@ -1700,17 +1700,13 @@
       <c r="H46" s="32" t="n"/>
       <c r="I46" s="13" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Péage autoroute France</t>
         </is>
       </c>
       <c r="J46" s="33" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K46" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="K46" s="28" t="n"/>
       <c r="L46" s="32" t="n"/>
     </row>
     <row r="47">
@@ -1720,18 +1716,18 @@
       <c r="H47" s="32" t="n"/>
       <c r="I47" s="13" t="inlineStr">
         <is>
-          <t>Carburant</t>
+          <t>Consommation - SV Victoria</t>
         </is>
       </c>
       <c r="J47" s="33" t="n">
-        <v>63.63</v>
-      </c>
-      <c r="K47" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L47" s="32" t="n"/>
+        <v>16.5</v>
+      </c>
+      <c r="K47" s="28" t="n"/>
+      <c r="L47" s="32" t="inlineStr">
+        <is>
+          <t>Rotterdam (Pays-Bas)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="E48" s="16" t="n"/>
@@ -1740,14 +1736,18 @@
       <c r="H48" s="32" t="n"/>
       <c r="I48" s="13" t="inlineStr">
         <is>
-          <t>Péage autoroute France</t>
+          <t>Consommation - SV Victoria</t>
         </is>
       </c>
       <c r="J48" s="33" t="n">
-        <v>42</v>
+        <v>4.45</v>
       </c>
       <c r="K48" s="28" t="n"/>
-      <c r="L48" s="32" t="n"/>
+      <c r="L48" s="32" t="inlineStr">
+        <is>
+          <t>Rotterdam (Pays-Bas)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="E49" s="16" t="n"/>
@@ -1756,18 +1756,18 @@
       <c r="H49" s="32" t="n"/>
       <c r="I49" s="13" t="inlineStr">
         <is>
-          <t>Consommation - SV Victoria</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="J49" s="33" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="K49" s="28" t="n"/>
-      <c r="L49" s="32" t="inlineStr">
-        <is>
-          <t>Rotterdam (Pays-Bas)</t>
-        </is>
-      </c>
+        <v>8.1</v>
+      </c>
+      <c r="K49" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L49" s="32" t="n"/>
     </row>
     <row r="50">
       <c r="E50" s="16" t="n"/>
@@ -1776,18 +1776,14 @@
       <c r="H50" s="32" t="n"/>
       <c r="I50" s="13" t="inlineStr">
         <is>
-          <t>Consommation - SV Victoria</t>
+          <t>Achat vêtements sport - NIKE</t>
         </is>
       </c>
       <c r="J50" s="33" t="n">
-        <v>4.45</v>
+        <v>230.48</v>
       </c>
       <c r="K50" s="28" t="n"/>
-      <c r="L50" s="32" t="inlineStr">
-        <is>
-          <t>Rotterdam (Pays-Bas)</t>
-        </is>
-      </c>
+      <c r="L50" s="32" t="n"/>
     </row>
     <row r="51">
       <c r="E51" s="16" t="n"/>
@@ -1796,17 +1792,13 @@
       <c r="H51" s="32" t="n"/>
       <c r="I51" s="13" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Achat vêtements sport - Sportsdirect</t>
         </is>
       </c>
       <c r="J51" s="33" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="K51" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="K51" s="28" t="n"/>
       <c r="L51" s="32" t="n"/>
     </row>
     <row r="52">
@@ -1816,13 +1808,17 @@
       <c r="H52" s="32" t="n"/>
       <c r="I52" s="13" t="inlineStr">
         <is>
-          <t>Achat vêtements sport - NIKE</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="J52" s="33" t="n">
-        <v>230.48</v>
-      </c>
-      <c r="K52" s="28" t="n"/>
+        <v>3.4</v>
+      </c>
+      <c r="K52" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L52" s="32" t="n"/>
     </row>
     <row r="53">
@@ -1832,13 +1828,17 @@
       <c r="H53" s="32" t="n"/>
       <c r="I53" s="13" t="inlineStr">
         <is>
-          <t>Achat vêtements sport - Sportsdirect</t>
+          <t>Carburant</t>
         </is>
       </c>
       <c r="J53" s="33" t="n">
-        <v>112</v>
-      </c>
-      <c r="K53" s="28" t="n"/>
+        <v>62.54</v>
+      </c>
+      <c r="K53" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L53" s="32" t="n"/>
     </row>
     <row r="54">
@@ -1852,7 +1852,7 @@
         </is>
       </c>
       <c r="J54" s="33" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="K54" s="28" t="inlineStr">
         <is>
@@ -1868,17 +1868,13 @@
       <c r="H55" s="32" t="n"/>
       <c r="I55" s="13" t="inlineStr">
         <is>
-          <t>Carburant</t>
+          <t>Précompte salarial fevrier 2026 Thibault Duchène</t>
         </is>
       </c>
       <c r="J55" s="33" t="n">
-        <v>62.54</v>
-      </c>
-      <c r="K55" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+        <v>2250</v>
+      </c>
+      <c r="K55" s="28" t="n"/>
       <c r="L55" s="32" t="n"/>
     </row>
     <row r="56">
@@ -1888,17 +1884,13 @@
       <c r="H56" s="32" t="n"/>
       <c r="I56" s="13" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>SD Worx</t>
         </is>
       </c>
       <c r="J56" s="33" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K56" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+        <v>332.49</v>
+      </c>
+      <c r="K56" s="28" t="n"/>
       <c r="L56" s="32" t="n"/>
     </row>
     <row r="57">
@@ -1908,111 +1900,131 @@
       <c r="H57" s="32" t="n"/>
       <c r="I57" s="13" t="inlineStr">
         <is>
-          <t>Précompte salarial fevrier 2026 Thibault Duchène</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="J57" s="33" t="n">
-        <v>2250</v>
-      </c>
-      <c r="K57" s="28" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="K57" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L57" s="32" t="n"/>
     </row>
     <row r="58">
-      <c r="E58" s="16" t="n"/>
-      <c r="F58" s="17" t="n"/>
-      <c r="G58" s="31" t="n"/>
-      <c r="H58" s="32" t="n"/>
-      <c r="I58" s="13" t="inlineStr">
-        <is>
-          <t>SD Worx</t>
-        </is>
-      </c>
-      <c r="J58" s="33" t="n">
-        <v>332.49</v>
-      </c>
-      <c r="K58" s="28" t="n"/>
-      <c r="L58" s="32" t="n"/>
+      <c r="G58" s="34" t="n"/>
+      <c r="H58" s="35" t="n"/>
+      <c r="J58" s="34" t="n"/>
+      <c r="L58" s="35" t="n"/>
     </row>
     <row r="59">
-      <c r="E59" s="16" t="n"/>
-      <c r="F59" s="17" t="n"/>
-      <c r="G59" s="31" t="n"/>
-      <c r="H59" s="32" t="n"/>
-      <c r="I59" s="13" t="inlineStr">
-        <is>
-          <t>Parking</t>
-        </is>
-      </c>
-      <c r="J59" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="K59" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L59" s="32" t="n"/>
+      <c r="G59" s="34" t="n"/>
+      <c r="H59" s="35" t="n"/>
+      <c r="J59" s="34" t="n"/>
+      <c r="L59" s="35" t="n"/>
     </row>
     <row r="60">
-      <c r="G60" s="34" t="n"/>
-      <c r="H60" s="35" t="n"/>
-      <c r="J60" s="34" t="n"/>
-      <c r="L60" s="35" t="n"/>
+      <c r="E60" s="16" t="inlineStr">
+        <is>
+          <t>Mars</t>
+        </is>
+      </c>
+      <c r="F60" s="37" t="inlineStr">
+        <is>
+          <t>Dépôt d'espèces</t>
+        </is>
+      </c>
+      <c r="G60" s="38" t="n">
+        <v>2600</v>
+      </c>
+      <c r="H60" s="39" t="inlineStr">
+        <is>
+          <t>Versement au distributeur, communication « PAIEMENTS » — origine des fonds à documenter</t>
+        </is>
+      </c>
+      <c r="I60" s="28" t="inlineStr">
+        <is>
+          <t>Achat vêtements sport - NIKE</t>
+        </is>
+      </c>
+      <c r="J60" s="36" t="n">
+        <v>130.46</v>
+      </c>
+      <c r="K60" s="28" t="n"/>
+      <c r="L60" s="32" t="n"/>
     </row>
     <row r="61">
-      <c r="G61" s="34" t="n"/>
-      <c r="H61" s="35" t="n"/>
-      <c r="J61" s="34" t="n"/>
-      <c r="L61" s="35" t="n"/>
+      <c r="E61" s="16" t="n"/>
+      <c r="F61" s="17" t="inlineStr">
+        <is>
+          <t>Remboursement hôtel Imola - Thibault Duchène</t>
+        </is>
+      </c>
+      <c r="G61" s="31" t="n">
+        <v>364.5</v>
+      </c>
+      <c r="H61" s="32" t="n"/>
+      <c r="I61" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J61" s="33" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K61" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L61" s="32" t="n"/>
     </row>
     <row r="62">
-      <c r="E62" s="16" t="inlineStr">
-        <is>
-          <t>Mars</t>
-        </is>
-      </c>
-      <c r="F62" s="37" t="inlineStr">
-        <is>
-          <t>Dépôt d'espèces</t>
-        </is>
-      </c>
-      <c r="G62" s="38" t="n">
-        <v>2600</v>
-      </c>
-      <c r="H62" s="39" t="inlineStr">
-        <is>
-          <t>Versement au distributeur, communication « PAIEMENTS » — origine des fonds à documenter</t>
-        </is>
-      </c>
-      <c r="I62" s="28" t="inlineStr">
-        <is>
-          <t>Achat vêtements sport - NIKE</t>
-        </is>
-      </c>
-      <c r="J62" s="36" t="n">
-        <v>130.46</v>
-      </c>
-      <c r="K62" s="28" t="n"/>
+      <c r="E62" s="16" t="n"/>
+      <c r="F62" s="17" t="inlineStr">
+        <is>
+          <t>Remboursement billet de train Bologne - Thibault Duchène</t>
+        </is>
+      </c>
+      <c r="G62" s="31" t="n">
+        <v>197.3</v>
+      </c>
+      <c r="H62" s="32" t="n"/>
+      <c r="I62" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J62" s="33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K62" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L62" s="32" t="n"/>
     </row>
     <row r="63">
       <c r="E63" s="16" t="n"/>
       <c r="F63" s="17" t="inlineStr">
         <is>
-          <t>Remboursement hôtel Imola - Thibault Duchène</t>
+          <t>LAM2603</t>
         </is>
       </c>
       <c r="G63" s="31" t="n">
-        <v>364.5</v>
+        <v>4110</v>
       </c>
       <c r="H63" s="32" t="n"/>
       <c r="I63" s="13" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Carburant</t>
         </is>
       </c>
       <c r="J63" s="33" t="n">
-        <v>4.5</v>
+        <v>64.62</v>
       </c>
       <c r="K63" s="28" t="inlineStr">
         <is>
@@ -2023,22 +2035,16 @@
     </row>
     <row r="64">
       <c r="E64" s="16" t="n"/>
-      <c r="F64" s="17" t="inlineStr">
-        <is>
-          <t>Remboursement billet de train Bologne - Thibault Duchène</t>
-        </is>
-      </c>
-      <c r="G64" s="31" t="n">
-        <v>197.3</v>
-      </c>
+      <c r="F64" s="17" t="n"/>
+      <c r="G64" s="31" t="n"/>
       <c r="H64" s="32" t="n"/>
       <c r="I64" s="13" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Crédit voiture</t>
         </is>
       </c>
       <c r="J64" s="33" t="n">
-        <v>1.7</v>
+        <v>724.12</v>
       </c>
       <c r="K64" s="28" t="inlineStr">
         <is>
@@ -2049,22 +2055,16 @@
     </row>
     <row r="65">
       <c r="E65" s="16" t="n"/>
-      <c r="F65" s="17" t="inlineStr">
-        <is>
-          <t>LAM2603</t>
-        </is>
-      </c>
-      <c r="G65" s="31" t="n">
-        <v>4110</v>
-      </c>
+      <c r="F65" s="17" t="n"/>
+      <c r="G65" s="31" t="n"/>
       <c r="H65" s="32" t="n"/>
       <c r="I65" s="13" t="inlineStr">
         <is>
-          <t>Carburant</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="J65" s="33" t="n">
-        <v>64.62</v>
+        <v>5.7</v>
       </c>
       <c r="K65" s="28" t="inlineStr">
         <is>
@@ -2080,17 +2080,13 @@
       <c r="H66" s="32" t="n"/>
       <c r="I66" s="13" t="inlineStr">
         <is>
-          <t>Crédit voiture</t>
+          <t>Partena</t>
         </is>
       </c>
       <c r="J66" s="33" t="n">
-        <v>724.12</v>
-      </c>
-      <c r="K66" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+        <v>1747.34</v>
+      </c>
+      <c r="K66" s="28" t="n"/>
       <c r="L66" s="32" t="n"/>
     </row>
     <row r="67">
@@ -2100,17 +2096,13 @@
       <c r="H67" s="32" t="n"/>
       <c r="I67" s="13" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Partena</t>
         </is>
       </c>
       <c r="J67" s="33" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="K67" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+        <v>935.96</v>
+      </c>
+      <c r="K67" s="28" t="n"/>
       <c r="L67" s="32" t="n"/>
     </row>
     <row r="68">
@@ -2120,11 +2112,11 @@
       <c r="H68" s="32" t="n"/>
       <c r="I68" s="13" t="inlineStr">
         <is>
-          <t>Partena</t>
+          <t>Proximus</t>
         </is>
       </c>
       <c r="J68" s="33" t="n">
-        <v>1747.34</v>
+        <v>293.82</v>
       </c>
       <c r="K68" s="28" t="n"/>
       <c r="L68" s="32" t="n"/>
@@ -2136,11 +2128,11 @@
       <c r="H69" s="32" t="n"/>
       <c r="I69" s="13" t="inlineStr">
         <is>
-          <t>Partena</t>
+          <t>Electrabel</t>
         </is>
       </c>
       <c r="J69" s="33" t="n">
-        <v>935.96</v>
+        <v>263.44</v>
       </c>
       <c r="K69" s="28" t="n"/>
       <c r="L69" s="32" t="n"/>
@@ -2152,13 +2144,17 @@
       <c r="H70" s="32" t="n"/>
       <c r="I70" s="13" t="inlineStr">
         <is>
-          <t>Proximus</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="J70" s="33" t="n">
-        <v>293.82</v>
-      </c>
-      <c r="K70" s="28" t="n"/>
+        <v>3.4</v>
+      </c>
+      <c r="K70" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L70" s="32" t="n"/>
     </row>
     <row r="71">
@@ -2168,13 +2164,17 @@
       <c r="H71" s="32" t="n"/>
       <c r="I71" s="13" t="inlineStr">
         <is>
-          <t>Electrabel</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="J71" s="33" t="n">
-        <v>263.44</v>
-      </c>
-      <c r="K71" s="28" t="n"/>
+        <v>1.7</v>
+      </c>
+      <c r="K71" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L71" s="32" t="n"/>
     </row>
     <row r="72">
@@ -2184,18 +2184,18 @@
       <c r="H72" s="32" t="n"/>
       <c r="I72" s="13" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Remboursement alimentation du compte - Thibault Duchène</t>
         </is>
       </c>
       <c r="J72" s="33" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K72" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L72" s="32" t="n"/>
+        <v>750</v>
+      </c>
+      <c r="K72" s="28" t="n"/>
+      <c r="L72" s="32" t="inlineStr">
+        <is>
+          <t>Restitution des apports de février 2026</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="E73" s="16" t="n"/>
@@ -2204,11 +2204,11 @@
       <c r="H73" s="32" t="n"/>
       <c r="I73" s="13" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Carburant</t>
         </is>
       </c>
       <c r="J73" s="33" t="n">
-        <v>1.7</v>
+        <v>76.45</v>
       </c>
       <c r="K73" s="28" t="inlineStr">
         <is>
@@ -2224,18 +2224,14 @@
       <c r="H74" s="32" t="n"/>
       <c r="I74" s="13" t="inlineStr">
         <is>
-          <t>Remboursement alimentation du compte - Thibault Duchène</t>
+          <t>Paiement carte de crédit</t>
         </is>
       </c>
       <c r="J74" s="33" t="n">
-        <v>750</v>
+        <v>1104.46</v>
       </c>
       <c r="K74" s="28" t="n"/>
-      <c r="L74" s="32" t="inlineStr">
-        <is>
-          <t>Restitution des apports de février 2026</t>
-        </is>
-      </c>
+      <c r="L74" s="32" t="n"/>
     </row>
     <row r="75">
       <c r="E75" s="16" t="n"/>
@@ -2244,11 +2240,11 @@
       <c r="H75" s="32" t="n"/>
       <c r="I75" s="13" t="inlineStr">
         <is>
-          <t>Carburant</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="J75" s="33" t="n">
-        <v>76.45</v>
+        <v>3.4</v>
       </c>
       <c r="K75" s="28" t="inlineStr">
         <is>
@@ -2264,13 +2260,17 @@
       <c r="H76" s="32" t="n"/>
       <c r="I76" s="13" t="inlineStr">
         <is>
-          <t>Paiement carte de crédit</t>
+          <t>Carburant</t>
         </is>
       </c>
       <c r="J76" s="33" t="n">
-        <v>1104.46</v>
-      </c>
-      <c r="K76" s="28" t="n"/>
+        <v>65.54000000000001</v>
+      </c>
+      <c r="K76" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L76" s="32" t="n"/>
     </row>
     <row r="77">
@@ -2284,7 +2284,7 @@
         </is>
       </c>
       <c r="J77" s="33" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="K77" s="28" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="J78" s="33" t="n">
-        <v>65.54000000000001</v>
+        <v>63.82</v>
       </c>
       <c r="K78" s="28" t="inlineStr">
         <is>
@@ -2324,14 +2324,18 @@
         </is>
       </c>
       <c r="J79" s="33" t="n">
-        <v>2.3</v>
+        <v>9</v>
       </c>
       <c r="K79" s="28" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="L79" s="32" t="n"/>
+      <c r="L79" s="32" t="inlineStr">
+        <is>
+          <t>Düsseldorf (Allemagne)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="E80" s="16" t="n"/>
@@ -2340,18 +2344,22 @@
       <c r="H80" s="32" t="n"/>
       <c r="I80" s="13" t="inlineStr">
         <is>
-          <t>Carburant</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="J80" s="33" t="n">
-        <v>63.82</v>
+        <v>10</v>
       </c>
       <c r="K80" s="28" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="L80" s="32" t="n"/>
+      <c r="L80" s="32" t="inlineStr">
+        <is>
+          <t>Düsseldorf (Allemagne)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="E81" s="16" t="n"/>
@@ -2360,44 +2368,40 @@
       <c r="H81" s="32" t="n"/>
       <c r="I81" s="13" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Carburant</t>
         </is>
       </c>
       <c r="J81" s="33" t="n">
-        <v>9</v>
+        <v>84.56</v>
       </c>
       <c r="K81" s="28" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="L81" s="32" t="inlineStr">
-        <is>
-          <t>Düsseldorf (Allemagne)</t>
-        </is>
-      </c>
+      <c r="L81" s="32" t="n"/>
     </row>
     <row r="82">
       <c r="E82" s="16" t="n"/>
       <c r="F82" s="17" t="n"/>
       <c r="G82" s="31" t="n"/>
       <c r="H82" s="32" t="n"/>
-      <c r="I82" s="13" t="inlineStr">
-        <is>
-          <t>Parking</t>
-        </is>
-      </c>
-      <c r="J82" s="33" t="n">
-        <v>10</v>
+      <c r="I82" s="40" t="inlineStr">
+        <is>
+          <t>Parking - Chirec</t>
+        </is>
+      </c>
+      <c r="J82" s="41" t="n">
+        <v>7.8</v>
       </c>
       <c r="K82" s="28" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="L82" s="32" t="inlineStr">
-        <is>
-          <t>Düsseldorf (Allemagne)</t>
+      <c r="L82" s="39" t="inlineStr">
+        <is>
+          <t>Hôpital, Bruxelles — à confirmer</t>
         </is>
       </c>
     </row>
@@ -2408,11 +2412,11 @@
       <c r="H83" s="32" t="n"/>
       <c r="I83" s="13" t="inlineStr">
         <is>
-          <t>Carburant</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="J83" s="33" t="n">
-        <v>84.56</v>
+        <v>2.1</v>
       </c>
       <c r="K83" s="28" t="inlineStr">
         <is>
@@ -2426,44 +2430,36 @@
       <c r="F84" s="17" t="n"/>
       <c r="G84" s="31" t="n"/>
       <c r="H84" s="32" t="n"/>
-      <c r="I84" s="40" t="inlineStr">
-        <is>
-          <t>Parking - Chirec</t>
-        </is>
-      </c>
-      <c r="J84" s="41" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="K84" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L84" s="39" t="inlineStr">
-        <is>
-          <t>Hôpital, Bruxelles — à confirmer</t>
-        </is>
-      </c>
+      <c r="I84" s="13" t="inlineStr">
+        <is>
+          <t>Précompte salarial mars 2026 Thibault Duchène</t>
+        </is>
+      </c>
+      <c r="J84" s="33" t="n">
+        <v>2250</v>
+      </c>
+      <c r="K84" s="28" t="n"/>
+      <c r="L84" s="32" t="n"/>
     </row>
     <row r="85">
       <c r="E85" s="16" t="n"/>
       <c r="F85" s="17" t="n"/>
       <c r="G85" s="31" t="n"/>
       <c r="H85" s="32" t="n"/>
-      <c r="I85" s="13" t="inlineStr">
-        <is>
-          <t>Parking</t>
-        </is>
-      </c>
-      <c r="J85" s="33" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="K85" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L85" s="32" t="n"/>
+      <c r="I85" s="40" t="inlineStr">
+        <is>
+          <t>Achat - Berca</t>
+        </is>
+      </c>
+      <c r="J85" s="41" t="n">
+        <v>38.97</v>
+      </c>
+      <c r="K85" s="28" t="n"/>
+      <c r="L85" s="39" t="inlineStr">
+        <is>
+          <t>Ardooie — à identifier</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="E86" s="16" t="n"/>
@@ -2472,32 +2468,44 @@
       <c r="H86" s="32" t="n"/>
       <c r="I86" s="13" t="inlineStr">
         <is>
-          <t>Précompte salarial mars 2026 Thibault Duchène</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="J86" s="33" t="n">
-        <v>2250</v>
-      </c>
-      <c r="K86" s="28" t="n"/>
-      <c r="L86" s="32" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="K86" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L86" s="32" t="inlineStr">
+        <is>
+          <t>Italie</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="E87" s="16" t="n"/>
       <c r="F87" s="17" t="n"/>
       <c r="G87" s="31" t="n"/>
       <c r="H87" s="32" t="n"/>
-      <c r="I87" s="40" t="inlineStr">
-        <is>
-          <t>Achat - Berca</t>
-        </is>
-      </c>
-      <c r="J87" s="41" t="n">
-        <v>38.97</v>
-      </c>
-      <c r="K87" s="28" t="n"/>
-      <c r="L87" s="39" t="inlineStr">
-        <is>
-          <t>Ardooie — à identifier</t>
+      <c r="I87" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J87" s="33" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="K87" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L87" s="32" t="inlineStr">
+        <is>
+          <t>Italie</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2520,7 @@
         </is>
       </c>
       <c r="J88" s="33" t="n">
-        <v>6</v>
+        <v>9.25</v>
       </c>
       <c r="K88" s="28" t="inlineStr">
         <is>
@@ -2532,20 +2540,16 @@
       <c r="H89" s="32" t="n"/>
       <c r="I89" s="13" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Remboursement alimentation du compte - Thibault Duchène</t>
         </is>
       </c>
       <c r="J89" s="33" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="K89" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+        <v>750</v>
+      </c>
+      <c r="K89" s="28" t="n"/>
       <c r="L89" s="32" t="inlineStr">
         <is>
-          <t>Italie</t>
+          <t>Restitution des apports de février 2026</t>
         </is>
       </c>
     </row>
@@ -2556,22 +2560,14 @@
       <c r="H90" s="32" t="n"/>
       <c r="I90" s="13" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>SD Worx</t>
         </is>
       </c>
       <c r="J90" s="33" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="K90" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L90" s="32" t="inlineStr">
-        <is>
-          <t>Italie</t>
-        </is>
-      </c>
+        <v>332.49</v>
+      </c>
+      <c r="K90" s="28" t="n"/>
+      <c r="L90" s="32" t="n"/>
     </row>
     <row r="91">
       <c r="E91" s="16" t="n"/>
@@ -2580,16 +2576,20 @@
       <c r="H91" s="32" t="n"/>
       <c r="I91" s="13" t="inlineStr">
         <is>
-          <t>Remboursement alimentation du compte - Thibault Duchène</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="J91" s="33" t="n">
-        <v>750</v>
-      </c>
-      <c r="K91" s="28" t="n"/>
+        <v>36.5</v>
+      </c>
+      <c r="K91" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L91" s="32" t="inlineStr">
         <is>
-          <t>Restitution des apports de février 2026</t>
+          <t>Italie</t>
         </is>
       </c>
     </row>
@@ -2600,131 +2600,139 @@
       <c r="H92" s="32" t="n"/>
       <c r="I92" s="13" t="inlineStr">
         <is>
-          <t>SD Worx</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="J92" s="33" t="n">
-        <v>332.49</v>
-      </c>
-      <c r="K92" s="28" t="n"/>
-      <c r="L92" s="32" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="K92" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L92" s="32" t="inlineStr">
+        <is>
+          <t>Italie</t>
+        </is>
+      </c>
     </row>
     <row r="93">
-      <c r="E93" s="16" t="n"/>
-      <c r="F93" s="17" t="n"/>
-      <c r="G93" s="31" t="n"/>
-      <c r="H93" s="32" t="n"/>
-      <c r="I93" s="13" t="inlineStr">
-        <is>
-          <t>Parking</t>
-        </is>
-      </c>
-      <c r="J93" s="33" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="K93" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L93" s="32" t="inlineStr">
+      <c r="G93" s="34" t="n"/>
+      <c r="H93" s="35" t="n"/>
+      <c r="J93" s="34" t="n"/>
+      <c r="L93" s="35" t="n"/>
+    </row>
+    <row r="94">
+      <c r="G94" s="34" t="n"/>
+      <c r="H94" s="35" t="n"/>
+      <c r="J94" s="34" t="n"/>
+      <c r="L94" s="35" t="n"/>
+    </row>
+    <row r="95">
+      <c r="E95" s="16" t="inlineStr">
+        <is>
+          <t>Avril</t>
+        </is>
+      </c>
+      <c r="F95" s="17" t="inlineStr">
+        <is>
+          <t>LAM2604</t>
+        </is>
+      </c>
+      <c r="G95" s="31" t="n">
+        <v>7000</v>
+      </c>
+      <c r="H95" s="32" t="n"/>
+      <c r="I95" s="28" t="inlineStr">
+        <is>
+          <t>Carburant</t>
+        </is>
+      </c>
+      <c r="J95" s="36" t="n">
+        <v>64.48</v>
+      </c>
+      <c r="K95" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L95" s="32" t="inlineStr">
+        <is>
+          <t>ENI (Italie)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="E96" s="16" t="n"/>
+      <c r="F96" s="17" t="inlineStr">
+        <is>
+          <t>Remboursement d'impôt - SPF Finances</t>
+        </is>
+      </c>
+      <c r="G96" s="31" t="n">
+        <v>2349.66</v>
+      </c>
+      <c r="H96" s="32" t="inlineStr">
+        <is>
+          <t>Rôle 0867847943</t>
+        </is>
+      </c>
+      <c r="I96" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J96" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="K96" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L96" s="32" t="inlineStr">
         <is>
           <t>Italie</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="E94" s="16" t="n"/>
-      <c r="F94" s="17" t="n"/>
-      <c r="G94" s="31" t="n"/>
-      <c r="H94" s="32" t="n"/>
-      <c r="I94" s="13" t="inlineStr">
-        <is>
-          <t>Parking</t>
-        </is>
-      </c>
-      <c r="J94" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K94" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L94" s="32" t="inlineStr">
+    <row r="97">
+      <c r="E97" s="16" t="n"/>
+      <c r="F97" s="17" t="n"/>
+      <c r="G97" s="31" t="n"/>
+      <c r="H97" s="32" t="n"/>
+      <c r="I97" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J97" s="33" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K97" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L97" s="32" t="inlineStr">
         <is>
           <t>Italie</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="G95" s="34" t="n"/>
-      <c r="H95" s="35" t="n"/>
-      <c r="J95" s="34" t="n"/>
-      <c r="L95" s="35" t="n"/>
-    </row>
-    <row r="96">
-      <c r="G96" s="34" t="n"/>
-      <c r="H96" s="35" t="n"/>
-      <c r="J96" s="34" t="n"/>
-      <c r="L96" s="35" t="n"/>
-    </row>
-    <row r="97">
-      <c r="E97" s="16" t="inlineStr">
-        <is>
-          <t>Avril</t>
-        </is>
-      </c>
-      <c r="F97" s="17" t="inlineStr">
-        <is>
-          <t>LAM2604</t>
-        </is>
-      </c>
-      <c r="G97" s="31" t="n">
-        <v>7000</v>
-      </c>
-      <c r="H97" s="32" t="n"/>
-      <c r="I97" s="28" t="inlineStr">
-        <is>
-          <t>Carburant</t>
-        </is>
-      </c>
-      <c r="J97" s="36" t="n">
-        <v>64.48</v>
-      </c>
-      <c r="K97" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L97" s="32" t="inlineStr">
-        <is>
-          <t>ENI (Italie)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="E98" s="16" t="n"/>
-      <c r="F98" s="17" t="inlineStr">
-        <is>
-          <t>Remboursement d'impôt - SPF Finances</t>
-        </is>
-      </c>
-      <c r="G98" s="31" t="n">
-        <v>2349.66</v>
-      </c>
-      <c r="H98" s="32" t="inlineStr">
-        <is>
-          <t>Rôle 0867847943</t>
-        </is>
-      </c>
+      <c r="F98" s="17" t="n"/>
+      <c r="G98" s="31" t="n"/>
+      <c r="H98" s="32" t="n"/>
       <c r="I98" s="13" t="inlineStr">
         <is>
           <t>Parking</t>
         </is>
       </c>
       <c r="J98" s="33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K98" s="28" t="inlineStr">
         <is>
@@ -2748,7 +2756,7 @@
         </is>
       </c>
       <c r="J99" s="33" t="n">
-        <v>5.5</v>
+        <v>2</v>
       </c>
       <c r="K99" s="28" t="inlineStr">
         <is>
@@ -2772,7 +2780,7 @@
         </is>
       </c>
       <c r="J100" s="33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K100" s="28" t="inlineStr">
         <is>
@@ -2816,11 +2824,11 @@
       <c r="H102" s="32" t="n"/>
       <c r="I102" s="13" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Carburant</t>
         </is>
       </c>
       <c r="J102" s="33" t="n">
-        <v>6</v>
+        <v>76.5</v>
       </c>
       <c r="K102" s="28" t="inlineStr">
         <is>
@@ -2829,7 +2837,7 @@
       </c>
       <c r="L102" s="32" t="inlineStr">
         <is>
-          <t>Italie</t>
+          <t>ENI (Italie)</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2852,7 @@
         </is>
       </c>
       <c r="J103" s="33" t="n">
-        <v>2</v>
+        <v>39.5</v>
       </c>
       <c r="K103" s="28" t="inlineStr">
         <is>
@@ -2864,22 +2872,18 @@
       <c r="H104" s="32" t="n"/>
       <c r="I104" s="13" t="inlineStr">
         <is>
-          <t>Carburant</t>
+          <t>Crédit voiture</t>
         </is>
       </c>
       <c r="J104" s="33" t="n">
-        <v>76.5</v>
+        <v>724.12</v>
       </c>
       <c r="K104" s="28" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="L104" s="32" t="inlineStr">
-        <is>
-          <t>ENI (Italie)</t>
-        </is>
-      </c>
+      <c r="L104" s="32" t="n"/>
     </row>
     <row r="105">
       <c r="E105" s="16" t="n"/>
@@ -2888,22 +2892,14 @@
       <c r="H105" s="32" t="n"/>
       <c r="I105" s="13" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Proximus</t>
         </is>
       </c>
       <c r="J105" s="33" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="K105" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L105" s="32" t="inlineStr">
-        <is>
-          <t>Italie</t>
-        </is>
-      </c>
+        <v>264.52</v>
+      </c>
+      <c r="K105" s="28" t="n"/>
+      <c r="L105" s="32" t="n"/>
     </row>
     <row r="106">
       <c r="E106" s="16" t="n"/>
@@ -2912,18 +2908,18 @@
       <c r="H106" s="32" t="n"/>
       <c r="I106" s="13" t="inlineStr">
         <is>
-          <t>Crédit voiture</t>
+          <t>Lavage voiture</t>
         </is>
       </c>
       <c r="J106" s="33" t="n">
-        <v>724.12</v>
-      </c>
-      <c r="K106" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L106" s="32" t="n"/>
+        <v>34</v>
+      </c>
+      <c r="K106" s="28" t="n"/>
+      <c r="L106" s="32" t="inlineStr">
+        <is>
+          <t>Wash Time Tervuren</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="E107" s="16" t="n"/>
@@ -2932,13 +2928,17 @@
       <c r="H107" s="32" t="n"/>
       <c r="I107" s="13" t="inlineStr">
         <is>
-          <t>Proximus</t>
+          <t>Transport - STIB</t>
         </is>
       </c>
       <c r="J107" s="33" t="n">
-        <v>264.52</v>
-      </c>
-      <c r="K107" s="28" t="n"/>
+        <v>2.4</v>
+      </c>
+      <c r="K107" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L107" s="32" t="n"/>
     </row>
     <row r="108">
@@ -2948,16 +2948,20 @@
       <c r="H108" s="32" t="n"/>
       <c r="I108" s="13" t="inlineStr">
         <is>
-          <t>Lavage voiture</t>
+          <t>Versement impôts anticipé</t>
         </is>
       </c>
       <c r="J108" s="33" t="n">
-        <v>34</v>
-      </c>
-      <c r="K108" s="28" t="n"/>
+        <v>5000</v>
+      </c>
+      <c r="K108" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L108" s="32" t="inlineStr">
         <is>
-          <t>Wash Time Tervuren</t>
+          <t>Comm. 073/4616/33527</t>
         </is>
       </c>
     </row>
@@ -2968,17 +2972,13 @@
       <c r="H109" s="32" t="n"/>
       <c r="I109" s="13" t="inlineStr">
         <is>
-          <t>Transport - STIB</t>
+          <t>Frais comptable BDH</t>
         </is>
       </c>
       <c r="J109" s="33" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="K109" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+        <v>254.1</v>
+      </c>
+      <c r="K109" s="28" t="n"/>
       <c r="L109" s="32" t="n"/>
     </row>
     <row r="110">
@@ -2988,11 +2988,11 @@
       <c r="H110" s="32" t="n"/>
       <c r="I110" s="13" t="inlineStr">
         <is>
-          <t>Versement impôts anticipé</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="J110" s="33" t="n">
-        <v>5000</v>
+        <v>3.8</v>
       </c>
       <c r="K110" s="28" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="L110" s="32" t="inlineStr">
         <is>
-          <t>Comm. 073/4616/33527</t>
+          <t>Italie</t>
         </is>
       </c>
     </row>
@@ -3012,11 +3012,11 @@
       <c r="H111" s="32" t="n"/>
       <c r="I111" s="13" t="inlineStr">
         <is>
-          <t>Frais comptable BDH</t>
+          <t>Farys (eau)</t>
         </is>
       </c>
       <c r="J111" s="33" t="n">
-        <v>254.1</v>
+        <v>306</v>
       </c>
       <c r="K111" s="28" t="n"/>
       <c r="L111" s="32" t="n"/>
@@ -3028,22 +3028,14 @@
       <c r="H112" s="32" t="n"/>
       <c r="I112" s="13" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Repas Lunch Garden</t>
         </is>
       </c>
       <c r="J112" s="33" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K112" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L112" s="32" t="inlineStr">
-        <is>
-          <t>Italie</t>
-        </is>
-      </c>
+        <v>30.48</v>
+      </c>
+      <c r="K112" s="28" t="n"/>
+      <c r="L112" s="32" t="n"/>
     </row>
     <row r="113">
       <c r="E113" s="16" t="n"/>
@@ -3052,11 +3044,11 @@
       <c r="H113" s="32" t="n"/>
       <c r="I113" s="13" t="inlineStr">
         <is>
-          <t>Farys (eau)</t>
+          <t>Frais bancaires trimestriels</t>
         </is>
       </c>
       <c r="J113" s="33" t="n">
-        <v>306</v>
+        <v>11.25</v>
       </c>
       <c r="K113" s="28" t="n"/>
       <c r="L113" s="32" t="n"/>
@@ -3068,11 +3060,11 @@
       <c r="H114" s="32" t="n"/>
       <c r="I114" s="13" t="inlineStr">
         <is>
-          <t>Repas Lunch Garden</t>
+          <t>Collation</t>
         </is>
       </c>
       <c r="J114" s="33" t="n">
-        <v>30.48</v>
+        <v>16.9</v>
       </c>
       <c r="K114" s="28" t="n"/>
       <c r="L114" s="32" t="n"/>
@@ -3084,13 +3076,17 @@
       <c r="H115" s="32" t="n"/>
       <c r="I115" s="13" t="inlineStr">
         <is>
-          <t>Frais bancaires trimestriels</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="J115" s="33" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="K115" s="28" t="n"/>
+        <v>1.7</v>
+      </c>
+      <c r="K115" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L115" s="32" t="n"/>
     </row>
     <row r="116">
@@ -3100,11 +3096,11 @@
       <c r="H116" s="32" t="n"/>
       <c r="I116" s="13" t="inlineStr">
         <is>
-          <t>Collation</t>
+          <t>Paiement carte de crédit</t>
         </is>
       </c>
       <c r="J116" s="33" t="n">
-        <v>16.9</v>
+        <v>275.86</v>
       </c>
       <c r="K116" s="28" t="n"/>
       <c r="L116" s="32" t="n"/>
@@ -3116,11 +3112,11 @@
       <c r="H117" s="32" t="n"/>
       <c r="I117" s="13" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Carburant</t>
         </is>
       </c>
       <c r="J117" s="33" t="n">
-        <v>1.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K117" s="28" t="inlineStr">
         <is>
@@ -3136,13 +3132,17 @@
       <c r="H118" s="32" t="n"/>
       <c r="I118" s="13" t="inlineStr">
         <is>
-          <t>Paiement carte de crédit</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="J118" s="33" t="n">
-        <v>275.86</v>
-      </c>
-      <c r="K118" s="28" t="n"/>
+        <v>3.4</v>
+      </c>
+      <c r="K118" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L118" s="32" t="n"/>
     </row>
     <row r="119">
@@ -3152,11 +3152,11 @@
       <c r="H119" s="32" t="n"/>
       <c r="I119" s="13" t="inlineStr">
         <is>
-          <t>Carburant</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="J119" s="33" t="n">
-        <v>80.90000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="K119" s="28" t="inlineStr">
         <is>
@@ -3170,20 +3170,20 @@
       <c r="F120" s="17" t="n"/>
       <c r="G120" s="31" t="n"/>
       <c r="H120" s="32" t="n"/>
-      <c r="I120" s="13" t="inlineStr">
-        <is>
-          <t>Parking</t>
-        </is>
-      </c>
-      <c r="J120" s="33" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K120" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L120" s="32" t="n"/>
+      <c r="I120" s="40" t="inlineStr">
+        <is>
+          <t>Redevance de stationnement - OPC</t>
+        </is>
+      </c>
+      <c r="J120" s="41" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K120" s="28" t="n"/>
+      <c r="L120" s="39" t="inlineStr">
+        <is>
+          <t>à confirmer (redevance ou amende)</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="E121" s="16" t="n"/>
@@ -3192,11 +3192,11 @@
       <c r="H121" s="32" t="n"/>
       <c r="I121" s="13" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Carburant</t>
         </is>
       </c>
       <c r="J121" s="33" t="n">
-        <v>7.2</v>
+        <v>77.88</v>
       </c>
       <c r="K121" s="28" t="inlineStr">
         <is>
@@ -3210,20 +3210,20 @@
       <c r="F122" s="17" t="n"/>
       <c r="G122" s="31" t="n"/>
       <c r="H122" s="32" t="n"/>
-      <c r="I122" s="40" t="inlineStr">
-        <is>
-          <t>Redevance de stationnement - OPC</t>
-        </is>
-      </c>
-      <c r="J122" s="41" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K122" s="28" t="n"/>
-      <c r="L122" s="39" t="inlineStr">
-        <is>
-          <t>à confirmer (redevance ou amende)</t>
-        </is>
-      </c>
+      <c r="I122" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J122" s="33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K122" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L122" s="32" t="n"/>
     </row>
     <row r="123">
       <c r="E123" s="16" t="n"/>
@@ -3232,17 +3232,13 @@
       <c r="H123" s="32" t="n"/>
       <c r="I123" s="13" t="inlineStr">
         <is>
-          <t>Carburant</t>
+          <t>Repas Lunch Garden</t>
         </is>
       </c>
       <c r="J123" s="33" t="n">
-        <v>77.88</v>
-      </c>
-      <c r="K123" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+        <v>16.54</v>
+      </c>
+      <c r="K123" s="28" t="n"/>
       <c r="L123" s="32" t="n"/>
     </row>
     <row r="124">
@@ -3250,20 +3246,20 @@
       <c r="F124" s="17" t="n"/>
       <c r="G124" s="31" t="n"/>
       <c r="H124" s="32" t="n"/>
-      <c r="I124" s="13" t="inlineStr">
-        <is>
-          <t>Parking</t>
-        </is>
-      </c>
-      <c r="J124" s="33" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="K124" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L124" s="32" t="n"/>
+      <c r="I124" s="40" t="inlineStr">
+        <is>
+          <t>Achat - Orgefi SPRL</t>
+        </is>
+      </c>
+      <c r="J124" s="41" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K124" s="28" t="n"/>
+      <c r="L124" s="39" t="inlineStr">
+        <is>
+          <t>Nivelles — à identifier</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="E125" s="16" t="n"/>
@@ -3272,14 +3268,22 @@
       <c r="H125" s="32" t="n"/>
       <c r="I125" s="13" t="inlineStr">
         <is>
-          <t>Repas Lunch Garden</t>
+          <t>Carburant</t>
         </is>
       </c>
       <c r="J125" s="33" t="n">
-        <v>16.54</v>
-      </c>
-      <c r="K125" s="28" t="n"/>
-      <c r="L125" s="32" t="n"/>
+        <v>4.35</v>
+      </c>
+      <c r="K125" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L125" s="32" t="inlineStr">
+        <is>
+          <t>Total Schaerbeek</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="E126" s="16" t="n"/>
@@ -3292,7 +3296,7 @@
         </is>
       </c>
       <c r="J126" s="41" t="n">
-        <v>9.5</v>
+        <v>3.6</v>
       </c>
       <c r="K126" s="28" t="n"/>
       <c r="L126" s="39" t="inlineStr">
@@ -3308,42 +3312,30 @@
       <c r="H127" s="32" t="n"/>
       <c r="I127" s="13" t="inlineStr">
         <is>
-          <t>Carburant</t>
+          <t>Assurance voiture</t>
         </is>
       </c>
       <c r="J127" s="33" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="K127" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L127" s="32" t="inlineStr">
-        <is>
-          <t>Total Schaerbeek</t>
-        </is>
-      </c>
+        <v>458.66</v>
+      </c>
+      <c r="K127" s="28" t="n"/>
+      <c r="L127" s="32" t="n"/>
     </row>
     <row r="128">
       <c r="E128" s="16" t="n"/>
       <c r="F128" s="17" t="n"/>
       <c r="G128" s="31" t="n"/>
       <c r="H128" s="32" t="n"/>
-      <c r="I128" s="40" t="inlineStr">
-        <is>
-          <t>Achat - Orgefi SPRL</t>
-        </is>
-      </c>
-      <c r="J128" s="41" t="n">
-        <v>3.6</v>
+      <c r="I128" s="13" t="inlineStr">
+        <is>
+          <t>Electrabel</t>
+        </is>
+      </c>
+      <c r="J128" s="33" t="n">
+        <v>270.94</v>
       </c>
       <c r="K128" s="28" t="n"/>
-      <c r="L128" s="39" t="inlineStr">
-        <is>
-          <t>Nivelles — à identifier</t>
-        </is>
-      </c>
+      <c r="L128" s="32" t="n"/>
     </row>
     <row r="129">
       <c r="E129" s="16" t="n"/>
@@ -3352,11 +3344,11 @@
       <c r="H129" s="32" t="n"/>
       <c r="I129" s="13" t="inlineStr">
         <is>
-          <t>Assurance voiture</t>
+          <t>Electrabel</t>
         </is>
       </c>
       <c r="J129" s="33" t="n">
-        <v>458.66</v>
+        <v>263.44</v>
       </c>
       <c r="K129" s="28" t="n"/>
       <c r="L129" s="32" t="n"/>
@@ -3368,11 +3360,11 @@
       <c r="H130" s="32" t="n"/>
       <c r="I130" s="13" t="inlineStr">
         <is>
-          <t>Electrabel</t>
+          <t>Proximus</t>
         </is>
       </c>
       <c r="J130" s="33" t="n">
-        <v>270.94</v>
+        <v>226.02</v>
       </c>
       <c r="K130" s="28" t="n"/>
       <c r="L130" s="32" t="n"/>
@@ -3384,11 +3376,11 @@
       <c r="H131" s="32" t="n"/>
       <c r="I131" s="13" t="inlineStr">
         <is>
-          <t>Electrabel</t>
+          <t>Réception marchandise - UPS</t>
         </is>
       </c>
       <c r="J131" s="33" t="n">
-        <v>263.44</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="K131" s="28" t="n"/>
       <c r="L131" s="32" t="n"/>
@@ -3400,11 +3392,11 @@
       <c r="H132" s="32" t="n"/>
       <c r="I132" s="13" t="inlineStr">
         <is>
-          <t>Proximus</t>
+          <t>Repas Lunch Garden</t>
         </is>
       </c>
       <c r="J132" s="33" t="n">
-        <v>226.02</v>
+        <v>51.02</v>
       </c>
       <c r="K132" s="28" t="n"/>
       <c r="L132" s="32" t="n"/>
@@ -3414,93 +3406,97 @@
       <c r="F133" s="17" t="n"/>
       <c r="G133" s="31" t="n"/>
       <c r="H133" s="32" t="n"/>
-      <c r="I133" s="13" t="inlineStr">
-        <is>
-          <t>Réception marchandise - UPS</t>
-        </is>
-      </c>
-      <c r="J133" s="33" t="n">
-        <v>8.029999999999999</v>
+      <c r="I133" s="40" t="inlineStr">
+        <is>
+          <t>Redevance de stationnement - OPC</t>
+        </is>
+      </c>
+      <c r="J133" s="41" t="n">
+        <v>40</v>
       </c>
       <c r="K133" s="28" t="n"/>
-      <c r="L133" s="32" t="n"/>
+      <c r="L133" s="39" t="inlineStr">
+        <is>
+          <t>à confirmer (redevance ou amende)</t>
+        </is>
+      </c>
     </row>
     <row r="134">
-      <c r="E134" s="16" t="n"/>
-      <c r="F134" s="17" t="n"/>
-      <c r="G134" s="31" t="n"/>
-      <c r="H134" s="32" t="n"/>
-      <c r="I134" s="13" t="inlineStr">
-        <is>
-          <t>Repas Lunch Garden</t>
-        </is>
-      </c>
-      <c r="J134" s="33" t="n">
-        <v>51.02</v>
-      </c>
-      <c r="K134" s="28" t="n"/>
-      <c r="L134" s="32" t="n"/>
+      <c r="G134" s="34" t="n"/>
+      <c r="H134" s="35" t="n"/>
+      <c r="J134" s="34" t="n"/>
+      <c r="L134" s="35" t="n"/>
     </row>
     <row r="135">
-      <c r="E135" s="16" t="n"/>
-      <c r="F135" s="17" t="n"/>
-      <c r="G135" s="31" t="n"/>
-      <c r="H135" s="32" t="n"/>
-      <c r="I135" s="40" t="inlineStr">
-        <is>
-          <t>Redevance de stationnement - OPC</t>
-        </is>
-      </c>
-      <c r="J135" s="41" t="n">
-        <v>40</v>
-      </c>
-      <c r="K135" s="28" t="n"/>
-      <c r="L135" s="39" t="inlineStr">
-        <is>
-          <t>à confirmer (redevance ou amende)</t>
-        </is>
-      </c>
+      <c r="G135" s="34" t="n"/>
+      <c r="H135" s="35" t="n"/>
+      <c r="J135" s="34" t="n"/>
+      <c r="L135" s="35" t="n"/>
     </row>
     <row r="136">
-      <c r="G136" s="34" t="n"/>
-      <c r="H136" s="35" t="n"/>
-      <c r="J136" s="34" t="n"/>
-      <c r="L136" s="35" t="n"/>
+      <c r="E136" s="16" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="F136" s="17" t="inlineStr">
+        <is>
+          <t>LAM2605</t>
+        </is>
+      </c>
+      <c r="G136" s="31" t="n">
+        <v>4619.2</v>
+      </c>
+      <c r="H136" s="32" t="n"/>
+      <c r="I136" s="28" t="inlineStr">
+        <is>
+          <t>Carburant</t>
+        </is>
+      </c>
+      <c r="J136" s="36" t="n">
+        <v>89.01000000000001</v>
+      </c>
+      <c r="K136" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L136" s="32" t="n"/>
     </row>
     <row r="137">
-      <c r="G137" s="34" t="n"/>
-      <c r="H137" s="35" t="n"/>
-      <c r="J137" s="34" t="n"/>
-      <c r="L137" s="35" t="n"/>
+      <c r="E137" s="16" t="n"/>
+      <c r="F137" s="17" t="n"/>
+      <c r="G137" s="31" t="n"/>
+      <c r="H137" s="32" t="n"/>
+      <c r="I137" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J137" s="33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K137" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L137" s="32" t="n"/>
     </row>
     <row r="138">
-      <c r="E138" s="16" t="inlineStr">
-        <is>
-          <t>Mai</t>
-        </is>
-      </c>
-      <c r="F138" s="17" t="inlineStr">
-        <is>
-          <t>LAM2605</t>
-        </is>
-      </c>
-      <c r="G138" s="31" t="n">
-        <v>4619.2</v>
-      </c>
+      <c r="E138" s="16" t="n"/>
+      <c r="F138" s="17" t="n"/>
+      <c r="G138" s="31" t="n"/>
       <c r="H138" s="32" t="n"/>
-      <c r="I138" s="28" t="inlineStr">
-        <is>
-          <t>Carburant</t>
-        </is>
-      </c>
-      <c r="J138" s="36" t="n">
-        <v>89.01000000000001</v>
-      </c>
-      <c r="K138" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="I138" s="13" t="inlineStr">
+        <is>
+          <t>Précompte salarial avril 2026 Thibault Duchène</t>
+        </is>
+      </c>
+      <c r="J138" s="33" t="n">
+        <v>2250</v>
+      </c>
+      <c r="K138" s="28" t="n"/>
       <c r="L138" s="32" t="n"/>
     </row>
     <row r="139">
@@ -3510,17 +3506,13 @@
       <c r="H139" s="32" t="n"/>
       <c r="I139" s="13" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Partena</t>
         </is>
       </c>
       <c r="J139" s="33" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="K139" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+        <v>1747.34</v>
+      </c>
+      <c r="K139" s="28" t="n"/>
       <c r="L139" s="32" t="n"/>
     </row>
     <row r="140">
@@ -3530,13 +3522,17 @@
       <c r="H140" s="32" t="n"/>
       <c r="I140" s="13" t="inlineStr">
         <is>
-          <t>Précompte salarial avril 2026 Thibault Duchène</t>
+          <t>Crédit voiture</t>
         </is>
       </c>
       <c r="J140" s="33" t="n">
-        <v>2250</v>
-      </c>
-      <c r="K140" s="28" t="n"/>
+        <v>724.12</v>
+      </c>
+      <c r="K140" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L140" s="32" t="n"/>
     </row>
     <row r="141">
@@ -3546,14 +3542,18 @@
       <c r="H141" s="32" t="n"/>
       <c r="I141" s="13" t="inlineStr">
         <is>
-          <t>Partena</t>
+          <t>Remboursement alimentation du compte - Thibault Duchène</t>
         </is>
       </c>
       <c r="J141" s="33" t="n">
-        <v>1747.34</v>
+        <v>500</v>
       </c>
       <c r="K141" s="28" t="n"/>
-      <c r="L141" s="32" t="n"/>
+      <c r="L141" s="32" t="inlineStr">
+        <is>
+          <t>Restitution des apports de février 2026</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="E142" s="16" t="n"/>
@@ -3562,17 +3562,13 @@
       <c r="H142" s="32" t="n"/>
       <c r="I142" s="13" t="inlineStr">
         <is>
-          <t>Crédit voiture</t>
+          <t>Collation</t>
         </is>
       </c>
       <c r="J142" s="33" t="n">
-        <v>724.12</v>
-      </c>
-      <c r="K142" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="K142" s="28" t="n"/>
       <c r="L142" s="32" t="n"/>
     </row>
     <row r="143">
@@ -3582,18 +3578,14 @@
       <c r="H143" s="32" t="n"/>
       <c r="I143" s="13" t="inlineStr">
         <is>
-          <t>Remboursement alimentation du compte - Thibault Duchène</t>
+          <t>Collation</t>
         </is>
       </c>
       <c r="J143" s="33" t="n">
-        <v>500</v>
+        <v>3</v>
       </c>
       <c r="K143" s="28" t="n"/>
-      <c r="L143" s="32" t="inlineStr">
-        <is>
-          <t>Restitution des apports de février 2026</t>
-        </is>
-      </c>
+      <c r="L143" s="32" t="n"/>
     </row>
     <row r="144">
       <c r="E144" s="16" t="n"/>
@@ -3602,14 +3594,22 @@
       <c r="H144" s="32" t="n"/>
       <c r="I144" s="13" t="inlineStr">
         <is>
-          <t>Collation</t>
+          <t>Carburant</t>
         </is>
       </c>
       <c r="J144" s="33" t="n">
-        <v>8</v>
-      </c>
-      <c r="K144" s="28" t="n"/>
-      <c r="L144" s="32" t="n"/>
+        <v>85.45</v>
+      </c>
+      <c r="K144" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L144" s="32" t="inlineStr">
+        <is>
+          <t>Total Schaerbeek</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="E145" s="16" t="n"/>
@@ -3618,13 +3618,17 @@
       <c r="H145" s="32" t="n"/>
       <c r="I145" s="13" t="inlineStr">
         <is>
-          <t>Collation</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="J145" s="33" t="n">
-        <v>3</v>
-      </c>
-      <c r="K145" s="28" t="n"/>
+        <v>11.7</v>
+      </c>
+      <c r="K145" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L145" s="32" t="n"/>
     </row>
     <row r="146">
@@ -3634,22 +3638,14 @@
       <c r="H146" s="32" t="n"/>
       <c r="I146" s="13" t="inlineStr">
         <is>
-          <t>Carburant</t>
+          <t>Collation</t>
         </is>
       </c>
       <c r="J146" s="33" t="n">
-        <v>85.45</v>
-      </c>
-      <c r="K146" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L146" s="32" t="inlineStr">
-        <is>
-          <t>Total Schaerbeek</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="K146" s="28" t="n"/>
+      <c r="L146" s="32" t="n"/>
     </row>
     <row r="147">
       <c r="E147" s="16" t="n"/>
@@ -3658,17 +3654,13 @@
       <c r="H147" s="32" t="n"/>
       <c r="I147" s="13" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Paiement carte de crédit</t>
         </is>
       </c>
       <c r="J147" s="33" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="K147" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+        <v>40.6</v>
+      </c>
+      <c r="K147" s="28" t="n"/>
       <c r="L147" s="32" t="n"/>
     </row>
     <row r="148">
@@ -3678,13 +3670,17 @@
       <c r="H148" s="32" t="n"/>
       <c r="I148" s="13" t="inlineStr">
         <is>
-          <t>Collation</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="J148" s="33" t="n">
-        <v>8</v>
-      </c>
-      <c r="K148" s="28" t="n"/>
+        <v>0.5</v>
+      </c>
+      <c r="K148" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L148" s="32" t="n"/>
     </row>
     <row r="149">
@@ -3694,13 +3690,17 @@
       <c r="H149" s="32" t="n"/>
       <c r="I149" s="13" t="inlineStr">
         <is>
-          <t>Paiement carte de crédit</t>
+          <t>Carburant</t>
         </is>
       </c>
       <c r="J149" s="33" t="n">
-        <v>40.6</v>
-      </c>
-      <c r="K149" s="28" t="n"/>
+        <v>72.66</v>
+      </c>
+      <c r="K149" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L149" s="32" t="n"/>
     </row>
     <row r="150">
@@ -3710,11 +3710,11 @@
       <c r="H150" s="32" t="n"/>
       <c r="I150" s="13" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Carburant</t>
         </is>
       </c>
       <c r="J150" s="33" t="n">
-        <v>0.5</v>
+        <v>6.55</v>
       </c>
       <c r="K150" s="28" t="inlineStr">
         <is>
@@ -3730,11 +3730,11 @@
       <c r="H151" s="32" t="n"/>
       <c r="I151" s="13" t="inlineStr">
         <is>
-          <t>Carburant</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="J151" s="33" t="n">
-        <v>72.66</v>
+        <v>4.2</v>
       </c>
       <c r="K151" s="28" t="inlineStr">
         <is>
@@ -3748,20 +3748,20 @@
       <c r="F152" s="17" t="n"/>
       <c r="G152" s="31" t="n"/>
       <c r="H152" s="32" t="n"/>
-      <c r="I152" s="13" t="inlineStr">
-        <is>
-          <t>Carburant</t>
-        </is>
-      </c>
-      <c r="J152" s="33" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="K152" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L152" s="32" t="n"/>
+      <c r="I152" s="40" t="inlineStr">
+        <is>
+          <t>Abonnement salle FitRaw</t>
+        </is>
+      </c>
+      <c r="J152" s="41" t="n">
+        <v>59.04</v>
+      </c>
+      <c r="K152" s="28" t="n"/>
+      <c r="L152" s="39" t="inlineStr">
+        <is>
+          <t>Sterrebeek — usage professionnel à confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="E153" s="16" t="n"/>
@@ -3770,38 +3770,38 @@
       <c r="H153" s="32" t="n"/>
       <c r="I153" s="13" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Lavage voiture</t>
         </is>
       </c>
       <c r="J153" s="33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K153" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L153" s="32" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="K153" s="28" t="n"/>
+      <c r="L153" s="32" t="inlineStr">
+        <is>
+          <t>Wash Time Tervuren</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="E154" s="16" t="n"/>
       <c r="F154" s="17" t="n"/>
       <c r="G154" s="31" t="n"/>
       <c r="H154" s="32" t="n"/>
-      <c r="I154" s="40" t="inlineStr">
-        <is>
-          <t>Abonnement salle FitRaw</t>
-        </is>
-      </c>
-      <c r="J154" s="41" t="n">
-        <v>59.04</v>
-      </c>
-      <c r="K154" s="28" t="n"/>
-      <c r="L154" s="39" t="inlineStr">
-        <is>
-          <t>Sterrebeek — usage professionnel à confirmer</t>
-        </is>
-      </c>
+      <c r="I154" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J154" s="33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K154" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L154" s="32" t="n"/>
     </row>
     <row r="155">
       <c r="E155" s="16" t="n"/>
@@ -3810,18 +3810,18 @@
       <c r="H155" s="32" t="n"/>
       <c r="I155" s="13" t="inlineStr">
         <is>
-          <t>Lavage voiture</t>
+          <t>Carburant</t>
         </is>
       </c>
       <c r="J155" s="33" t="n">
-        <v>32</v>
-      </c>
-      <c r="K155" s="28" t="n"/>
-      <c r="L155" s="32" t="inlineStr">
-        <is>
-          <t>Wash Time Tervuren</t>
-        </is>
-      </c>
+        <v>79.51000000000001</v>
+      </c>
+      <c r="K155" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L155" s="32" t="n"/>
     </row>
     <row r="156">
       <c r="E156" s="16" t="n"/>
@@ -3834,14 +3834,18 @@
         </is>
       </c>
       <c r="J156" s="33" t="n">
-        <v>1.7</v>
+        <v>15.6</v>
       </c>
       <c r="K156" s="28" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="L156" s="32" t="n"/>
+      <c r="L156" s="32" t="inlineStr">
+        <is>
+          <t>Schiphol (Pays-Bas)</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="E157" s="16" t="n"/>
@@ -3850,11 +3854,11 @@
       <c r="H157" s="32" t="n"/>
       <c r="I157" s="13" t="inlineStr">
         <is>
-          <t>Carburant</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="J157" s="33" t="n">
-        <v>79.51000000000001</v>
+        <v>5</v>
       </c>
       <c r="K157" s="28" t="inlineStr">
         <is>
@@ -3874,93 +3878,95 @@
         </is>
       </c>
       <c r="J158" s="33" t="n">
-        <v>15.6</v>
+        <v>6.8</v>
       </c>
       <c r="K158" s="28" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="L158" s="32" t="inlineStr">
-        <is>
-          <t>Schiphol (Pays-Bas)</t>
-        </is>
-      </c>
+      <c r="L158" s="32" t="n"/>
     </row>
     <row r="159">
-      <c r="E159" s="16" t="n"/>
-      <c r="F159" s="17" t="n"/>
-      <c r="G159" s="31" t="n"/>
-      <c r="H159" s="32" t="n"/>
-      <c r="I159" s="13" t="inlineStr">
-        <is>
-          <t>Parking</t>
-        </is>
-      </c>
-      <c r="J159" s="33" t="n">
-        <v>5</v>
-      </c>
-      <c r="K159" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L159" s="32" t="n"/>
+      <c r="G159" s="34" t="n"/>
+      <c r="H159" s="35" t="n"/>
+      <c r="J159" s="34" t="n"/>
+      <c r="L159" s="35" t="n"/>
     </row>
     <row r="160">
-      <c r="E160" s="16" t="n"/>
-      <c r="F160" s="17" t="n"/>
-      <c r="G160" s="31" t="n"/>
-      <c r="H160" s="32" t="n"/>
-      <c r="I160" s="13" t="inlineStr">
-        <is>
-          <t>Parking</t>
-        </is>
-      </c>
-      <c r="J160" s="33" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K160" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L160" s="32" t="n"/>
+      <c r="G160" s="34" t="n"/>
+      <c r="H160" s="35" t="n"/>
+      <c r="J160" s="34" t="n"/>
+      <c r="L160" s="35" t="n"/>
     </row>
     <row r="161">
-      <c r="G161" s="34" t="n"/>
-      <c r="H161" s="35" t="n"/>
-      <c r="J161" s="34" t="n"/>
-      <c r="L161" s="35" t="n"/>
+      <c r="E161" s="16" t="inlineStr">
+        <is>
+          <t>Juin</t>
+        </is>
+      </c>
+      <c r="F161" s="17" t="inlineStr">
+        <is>
+          <t>LAM2606</t>
+        </is>
+      </c>
+      <c r="G161" s="31" t="n">
+        <v>4803.5</v>
+      </c>
+      <c r="H161" s="32" t="n"/>
+      <c r="I161" s="28" t="inlineStr">
+        <is>
+          <t>Carburant</t>
+        </is>
+      </c>
+      <c r="J161" s="36" t="n">
+        <v>75.41</v>
+      </c>
+      <c r="K161" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L161" s="32" t="n"/>
     </row>
     <row r="162">
-      <c r="G162" s="34" t="n"/>
-      <c r="H162" s="35" t="n"/>
-      <c r="J162" s="34" t="n"/>
-      <c r="L162" s="35" t="n"/>
+      <c r="E162" s="16" t="n"/>
+      <c r="F162" s="17" t="inlineStr">
+        <is>
+          <t>Remboursement billet d'avion - Thibault Duchène</t>
+        </is>
+      </c>
+      <c r="G162" s="31" t="n">
+        <v>1815.16</v>
+      </c>
+      <c r="H162" s="32" t="n"/>
+      <c r="I162" s="40" t="inlineStr">
+        <is>
+          <t>Abonnement club David Lloyd</t>
+        </is>
+      </c>
+      <c r="J162" s="41" t="n">
+        <v>493</v>
+      </c>
+      <c r="K162" s="28" t="n"/>
+      <c r="L162" s="39" t="inlineStr">
+        <is>
+          <t>Sterrebeek — usage professionnel à confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="163">
-      <c r="E163" s="16" t="inlineStr">
-        <is>
-          <t>Juin</t>
-        </is>
-      </c>
-      <c r="F163" s="17" t="inlineStr">
-        <is>
-          <t>LAM2606</t>
-        </is>
-      </c>
-      <c r="G163" s="31" t="n">
-        <v>4803.5</v>
-      </c>
+      <c r="E163" s="16" t="n"/>
+      <c r="F163" s="17" t="n"/>
+      <c r="G163" s="31" t="n"/>
       <c r="H163" s="32" t="n"/>
-      <c r="I163" s="28" t="inlineStr">
-        <is>
-          <t>Carburant</t>
-        </is>
-      </c>
-      <c r="J163" s="36" t="n">
-        <v>75.41</v>
+      <c r="I163" s="13" t="inlineStr">
+        <is>
+          <t>Crédit voiture</t>
+        </is>
+      </c>
+      <c r="J163" s="33" t="n">
+        <v>724.12</v>
       </c>
       <c r="K163" s="28" t="inlineStr">
         <is>
@@ -3971,29 +3977,23 @@
     </row>
     <row r="164">
       <c r="E164" s="16" t="n"/>
-      <c r="F164" s="17" t="inlineStr">
-        <is>
-          <t>Remboursement billet d'avion - Thibault Duchène</t>
-        </is>
-      </c>
-      <c r="G164" s="31" t="n">
-        <v>1815.16</v>
-      </c>
+      <c r="F164" s="17" t="n"/>
+      <c r="G164" s="31" t="n"/>
       <c r="H164" s="32" t="n"/>
-      <c r="I164" s="40" t="inlineStr">
-        <is>
-          <t>Abonnement club David Lloyd</t>
-        </is>
-      </c>
-      <c r="J164" s="41" t="n">
-        <v>493</v>
-      </c>
-      <c r="K164" s="28" t="n"/>
-      <c r="L164" s="39" t="inlineStr">
-        <is>
-          <t>Sterrebeek — usage professionnel à confirmer</t>
-        </is>
-      </c>
+      <c r="I164" s="13" t="inlineStr">
+        <is>
+          <t>Carburant</t>
+        </is>
+      </c>
+      <c r="J164" s="33" t="n">
+        <v>83.72</v>
+      </c>
+      <c r="K164" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L164" s="32" t="n"/>
     </row>
     <row r="165">
       <c r="E165" s="16" t="n"/>
@@ -4002,11 +4002,11 @@
       <c r="H165" s="32" t="n"/>
       <c r="I165" s="13" t="inlineStr">
         <is>
-          <t>Crédit voiture</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="J165" s="33" t="n">
-        <v>724.12</v>
+        <v>43.75</v>
       </c>
       <c r="K165" s="28" t="inlineStr">
         <is>
@@ -4022,17 +4022,13 @@
       <c r="H166" s="32" t="n"/>
       <c r="I166" s="13" t="inlineStr">
         <is>
-          <t>Carburant</t>
+          <t>Précompte salarial mai 2026 Thibault Duchène</t>
         </is>
       </c>
       <c r="J166" s="33" t="n">
-        <v>83.72</v>
-      </c>
-      <c r="K166" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+        <v>2250</v>
+      </c>
+      <c r="K166" s="28" t="n"/>
       <c r="L166" s="32" t="n"/>
     </row>
     <row r="167">
@@ -4042,17 +4038,13 @@
       <c r="H167" s="32" t="n"/>
       <c r="I167" s="13" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>SD Worx</t>
         </is>
       </c>
       <c r="J167" s="33" t="n">
-        <v>43.75</v>
-      </c>
-      <c r="K167" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+        <v>332.84</v>
+      </c>
+      <c r="K167" s="28" t="n"/>
       <c r="L167" s="32" t="n"/>
     </row>
     <row r="168">
@@ -4062,11 +4054,11 @@
       <c r="H168" s="32" t="n"/>
       <c r="I168" s="13" t="inlineStr">
         <is>
-          <t>Précompte salarial mai 2026 Thibault Duchène</t>
+          <t>Proximus</t>
         </is>
       </c>
       <c r="J168" s="33" t="n">
-        <v>2250</v>
+        <v>203.91</v>
       </c>
       <c r="K168" s="28" t="n"/>
       <c r="L168" s="32" t="n"/>
@@ -4078,13 +4070,17 @@
       <c r="H169" s="32" t="n"/>
       <c r="I169" s="13" t="inlineStr">
         <is>
-          <t>SD Worx</t>
+          <t>Carburant</t>
         </is>
       </c>
       <c r="J169" s="33" t="n">
-        <v>332.84</v>
-      </c>
-      <c r="K169" s="28" t="n"/>
+        <v>80.15000000000001</v>
+      </c>
+      <c r="K169" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L169" s="32" t="n"/>
     </row>
     <row r="170">
@@ -4094,13 +4090,17 @@
       <c r="H170" s="32" t="n"/>
       <c r="I170" s="13" t="inlineStr">
         <is>
-          <t>Proximus</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="J170" s="33" t="n">
-        <v>203.91</v>
-      </c>
-      <c r="K170" s="28" t="n"/>
+        <v>1.9</v>
+      </c>
+      <c r="K170" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L170" s="32" t="n"/>
     </row>
     <row r="171">
@@ -4110,18 +4110,18 @@
       <c r="H171" s="32" t="n"/>
       <c r="I171" s="13" t="inlineStr">
         <is>
-          <t>Carburant</t>
+          <t>Lavage voiture</t>
         </is>
       </c>
       <c r="J171" s="33" t="n">
-        <v>80.15000000000001</v>
-      </c>
-      <c r="K171" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L171" s="32" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="K171" s="28" t="n"/>
+      <c r="L171" s="32" t="inlineStr">
+        <is>
+          <t>Wash Time Tervuren</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="E172" s="16" t="n"/>
@@ -4130,17 +4130,13 @@
       <c r="H172" s="32" t="n"/>
       <c r="I172" s="13" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Paiement carte de crédit</t>
         </is>
       </c>
       <c r="J172" s="33" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="K172" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+        <v>1815.16</v>
+      </c>
+      <c r="K172" s="28" t="n"/>
       <c r="L172" s="32" t="n"/>
     </row>
     <row r="173">
@@ -4150,18 +4146,18 @@
       <c r="H173" s="32" t="n"/>
       <c r="I173" s="13" t="inlineStr">
         <is>
-          <t>Lavage voiture</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="J173" s="33" t="n">
-        <v>17</v>
-      </c>
-      <c r="K173" s="28" t="n"/>
-      <c r="L173" s="32" t="inlineStr">
-        <is>
-          <t>Wash Time Tervuren</t>
-        </is>
-      </c>
+        <v>6.3</v>
+      </c>
+      <c r="K173" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L173" s="32" t="n"/>
     </row>
     <row r="174">
       <c r="E174" s="16" t="n"/>
@@ -4170,13 +4166,17 @@
       <c r="H174" s="32" t="n"/>
       <c r="I174" s="13" t="inlineStr">
         <is>
-          <t>Paiement carte de crédit</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="J174" s="33" t="n">
-        <v>1815.16</v>
-      </c>
-      <c r="K174" s="28" t="n"/>
+        <v>3.8</v>
+      </c>
+      <c r="K174" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L174" s="32" t="n"/>
     </row>
     <row r="175">
@@ -4186,17 +4186,13 @@
       <c r="H175" s="32" t="n"/>
       <c r="I175" s="13" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Electrabel</t>
         </is>
       </c>
       <c r="J175" s="33" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="K175" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+        <v>297.28</v>
+      </c>
+      <c r="K175" s="28" t="n"/>
       <c r="L175" s="32" t="n"/>
     </row>
     <row r="176">
@@ -4206,17 +4202,13 @@
       <c r="H176" s="32" t="n"/>
       <c r="I176" s="13" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Electrabel</t>
         </is>
       </c>
       <c r="J176" s="33" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K176" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+        <v>270.94</v>
+      </c>
+      <c r="K176" s="28" t="n"/>
       <c r="L176" s="32" t="n"/>
     </row>
     <row r="177">
@@ -4226,11 +4218,11 @@
       <c r="H177" s="32" t="n"/>
       <c r="I177" s="13" t="inlineStr">
         <is>
-          <t>Electrabel</t>
+          <t>Proximus</t>
         </is>
       </c>
       <c r="J177" s="33" t="n">
-        <v>297.28</v>
+        <v>239.76</v>
       </c>
       <c r="K177" s="28" t="n"/>
       <c r="L177" s="32" t="n"/>
@@ -4242,13 +4234,17 @@
       <c r="H178" s="32" t="n"/>
       <c r="I178" s="13" t="inlineStr">
         <is>
-          <t>Electrabel</t>
+          <t>Carburant</t>
         </is>
       </c>
       <c r="J178" s="33" t="n">
-        <v>270.94</v>
-      </c>
-      <c r="K178" s="28" t="n"/>
+        <v>83.5</v>
+      </c>
+      <c r="K178" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L178" s="32" t="n"/>
     </row>
     <row r="179">
@@ -4258,11 +4254,11 @@
       <c r="H179" s="32" t="n"/>
       <c r="I179" s="13" t="inlineStr">
         <is>
-          <t>Proximus</t>
+          <t>Achat matériel sportif - DECATHLON</t>
         </is>
       </c>
       <c r="J179" s="33" t="n">
-        <v>239.76</v>
+        <v>82.5</v>
       </c>
       <c r="K179" s="28" t="n"/>
       <c r="L179" s="32" t="n"/>
@@ -4274,17 +4270,13 @@
       <c r="H180" s="32" t="n"/>
       <c r="I180" s="13" t="inlineStr">
         <is>
-          <t>Carburant</t>
+          <t>SD Worx</t>
         </is>
       </c>
       <c r="J180" s="33" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="K180" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+        <v>32.84</v>
+      </c>
+      <c r="K180" s="28" t="n"/>
       <c r="L180" s="32" t="n"/>
     </row>
     <row r="181">
@@ -4294,13 +4286,17 @@
       <c r="H181" s="32" t="n"/>
       <c r="I181" s="13" t="inlineStr">
         <is>
-          <t>Achat matériel sportif - DECATHLON</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="J181" s="33" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="K181" s="28" t="n"/>
+        <v>8.43</v>
+      </c>
+      <c r="K181" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L181" s="32" t="n"/>
     </row>
     <row r="182">
@@ -4310,13 +4306,17 @@
       <c r="H182" s="32" t="n"/>
       <c r="I182" s="13" t="inlineStr">
         <is>
-          <t>SD Worx</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="J182" s="33" t="n">
-        <v>32.84</v>
-      </c>
-      <c r="K182" s="28" t="n"/>
+        <v>35</v>
+      </c>
+      <c r="K182" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L182" s="32" t="n"/>
     </row>
     <row r="183">
@@ -4326,18 +4326,18 @@
       <c r="H183" s="32" t="n"/>
       <c r="I183" s="13" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Divers - sanitaires autoroute</t>
         </is>
       </c>
       <c r="J183" s="33" t="n">
-        <v>8.43</v>
-      </c>
-      <c r="K183" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L183" s="32" t="n"/>
+        <v>0.8</v>
+      </c>
+      <c r="K183" s="28" t="n"/>
+      <c r="L183" s="32" t="inlineStr">
+        <is>
+          <t>Aire de Rotselaar</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="E184" s="16" t="n"/>
@@ -4346,18 +4346,18 @@
       <c r="H184" s="32" t="n"/>
       <c r="I184" s="13" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Divers - sanitaires autoroute</t>
         </is>
       </c>
       <c r="J184" s="33" t="n">
-        <v>35</v>
-      </c>
-      <c r="K184" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L184" s="32" t="n"/>
+        <v>0.8</v>
+      </c>
+      <c r="K184" s="28" t="n"/>
+      <c r="L184" s="32" t="inlineStr">
+        <is>
+          <t>Aire de Rotselaar</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="E185" s="16" t="n"/>
@@ -4366,18 +4366,18 @@
       <c r="H185" s="32" t="n"/>
       <c r="I185" s="13" t="inlineStr">
         <is>
-          <t>Divers - sanitaires autoroute</t>
+          <t>Carburant</t>
         </is>
       </c>
       <c r="J185" s="33" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K185" s="28" t="n"/>
-      <c r="L185" s="32" t="inlineStr">
-        <is>
-          <t>Aire de Rotselaar</t>
-        </is>
-      </c>
+        <v>77.3</v>
+      </c>
+      <c r="K185" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L185" s="32" t="n"/>
     </row>
     <row r="186">
       <c r="E186" s="16" t="n"/>
@@ -4386,18 +4386,18 @@
       <c r="H186" s="32" t="n"/>
       <c r="I186" s="13" t="inlineStr">
         <is>
-          <t>Divers - sanitaires autoroute</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="J186" s="33" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K186" s="28" t="n"/>
-      <c r="L186" s="32" t="inlineStr">
-        <is>
-          <t>Aire de Rotselaar</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="K186" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L186" s="32" t="n"/>
     </row>
     <row r="187">
       <c r="E187" s="16" t="n"/>
@@ -4406,11 +4406,11 @@
       <c r="H187" s="32" t="n"/>
       <c r="I187" s="13" t="inlineStr">
         <is>
-          <t>Carburant</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="J187" s="33" t="n">
-        <v>77.3</v>
+        <v>4</v>
       </c>
       <c r="K187" s="28" t="inlineStr">
         <is>
@@ -4424,20 +4424,20 @@
       <c r="F188" s="17" t="n"/>
       <c r="G188" s="31" t="n"/>
       <c r="H188" s="32" t="n"/>
-      <c r="I188" s="13" t="inlineStr">
-        <is>
-          <t>Parking</t>
-        </is>
-      </c>
-      <c r="J188" s="33" t="n">
-        <v>4</v>
-      </c>
-      <c r="K188" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L188" s="32" t="n"/>
+      <c r="I188" s="40" t="inlineStr">
+        <is>
+          <t>Hôtel Ibis Nieuwpoort</t>
+        </is>
+      </c>
+      <c r="J188" s="41" t="n">
+        <v>15</v>
+      </c>
+      <c r="K188" s="28" t="n"/>
+      <c r="L188" s="39" t="inlineStr">
+        <is>
+          <t>à confirmer (nuitée ou consommation)</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="E189" s="16" t="n"/>
@@ -4450,7 +4450,7 @@
         </is>
       </c>
       <c r="J189" s="33" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K189" s="28" t="inlineStr">
         <is>
@@ -4464,169 +4464,165 @@
       <c r="F190" s="17" t="n"/>
       <c r="G190" s="31" t="n"/>
       <c r="H190" s="32" t="n"/>
-      <c r="I190" s="40" t="inlineStr">
-        <is>
-          <t>Hôtel Ibis Nieuwpoort</t>
-        </is>
-      </c>
-      <c r="J190" s="41" t="n">
-        <v>15</v>
-      </c>
-      <c r="K190" s="28" t="n"/>
-      <c r="L190" s="39" t="inlineStr">
-        <is>
-          <t>à confirmer (nuitée ou consommation)</t>
-        </is>
-      </c>
+      <c r="I190" s="13" t="inlineStr">
+        <is>
+          <t>Carburant</t>
+        </is>
+      </c>
+      <c r="J190" s="33" t="n">
+        <v>76.98999999999999</v>
+      </c>
+      <c r="K190" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L190" s="32" t="n"/>
     </row>
     <row r="191">
-      <c r="E191" s="16" t="n"/>
-      <c r="F191" s="17" t="n"/>
-      <c r="G191" s="31" t="n"/>
-      <c r="H191" s="32" t="n"/>
-      <c r="I191" s="13" t="inlineStr">
-        <is>
-          <t>Parking</t>
-        </is>
-      </c>
-      <c r="J191" s="33" t="n">
-        <v>8</v>
-      </c>
-      <c r="K191" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L191" s="32" t="n"/>
+      <c r="G191" s="34" t="n"/>
+      <c r="H191" s="35" t="n"/>
+      <c r="J191" s="34" t="n"/>
+      <c r="L191" s="35" t="n"/>
     </row>
     <row r="192">
-      <c r="E192" s="16" t="n"/>
-      <c r="F192" s="17" t="n"/>
-      <c r="G192" s="31" t="n"/>
-      <c r="H192" s="32" t="n"/>
-      <c r="I192" s="13" t="inlineStr">
-        <is>
-          <t>Carburant</t>
-        </is>
-      </c>
-      <c r="J192" s="33" t="n">
-        <v>76.98999999999999</v>
-      </c>
-      <c r="K192" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L192" s="32" t="n"/>
+      <c r="G192" s="34" t="n"/>
+      <c r="H192" s="35" t="n"/>
+      <c r="J192" s="34" t="n"/>
+      <c r="L192" s="35" t="n"/>
     </row>
     <row r="193">
-      <c r="G193" s="34" t="n"/>
-      <c r="H193" s="35" t="n"/>
-      <c r="J193" s="34" t="n"/>
-      <c r="L193" s="35" t="n"/>
+      <c r="E193" s="16" t="inlineStr">
+        <is>
+          <t>Juillet</t>
+        </is>
+      </c>
+      <c r="F193" s="17" t="inlineStr">
+        <is>
+          <t>LAM2607</t>
+        </is>
+      </c>
+      <c r="G193" s="31" t="n">
+        <v>4156.08</v>
+      </c>
+      <c r="H193" s="32" t="n"/>
+      <c r="I193" s="42" t="inlineStr">
+        <is>
+          <t>Abonnement club David Lloyd</t>
+        </is>
+      </c>
+      <c r="J193" s="43" t="n">
+        <v>493</v>
+      </c>
+      <c r="K193" s="28" t="n"/>
+      <c r="L193" s="39" t="inlineStr">
+        <is>
+          <t>Sterrebeek — usage professionnel à confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="194">
-      <c r="G194" s="34" t="n"/>
-      <c r="H194" s="35" t="n"/>
-      <c r="J194" s="34" t="n"/>
-      <c r="L194" s="35" t="n"/>
+      <c r="E194" s="16" t="n"/>
+      <c r="F194" s="17" t="inlineStr">
+        <is>
+          <t>Remboursement SD Worx</t>
+        </is>
+      </c>
+      <c r="G194" s="31" t="n">
+        <v>32.84</v>
+      </c>
+      <c r="H194" s="32" t="inlineStr">
+        <is>
+          <t>Cotisation payée deux fois</t>
+        </is>
+      </c>
+      <c r="I194" s="13" t="inlineStr">
+        <is>
+          <t>Précompte salarial juin 2026 Thibault Duchène</t>
+        </is>
+      </c>
+      <c r="J194" s="33" t="n">
+        <v>2250</v>
+      </c>
+      <c r="K194" s="28" t="n"/>
+      <c r="L194" s="32" t="n"/>
     </row>
     <row r="195">
-      <c r="E195" s="16" t="inlineStr">
-        <is>
-          <t>Juillet</t>
-        </is>
-      </c>
+      <c r="E195" s="16" t="n"/>
       <c r="F195" s="17" t="inlineStr">
         <is>
-          <t>LAM2607</t>
+          <t>LAM2608</t>
         </is>
       </c>
       <c r="G195" s="31" t="n">
-        <v>4156.08</v>
+        <v>6448.4</v>
       </c>
       <c r="H195" s="32" t="n"/>
-      <c r="I195" s="42" t="inlineStr">
-        <is>
-          <t>Abonnement club David Lloyd</t>
-        </is>
-      </c>
-      <c r="J195" s="43" t="n">
-        <v>493</v>
+      <c r="I195" s="13" t="inlineStr">
+        <is>
+          <t>SD Worx</t>
+        </is>
+      </c>
+      <c r="J195" s="33" t="n">
+        <v>332.84</v>
       </c>
       <c r="K195" s="28" t="n"/>
-      <c r="L195" s="39" t="inlineStr">
-        <is>
-          <t>Sterrebeek — usage professionnel à confirmer</t>
-        </is>
-      </c>
+      <c r="L195" s="32" t="n"/>
     </row>
     <row r="196">
       <c r="E196" s="16" t="n"/>
       <c r="F196" s="17" t="inlineStr">
         <is>
-          <t>Remboursement SD Worx</t>
+          <t>Remboursement Airbnb - Thibault Duchène</t>
         </is>
       </c>
       <c r="G196" s="31" t="n">
-        <v>32.84</v>
-      </c>
-      <c r="H196" s="32" t="inlineStr">
-        <is>
-          <t>Cotisation payée deux fois</t>
-        </is>
-      </c>
+        <v>2431.44</v>
+      </c>
+      <c r="H196" s="32" t="n"/>
       <c r="I196" s="13" t="inlineStr">
         <is>
-          <t>Précompte salarial juin 2026 Thibault Duchène</t>
+          <t>SD Worx</t>
         </is>
       </c>
       <c r="J196" s="33" t="n">
-        <v>2250</v>
+        <v>332.84</v>
       </c>
       <c r="K196" s="28" t="n"/>
       <c r="L196" s="32" t="n"/>
     </row>
     <row r="197">
       <c r="E197" s="16" t="n"/>
-      <c r="F197" s="17" t="inlineStr">
-        <is>
-          <t>LAM2608</t>
-        </is>
-      </c>
-      <c r="G197" s="31" t="n">
-        <v>6448.4</v>
-      </c>
+      <c r="F197" s="17" t="n"/>
+      <c r="G197" s="31" t="n"/>
       <c r="H197" s="32" t="n"/>
       <c r="I197" s="13" t="inlineStr">
         <is>
-          <t>SD Worx</t>
+          <t>Crédit voiture</t>
         </is>
       </c>
       <c r="J197" s="33" t="n">
-        <v>332.84</v>
-      </c>
-      <c r="K197" s="28" t="n"/>
+        <v>724.12</v>
+      </c>
+      <c r="K197" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L197" s="32" t="n"/>
     </row>
     <row r="198">
       <c r="E198" s="16" t="n"/>
-      <c r="F198" s="17" t="inlineStr">
-        <is>
-          <t>Remboursement Airbnb - Thibault Duchène</t>
-        </is>
-      </c>
-      <c r="G198" s="31" t="n">
-        <v>2431.44</v>
-      </c>
+      <c r="F198" s="17" t="n"/>
+      <c r="G198" s="31" t="n"/>
       <c r="H198" s="32" t="n"/>
       <c r="I198" s="13" t="inlineStr">
         <is>
-          <t>SD Worx</t>
+          <t>Frais bancaires trimestriels</t>
         </is>
       </c>
       <c r="J198" s="33" t="n">
-        <v>332.84</v>
+        <v>11.25</v>
       </c>
       <c r="K198" s="28" t="n"/>
       <c r="L198" s="32" t="n"/>
@@ -4638,11 +4634,11 @@
       <c r="H199" s="32" t="n"/>
       <c r="I199" s="13" t="inlineStr">
         <is>
-          <t>Crédit voiture</t>
+          <t>Carburant</t>
         </is>
       </c>
       <c r="J199" s="33" t="n">
-        <v>724.12</v>
+        <v>79.41</v>
       </c>
       <c r="K199" s="28" t="inlineStr">
         <is>
@@ -4658,13 +4654,17 @@
       <c r="H200" s="32" t="n"/>
       <c r="I200" s="13" t="inlineStr">
         <is>
-          <t>Frais bancaires trimestriels</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="J200" s="33" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="K200" s="28" t="n"/>
+        <v>1.9</v>
+      </c>
+      <c r="K200" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L200" s="32" t="n"/>
     </row>
     <row r="201">
@@ -4674,11 +4674,11 @@
       <c r="H201" s="32" t="n"/>
       <c r="I201" s="13" t="inlineStr">
         <is>
-          <t>Carburant</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="J201" s="33" t="n">
-        <v>79.41</v>
+        <v>1.9</v>
       </c>
       <c r="K201" s="28" t="inlineStr">
         <is>
@@ -4694,17 +4694,13 @@
       <c r="H202" s="32" t="n"/>
       <c r="I202" s="13" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Collation</t>
         </is>
       </c>
       <c r="J202" s="33" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="K202" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="K202" s="28" t="n"/>
       <c r="L202" s="32" t="n"/>
     </row>
     <row r="203">
@@ -4718,7 +4714,7 @@
         </is>
       </c>
       <c r="J203" s="33" t="n">
-        <v>1.9</v>
+        <v>5.5</v>
       </c>
       <c r="K203" s="28" t="inlineStr">
         <is>
@@ -4734,11 +4730,11 @@
       <c r="H204" s="32" t="n"/>
       <c r="I204" s="13" t="inlineStr">
         <is>
-          <t>Collation</t>
+          <t>Péage autoroute France</t>
         </is>
       </c>
       <c r="J204" s="33" t="n">
-        <v>3</v>
+        <v>69.3</v>
       </c>
       <c r="K204" s="28" t="n"/>
       <c r="L204" s="32" t="n"/>
@@ -4750,11 +4746,11 @@
       <c r="H205" s="32" t="n"/>
       <c r="I205" s="13" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Carburant</t>
         </is>
       </c>
       <c r="J205" s="33" t="n">
-        <v>5.5</v>
+        <v>79.42</v>
       </c>
       <c r="K205" s="28" t="inlineStr">
         <is>
@@ -4770,11 +4766,11 @@
       <c r="H206" s="32" t="n"/>
       <c r="I206" s="13" t="inlineStr">
         <is>
-          <t>Péage autoroute France</t>
+          <t>Collation</t>
         </is>
       </c>
       <c r="J206" s="33" t="n">
-        <v>69.3</v>
+        <v>2.7</v>
       </c>
       <c r="K206" s="28" t="n"/>
       <c r="L206" s="32" t="n"/>
@@ -4786,11 +4782,11 @@
       <c r="H207" s="32" t="n"/>
       <c r="I207" s="13" t="inlineStr">
         <is>
-          <t>Carburant</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="J207" s="33" t="n">
-        <v>79.42</v>
+        <v>2.8</v>
       </c>
       <c r="K207" s="28" t="inlineStr">
         <is>
@@ -4806,14 +4802,18 @@
       <c r="H208" s="32" t="n"/>
       <c r="I208" s="13" t="inlineStr">
         <is>
-          <t>Collation</t>
+          <t>Lavage voiture</t>
         </is>
       </c>
       <c r="J208" s="33" t="n">
-        <v>2.7</v>
+        <v>32</v>
       </c>
       <c r="K208" s="28" t="n"/>
-      <c r="L208" s="32" t="n"/>
+      <c r="L208" s="32" t="inlineStr">
+        <is>
+          <t>Wash Time Tervuren</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="E209" s="16" t="n"/>
@@ -4822,17 +4822,13 @@
       <c r="H209" s="32" t="n"/>
       <c r="I209" s="13" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Achat matériel sportif - DECATHLON</t>
         </is>
       </c>
       <c r="J209" s="33" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K209" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="K209" s="28" t="n"/>
       <c r="L209" s="32" t="n"/>
     </row>
     <row r="210">
@@ -4842,18 +4838,18 @@
       <c r="H210" s="32" t="n"/>
       <c r="I210" s="13" t="inlineStr">
         <is>
-          <t>Lavage voiture</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="J210" s="33" t="n">
-        <v>32</v>
-      </c>
-      <c r="K210" s="28" t="n"/>
-      <c r="L210" s="32" t="inlineStr">
-        <is>
-          <t>Wash Time Tervuren</t>
-        </is>
-      </c>
+        <v>3.6</v>
+      </c>
+      <c r="K210" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L210" s="32" t="n"/>
     </row>
     <row r="211">
       <c r="E211" s="16" t="n"/>
@@ -4862,11 +4858,11 @@
       <c r="H211" s="32" t="n"/>
       <c r="I211" s="13" t="inlineStr">
         <is>
-          <t>Achat matériel sportif - DECATHLON</t>
+          <t>Proximus</t>
         </is>
       </c>
       <c r="J211" s="33" t="n">
-        <v>9</v>
+        <v>180.92</v>
       </c>
       <c r="K211" s="28" t="n"/>
       <c r="L211" s="32" t="n"/>
@@ -4878,11 +4874,11 @@
       <c r="H212" s="32" t="n"/>
       <c r="I212" s="13" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Carburant</t>
         </is>
       </c>
       <c r="J212" s="33" t="n">
-        <v>3.6</v>
+        <v>76.89</v>
       </c>
       <c r="K212" s="28" t="inlineStr">
         <is>
@@ -4896,16 +4892,20 @@
       <c r="F213" s="17" t="n"/>
       <c r="G213" s="31" t="n"/>
       <c r="H213" s="32" t="n"/>
-      <c r="I213" s="13" t="inlineStr">
-        <is>
-          <t>Proximus</t>
-        </is>
-      </c>
-      <c r="J213" s="33" t="n">
-        <v>180.92</v>
+      <c r="I213" s="40" t="inlineStr">
+        <is>
+          <t>Abonnement salle FitRaw</t>
+        </is>
+      </c>
+      <c r="J213" s="41" t="n">
+        <v>22.86</v>
       </c>
       <c r="K213" s="28" t="n"/>
-      <c r="L213" s="32" t="n"/>
+      <c r="L213" s="39" t="inlineStr">
+        <is>
+          <t>Sterrebeek — usage professionnel à confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="E214" s="16" t="n"/>
@@ -4914,17 +4914,13 @@
       <c r="H214" s="32" t="n"/>
       <c r="I214" s="13" t="inlineStr">
         <is>
-          <t>Carburant</t>
+          <t>Précompte salarial juillet 2026 Thibault Duchène</t>
         </is>
       </c>
       <c r="J214" s="33" t="n">
-        <v>76.89</v>
-      </c>
-      <c r="K214" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+        <v>2250</v>
+      </c>
+      <c r="K214" s="28" t="n"/>
       <c r="L214" s="32" t="n"/>
     </row>
     <row r="215">
@@ -4932,20 +4928,16 @@
       <c r="F215" s="17" t="n"/>
       <c r="G215" s="31" t="n"/>
       <c r="H215" s="32" t="n"/>
-      <c r="I215" s="40" t="inlineStr">
-        <is>
-          <t>Abonnement salle FitRaw</t>
-        </is>
-      </c>
-      <c r="J215" s="41" t="n">
-        <v>22.86</v>
+      <c r="I215" s="13" t="inlineStr">
+        <is>
+          <t>Assurance voiture - Yuzzu</t>
+        </is>
+      </c>
+      <c r="J215" s="33" t="n">
+        <v>1190.65</v>
       </c>
       <c r="K215" s="28" t="n"/>
-      <c r="L215" s="39" t="inlineStr">
-        <is>
-          <t>Sterrebeek — usage professionnel à confirmer</t>
-        </is>
-      </c>
+      <c r="L215" s="32" t="n"/>
     </row>
     <row r="216">
       <c r="E216" s="16" t="n"/>
@@ -4954,11 +4946,11 @@
       <c r="H216" s="32" t="n"/>
       <c r="I216" s="13" t="inlineStr">
         <is>
-          <t>Précompte salarial juillet 2026 Thibault Duchène</t>
+          <t>Entretien voiture - Monsieur Pneus</t>
         </is>
       </c>
       <c r="J216" s="33" t="n">
-        <v>2250</v>
+        <v>423.98</v>
       </c>
       <c r="K216" s="28" t="n"/>
       <c r="L216" s="32" t="n"/>
@@ -4970,103 +4962,107 @@
       <c r="H217" s="32" t="n"/>
       <c r="I217" s="13" t="inlineStr">
         <is>
-          <t>Assurance voiture - Yuzzu</t>
+          <t>SD Worx</t>
         </is>
       </c>
       <c r="J217" s="33" t="n">
-        <v>1190.65</v>
+        <v>333.29</v>
       </c>
       <c r="K217" s="28" t="n"/>
       <c r="L217" s="32" t="n"/>
     </row>
     <row r="218">
-      <c r="E218" s="16" t="n"/>
-      <c r="F218" s="17" t="n"/>
-      <c r="G218" s="31" t="n"/>
-      <c r="H218" s="32" t="n"/>
-      <c r="I218" s="13" t="inlineStr">
-        <is>
-          <t>Entretien voiture - Monsieur Pneus</t>
-        </is>
-      </c>
-      <c r="J218" s="33" t="n">
-        <v>423.98</v>
-      </c>
-      <c r="K218" s="28" t="n"/>
-      <c r="L218" s="32" t="n"/>
+      <c r="G218" s="34" t="n"/>
+      <c r="H218" s="35" t="n"/>
+      <c r="J218" s="34" t="n"/>
+      <c r="L218" s="35" t="n"/>
     </row>
     <row r="219">
-      <c r="E219" s="16" t="n"/>
-      <c r="F219" s="17" t="n"/>
-      <c r="G219" s="31" t="n"/>
-      <c r="H219" s="32" t="n"/>
-      <c r="I219" s="13" t="inlineStr">
-        <is>
-          <t>SD Worx</t>
-        </is>
-      </c>
-      <c r="J219" s="33" t="n">
-        <v>333.29</v>
-      </c>
-      <c r="K219" s="28" t="n"/>
-      <c r="L219" s="32" t="n"/>
+      <c r="G219" s="34" t="n"/>
+      <c r="H219" s="35" t="n"/>
+      <c r="J219" s="34" t="n"/>
+      <c r="L219" s="35" t="n"/>
     </row>
     <row r="220">
-      <c r="G220" s="34" t="n"/>
-      <c r="H220" s="35" t="n"/>
-      <c r="J220" s="34" t="n"/>
-      <c r="L220" s="35" t="n"/>
+      <c r="E220" s="16" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="F220" s="17" t="inlineStr">
+        <is>
+          <t>LAM2609</t>
+        </is>
+      </c>
+      <c r="G220" s="31" t="n">
+        <v>5341.8</v>
+      </c>
+      <c r="H220" s="32" t="n"/>
+      <c r="I220" s="28" t="inlineStr">
+        <is>
+          <t>Divers - Mister Minit</t>
+        </is>
+      </c>
+      <c r="J220" s="36" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="K220" s="28" t="n"/>
+      <c r="L220" s="32" t="n"/>
     </row>
     <row r="221">
-      <c r="G221" s="34" t="n"/>
-      <c r="H221" s="35" t="n"/>
-      <c r="J221" s="34" t="n"/>
-      <c r="L221" s="35" t="n"/>
+      <c r="E221" s="16" t="n"/>
+      <c r="F221" s="17" t="inlineStr">
+        <is>
+          <t>LAM2610</t>
+        </is>
+      </c>
+      <c r="G221" s="31" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H221" s="32" t="n"/>
+      <c r="I221" s="13" t="inlineStr">
+        <is>
+          <t>Achat matériel sportif - Bellissimo Sport</t>
+        </is>
+      </c>
+      <c r="J221" s="33" t="n">
+        <v>12</v>
+      </c>
+      <c r="K221" s="28" t="n"/>
+      <c r="L221" s="32" t="n"/>
     </row>
     <row r="222">
-      <c r="E222" s="16" t="inlineStr">
-        <is>
-          <t>Août</t>
-        </is>
-      </c>
-      <c r="F222" s="17" t="inlineStr">
-        <is>
-          <t>LAM2609</t>
-        </is>
-      </c>
-      <c r="G222" s="31" t="n">
-        <v>5341.8</v>
-      </c>
+      <c r="E222" s="16" t="n"/>
+      <c r="F222" s="17" t="n"/>
+      <c r="G222" s="31" t="n"/>
       <c r="H222" s="32" t="n"/>
-      <c r="I222" s="28" t="inlineStr">
-        <is>
-          <t>Divers - Mister Minit</t>
-        </is>
-      </c>
-      <c r="J222" s="36" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="K222" s="28" t="n"/>
+      <c r="I222" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J222" s="33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K222" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L222" s="32" t="n"/>
     </row>
     <row r="223">
       <c r="E223" s="16" t="n"/>
-      <c r="F223" s="17" t="inlineStr">
-        <is>
-          <t>LAM2610</t>
-        </is>
-      </c>
-      <c r="G223" s="31" t="n">
-        <v>5000</v>
-      </c>
+      <c r="F223" s="17" t="n"/>
+      <c r="G223" s="31" t="n"/>
       <c r="H223" s="32" t="n"/>
       <c r="I223" s="13" t="inlineStr">
         <is>
-          <t>Achat matériel sportif - Bellissimo Sport</t>
+          <t>Farys (eau)</t>
         </is>
       </c>
       <c r="J223" s="33" t="n">
-        <v>12</v>
+        <v>306</v>
       </c>
       <c r="K223" s="28" t="n"/>
       <c r="L223" s="32" t="n"/>
@@ -5078,17 +5074,13 @@
       <c r="H224" s="32" t="n"/>
       <c r="I224" s="13" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Electrabel</t>
         </is>
       </c>
       <c r="J224" s="33" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="K224" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+        <v>141.56</v>
+      </c>
+      <c r="K224" s="28" t="n"/>
       <c r="L224" s="32" t="n"/>
     </row>
     <row r="225">
@@ -5098,13 +5090,17 @@
       <c r="H225" s="32" t="n"/>
       <c r="I225" s="13" t="inlineStr">
         <is>
-          <t>Farys (eau)</t>
+          <t>Crédit voiture</t>
         </is>
       </c>
       <c r="J225" s="33" t="n">
-        <v>306</v>
-      </c>
-      <c r="K225" s="28" t="n"/>
+        <v>724.12</v>
+      </c>
+      <c r="K225" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L225" s="32" t="n"/>
     </row>
     <row r="226">
@@ -5112,16 +5108,20 @@
       <c r="F226" s="17" t="n"/>
       <c r="G226" s="31" t="n"/>
       <c r="H226" s="32" t="n"/>
-      <c r="I226" s="13" t="inlineStr">
-        <is>
-          <t>Electrabel</t>
-        </is>
-      </c>
-      <c r="J226" s="33" t="n">
-        <v>141.56</v>
+      <c r="I226" s="40" t="inlineStr">
+        <is>
+          <t>Abonnement club David Lloyd</t>
+        </is>
+      </c>
+      <c r="J226" s="41" t="n">
+        <v>493</v>
       </c>
       <c r="K226" s="28" t="n"/>
-      <c r="L226" s="32" t="n"/>
+      <c r="L226" s="39" t="inlineStr">
+        <is>
+          <t>Sterrebeek — usage professionnel à confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="E227" s="16" t="n"/>
@@ -5130,11 +5130,11 @@
       <c r="H227" s="32" t="n"/>
       <c r="I227" s="13" t="inlineStr">
         <is>
-          <t>Crédit voiture</t>
+          <t>Carburant</t>
         </is>
       </c>
       <c r="J227" s="33" t="n">
-        <v>724.12</v>
+        <v>98.54000000000001</v>
       </c>
       <c r="K227" s="28" t="inlineStr">
         <is>
@@ -5148,20 +5148,20 @@
       <c r="F228" s="17" t="n"/>
       <c r="G228" s="31" t="n"/>
       <c r="H228" s="32" t="n"/>
-      <c r="I228" s="40" t="inlineStr">
-        <is>
-          <t>Abonnement club David Lloyd</t>
-        </is>
-      </c>
-      <c r="J228" s="41" t="n">
-        <v>493</v>
-      </c>
-      <c r="K228" s="28" t="n"/>
-      <c r="L228" s="39" t="inlineStr">
-        <is>
-          <t>Sterrebeek — usage professionnel à confirmer</t>
-        </is>
-      </c>
+      <c r="I228" s="13" t="inlineStr">
+        <is>
+          <t>Carburant</t>
+        </is>
+      </c>
+      <c r="J228" s="33" t="n">
+        <v>84.61</v>
+      </c>
+      <c r="K228" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L228" s="32" t="n"/>
     </row>
     <row r="229">
       <c r="E229" s="16" t="n"/>
@@ -5170,18 +5170,22 @@
       <c r="H229" s="32" t="n"/>
       <c r="I229" s="13" t="inlineStr">
         <is>
-          <t>Carburant</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="J229" s="33" t="n">
-        <v>98.54000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="K229" s="28" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="L229" s="32" t="n"/>
+      <c r="L229" s="32" t="inlineStr">
+        <is>
+          <t>Côte d'Azur (France)</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="E230" s="16" t="n"/>
@@ -5190,18 +5194,22 @@
       <c r="H230" s="32" t="n"/>
       <c r="I230" s="13" t="inlineStr">
         <is>
-          <t>Carburant</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="J230" s="33" t="n">
-        <v>84.61</v>
+        <v>7.5</v>
       </c>
       <c r="K230" s="28" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="L230" s="32" t="n"/>
+      <c r="L230" s="32" t="inlineStr">
+        <is>
+          <t>Côte d'Azur (France)</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="E231" s="16" t="n"/>
@@ -5214,7 +5222,7 @@
         </is>
       </c>
       <c r="J231" s="33" t="n">
-        <v>5.4</v>
+        <v>7.5</v>
       </c>
       <c r="K231" s="28" t="inlineStr">
         <is>
@@ -5238,7 +5246,7 @@
         </is>
       </c>
       <c r="J232" s="33" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="K232" s="28" t="inlineStr">
         <is>
@@ -5262,7 +5270,7 @@
         </is>
       </c>
       <c r="J233" s="33" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="K233" s="28" t="inlineStr">
         <is>
@@ -5286,40 +5294,32 @@
         </is>
       </c>
       <c r="J234" s="33" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="K234" s="28" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="L234" s="32" t="inlineStr">
-        <is>
-          <t>Côte d'Azur (France)</t>
-        </is>
-      </c>
+      <c r="L234" s="32" t="n"/>
     </row>
     <row r="235">
       <c r="E235" s="16" t="n"/>
       <c r="F235" s="17" t="n"/>
       <c r="G235" s="31" t="n"/>
       <c r="H235" s="32" t="n"/>
-      <c r="I235" s="13" t="inlineStr">
-        <is>
-          <t>Parking</t>
-        </is>
-      </c>
-      <c r="J235" s="33" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K235" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L235" s="32" t="inlineStr">
-        <is>
-          <t>Côte d'Azur (France)</t>
+      <c r="I235" s="40" t="inlineStr">
+        <is>
+          <t>Achat - Castillon Fréjus</t>
+        </is>
+      </c>
+      <c r="J235" s="41" t="n">
+        <v>80</v>
+      </c>
+      <c r="K235" s="28" t="n"/>
+      <c r="L235" s="39" t="inlineStr">
+        <is>
+          <t>France — à identifier</t>
         </is>
       </c>
     </row>
@@ -5334,32 +5334,40 @@
         </is>
       </c>
       <c r="J236" s="33" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="K236" s="28" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="L236" s="32" t="n"/>
+      <c r="L236" s="32" t="inlineStr">
+        <is>
+          <t>Côte d'Azur (France)</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="E237" s="16" t="n"/>
       <c r="F237" s="17" t="n"/>
       <c r="G237" s="31" t="n"/>
       <c r="H237" s="32" t="n"/>
-      <c r="I237" s="40" t="inlineStr">
-        <is>
-          <t>Achat - Castillon Fréjus</t>
-        </is>
-      </c>
-      <c r="J237" s="41" t="n">
-        <v>80</v>
-      </c>
-      <c r="K237" s="28" t="n"/>
-      <c r="L237" s="39" t="inlineStr">
-        <is>
-          <t>France — à identifier</t>
+      <c r="I237" s="13" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="J237" s="33" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="K237" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L237" s="32" t="inlineStr">
+        <is>
+          <t>Côte d'Azur (France)</t>
         </is>
       </c>
     </row>
@@ -5374,7 +5382,7 @@
         </is>
       </c>
       <c r="J238" s="33" t="n">
-        <v>19</v>
+        <v>6.4</v>
       </c>
       <c r="K238" s="28" t="inlineStr">
         <is>
@@ -5398,7 +5406,7 @@
         </is>
       </c>
       <c r="J239" s="33" t="n">
-        <v>10.6</v>
+        <v>4.2</v>
       </c>
       <c r="K239" s="28" t="inlineStr">
         <is>
@@ -5418,44 +5426,36 @@
       <c r="H240" s="32" t="n"/>
       <c r="I240" s="13" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Paiement carte de crédit</t>
         </is>
       </c>
       <c r="J240" s="33" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="K240" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L240" s="32" t="inlineStr">
-        <is>
-          <t>Côte d'Azur (France)</t>
-        </is>
-      </c>
+        <v>2431.44</v>
+      </c>
+      <c r="K240" s="28" t="n"/>
+      <c r="L240" s="32" t="n"/>
     </row>
     <row r="241">
       <c r="E241" s="16" t="n"/>
       <c r="F241" s="17" t="n"/>
       <c r="G241" s="31" t="n"/>
       <c r="H241" s="32" t="n"/>
-      <c r="I241" s="13" t="inlineStr">
-        <is>
-          <t>Parking</t>
-        </is>
-      </c>
-      <c r="J241" s="33" t="n">
-        <v>4.2</v>
+      <c r="I241" s="40" t="inlineStr">
+        <is>
+          <t>Carburant</t>
+        </is>
+      </c>
+      <c r="J241" s="41" t="n">
+        <v>75.33</v>
       </c>
       <c r="K241" s="28" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="L241" s="32" t="inlineStr">
-        <is>
-          <t>Côte d'Azur (France)</t>
+      <c r="L241" s="39" t="inlineStr">
+        <is>
+          <t>E.Leclerc Mornas (France) — à confirmer</t>
         </is>
       </c>
     </row>
@@ -5466,13 +5466,17 @@
       <c r="H242" s="32" t="n"/>
       <c r="I242" s="13" t="inlineStr">
         <is>
-          <t>Paiement carte de crédit</t>
+          <t>Carburant</t>
         </is>
       </c>
       <c r="J242" s="33" t="n">
-        <v>2431.44</v>
-      </c>
-      <c r="K242" s="28" t="n"/>
+        <v>83.84999999999999</v>
+      </c>
+      <c r="K242" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L242" s="32" t="n"/>
     </row>
     <row r="243">
@@ -5480,24 +5484,20 @@
       <c r="F243" s="17" t="n"/>
       <c r="G243" s="31" t="n"/>
       <c r="H243" s="32" t="n"/>
-      <c r="I243" s="40" t="inlineStr">
+      <c r="I243" s="13" t="inlineStr">
         <is>
           <t>Carburant</t>
         </is>
       </c>
-      <c r="J243" s="41" t="n">
-        <v>75.33</v>
+      <c r="J243" s="33" t="n">
+        <v>77.98</v>
       </c>
       <c r="K243" s="28" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="L243" s="39" t="inlineStr">
-        <is>
-          <t>E.Leclerc Mornas (France) — à confirmer</t>
-        </is>
-      </c>
+      <c r="L243" s="32" t="n"/>
     </row>
     <row r="244">
       <c r="E244" s="16" t="n"/>
@@ -5506,11 +5506,11 @@
       <c r="H244" s="32" t="n"/>
       <c r="I244" s="13" t="inlineStr">
         <is>
-          <t>Carburant</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="J244" s="33" t="n">
-        <v>83.84999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="K244" s="28" t="inlineStr">
         <is>
@@ -5526,11 +5526,11 @@
       <c r="H245" s="32" t="n"/>
       <c r="I245" s="13" t="inlineStr">
         <is>
-          <t>Carburant</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="J245" s="33" t="n">
-        <v>77.98</v>
+        <v>5.4</v>
       </c>
       <c r="K245" s="28" t="inlineStr">
         <is>
@@ -5566,17 +5566,13 @@
       <c r="H247" s="32" t="n"/>
       <c r="I247" s="13" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Précompte salarial aout 2026 Thibault Duchène</t>
         </is>
       </c>
       <c r="J247" s="33" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="K247" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+        <v>2250</v>
+      </c>
+      <c r="K247" s="28" t="n"/>
       <c r="L247" s="32" t="n"/>
     </row>
     <row r="248">
@@ -5586,17 +5582,13 @@
       <c r="H248" s="32" t="n"/>
       <c r="I248" s="13" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Partena</t>
         </is>
       </c>
       <c r="J248" s="33" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="K248" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+        <v>1747.34</v>
+      </c>
+      <c r="K248" s="28" t="n"/>
       <c r="L248" s="32" t="n"/>
     </row>
     <row r="249">
@@ -5606,11 +5598,11 @@
       <c r="H249" s="32" t="n"/>
       <c r="I249" s="13" t="inlineStr">
         <is>
-          <t>Précompte salarial aout 2026 Thibault Duchène</t>
+          <t>SD Worx</t>
         </is>
       </c>
       <c r="J249" s="33" t="n">
-        <v>2250</v>
+        <v>333.29</v>
       </c>
       <c r="K249" s="28" t="n"/>
       <c r="L249" s="32" t="n"/>
@@ -5622,11 +5614,11 @@
       <c r="H250" s="32" t="n"/>
       <c r="I250" s="13" t="inlineStr">
         <is>
-          <t>Partena</t>
+          <t>Electrabel</t>
         </is>
       </c>
       <c r="J250" s="33" t="n">
-        <v>1747.34</v>
+        <v>294.73</v>
       </c>
       <c r="K250" s="28" t="n"/>
       <c r="L250" s="32" t="n"/>
@@ -5638,13 +5630,17 @@
       <c r="H251" s="32" t="n"/>
       <c r="I251" s="13" t="inlineStr">
         <is>
-          <t>SD Worx</t>
+          <t>Vlaamse Belastingsdienst - taxe de circulation</t>
         </is>
       </c>
       <c r="J251" s="33" t="n">
-        <v>333.29</v>
-      </c>
-      <c r="K251" s="28" t="n"/>
+        <v>167.59</v>
+      </c>
+      <c r="K251" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L251" s="32" t="n"/>
     </row>
     <row r="252">
@@ -5654,78 +5650,42 @@
       <c r="H252" s="32" t="n"/>
       <c r="I252" s="13" t="inlineStr">
         <is>
-          <t>Electrabel</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="J252" s="33" t="n">
-        <v>294.73</v>
-      </c>
-      <c r="K252" s="28" t="n"/>
+        <v>1.7</v>
+      </c>
+      <c r="K252" s="28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L252" s="32" t="n"/>
     </row>
     <row r="253">
-      <c r="E253" s="16" t="n"/>
-      <c r="F253" s="17" t="n"/>
-      <c r="G253" s="31" t="n"/>
-      <c r="H253" s="32" t="n"/>
-      <c r="I253" s="13" t="inlineStr">
-        <is>
-          <t>Vlaamse Belastingsdienst - taxe de circulation</t>
-        </is>
-      </c>
-      <c r="J253" s="33" t="n">
-        <v>167.59</v>
-      </c>
-      <c r="K253" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L253" s="32" t="n"/>
+      <c r="G253" s="34" t="n"/>
+      <c r="H253" s="35" t="n"/>
+      <c r="J253" s="34" t="n"/>
+      <c r="L253" s="35" t="n"/>
     </row>
     <row r="254">
-      <c r="E254" s="16" t="n"/>
-      <c r="F254" s="17" t="n"/>
-      <c r="G254" s="31" t="n"/>
-      <c r="H254" s="32" t="n"/>
-      <c r="I254" s="13" t="inlineStr">
-        <is>
-          <t>Parking</t>
-        </is>
-      </c>
-      <c r="J254" s="33" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="K254" s="28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L254" s="32" t="n"/>
+      <c r="G254" s="34" t="n"/>
+      <c r="H254" s="35" t="n"/>
+      <c r="J254" s="34" t="n"/>
+      <c r="L254" s="35" t="n"/>
     </row>
     <row r="255">
-      <c r="G255" s="34" t="n"/>
+      <c r="G255" s="34">
+        <f>SUM(G6:G254)</f>
+        <v/>
+      </c>
       <c r="H255" s="35" t="n"/>
-      <c r="J255" s="34" t="n"/>
+      <c r="J255" s="34">
+        <f>SUM(J6:J254)</f>
+        <v/>
+      </c>
       <c r="L255" s="35" t="n"/>
-    </row>
-    <row r="256">
-      <c r="G256" s="34" t="n"/>
-      <c r="H256" s="35" t="n"/>
-      <c r="J256" s="34" t="n"/>
-      <c r="L256" s="35" t="n"/>
-    </row>
-    <row r="257">
-      <c r="G257" s="34">
-        <f>SUM(G6:G256)</f>
-        <v/>
-      </c>
-      <c r="H257" s="35" t="n"/>
-      <c r="J257" s="34">
-        <f>SUM(J6:J256)</f>
-        <v/>
-      </c>
-      <c r="L257" s="35" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
